--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -75,11 +75,50 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+Administrator:
+游客来访的频率（即游客的生成频率）
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Administrator:
+百分比；
+在赌场进行曝光的时候，游客来访间隔的时间=游客基础来访间隔 * 曝光度来访间隔系数
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 空值表示不需要道具</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -126,12 +165,21 @@
     <t>曝光持续基础时长（秒）</t>
   </si>
   <si>
+    <t>游客基础来访间隔(秒)</t>
+  </si>
+  <si>
+    <t>曝光度来访间隔系数</t>
+  </si>
+  <si>
     <t>升级消耗道具</t>
   </si>
   <si>
     <t>升级产出能量</t>
   </si>
   <si>
+    <t>离线收益时长（分）</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -153,10 +201,19 @@
     <t>ViewableDuration</t>
   </si>
   <si>
+    <t>BaseVisitInterval</t>
+  </si>
+  <si>
+    <t>VisitIntervalCoefficient</t>
+  </si>
+  <si>
     <t>UpgradeCost</t>
   </si>
   <si>
     <t>UpgradeOutput</t>
+  </si>
+  <si>
+    <t>OfflineDuration</t>
   </si>
   <si>
     <t>赌场</t>
@@ -828,18 +885,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1158,8 +1224,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
@@ -1167,11 +1233,15 @@
     <col min="4" max="4" width="14.5" customWidth="1"/>
     <col min="5" max="5" width="16.25" customWidth="1"/>
     <col min="6" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="32.375" customWidth="1"/>
-    <col min="8" max="16382" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="29.25" customWidth="1"/>
+    <col min="8" max="8" width="23.375" customWidth="1"/>
+    <col min="9" max="9" width="23.625" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="18.75" customWidth="1"/>
+    <col min="12" max="16384" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:8">
+    <row r="1" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,223 +1260,307 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:8">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>8</v>
+    <row r="2" customHeight="1" spans="1:11">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:8">
-      <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="3" t="s">
+    <row r="3" customHeight="1" spans="1:11">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="H3" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+    <row r="4" customHeight="1" spans="1:11">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="7"/>
     </row>
-    <row r="5" customHeight="1" spans="1:8">
-      <c r="A5" s="3">
+    <row r="5" customHeight="1" spans="1:11">
+      <c r="A5" s="4">
         <v>1001</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4">
         <v>0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>100</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>1000</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>3600</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="5">
+      <c r="G5" s="4">
+        <v>60</v>
+      </c>
+      <c r="H5" s="4">
+        <v>90</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="8">
         <v>0</v>
       </c>
+      <c r="K5" s="6">
+        <v>120</v>
+      </c>
     </row>
-    <row r="6" customHeight="1" spans="1:8">
-      <c r="A6" s="3">
+    <row r="6" customHeight="1" spans="1:11">
+      <c r="A6" s="4">
         <v>1002</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>100</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>2000</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>3600</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="G6" s="4">
+        <v>65</v>
+      </c>
+      <c r="H6" s="4">
+        <v>80</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="8">
         <v>20</v>
       </c>
+      <c r="K6" s="6">
+        <v>120</v>
+      </c>
     </row>
-    <row r="7" customHeight="1" spans="1:8">
-      <c r="A7" s="3">
+    <row r="7" customHeight="1" spans="1:11">
+      <c r="A7" s="4">
         <v>1003</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>100</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <v>3000</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>3600</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7" s="4">
+        <v>70</v>
+      </c>
+      <c r="H7" s="4">
+        <v>75</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="8">
         <v>30</v>
       </c>
+      <c r="K7" s="6">
+        <v>120</v>
+      </c>
     </row>
-    <row r="8" customHeight="1" spans="1:8">
-      <c r="A8" s="3">
+    <row r="8" customHeight="1" spans="1:11">
+      <c r="A8" s="4">
         <v>1004</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="4">
         <v>4000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>3600</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="G8" s="4">
+        <v>75</v>
+      </c>
+      <c r="H8" s="4">
+        <v>70</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="8">
         <v>40</v>
       </c>
+      <c r="K8" s="6">
+        <v>120</v>
+      </c>
     </row>
-    <row r="9" customHeight="1" spans="1:8">
-      <c r="A9" s="3">
+    <row r="9" customHeight="1" spans="1:11">
+      <c r="A9" s="4">
         <v>1005</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="4">
         <v>5000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>3600</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="G9" s="4">
+        <v>80</v>
+      </c>
+      <c r="H9" s="4">
+        <v>60</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="8">
         <v>50</v>
       </c>
+      <c r="K9" s="6">
+        <v>120</v>
+      </c>
     </row>
-    <row r="10" customHeight="1" spans="1:8">
-      <c r="A10" s="3">
+    <row r="10" customHeight="1" spans="1:11">
+      <c r="A10" s="4">
         <v>1006</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="B10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="4">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>6000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>3600</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="5">
+      <c r="G10" s="4">
+        <v>85</v>
+      </c>
+      <c r="H10" s="4">
+        <v>55</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="8">
         <v>60</v>
+      </c>
+      <c r="K10" s="6">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -34,7 +34,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -81,22 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-百分比；
-在赌场进行曝光的时候，游客来访间隔的时间=游客基础来访间隔 * 曝光度来访间隔系数
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -118,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -153,25 +138,19 @@
     <t>名称</t>
   </si>
   <si>
+    <t>地区 ID</t>
+  </si>
+  <si>
     <t>等级</t>
   </si>
   <si>
     <t>基础繁荣度</t>
   </si>
   <si>
-    <t>开启曝光所需值</t>
-  </si>
-  <si>
-    <t>曝光持续基础时长（秒）</t>
-  </si>
-  <si>
     <t>游客基础来访间隔(秒)</t>
   </si>
   <si>
-    <t>曝光度来访间隔系数</t>
-  </si>
-  <si>
-    <t>升级消耗道具</t>
+    <t>升级消耗数量</t>
   </si>
   <si>
     <t>升级产出能量</t>
@@ -183,30 +162,21 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{|}</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
+    <t>RegionID</t>
+  </si>
+  <si>
     <t>level</t>
   </si>
   <si>
     <t>Prosperity</t>
   </si>
   <si>
-    <t>ExposureValue</t>
-  </si>
-  <si>
-    <t>ViewableDuration</t>
-  </si>
-  <si>
     <t>BaseVisitInterval</t>
   </si>
   <si>
-    <t>VisitIntervalCoefficient</t>
-  </si>
-  <si>
     <t>UpgradeCost</t>
   </si>
   <si>
@@ -216,19 +186,7 @@
     <t>OfflineDuration</t>
   </si>
   <si>
-    <t>赌场</t>
-  </si>
-  <si>
-    <t>1990000_10000|1970000_1000</t>
-  </si>
-  <si>
-    <t>1990000_50000|1970000_1000</t>
-  </si>
-  <si>
-    <t>1990000_100000|1970000_1000</t>
-  </si>
-  <si>
-    <t>1990000_200000|1970000_1000</t>
+    <t>拉斯维加斯</t>
   </si>
 </sst>
 </file>
@@ -885,27 +843,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1224,24 +1173,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
-    <col min="3" max="3" width="11.875" customWidth="1"/>
-    <col min="4" max="4" width="14.5" customWidth="1"/>
-    <col min="5" max="5" width="16.25" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="29.25" customWidth="1"/>
-    <col min="8" max="8" width="23.375" customWidth="1"/>
-    <col min="9" max="9" width="23.625" customWidth="1"/>
-    <col min="10" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="18.75" customWidth="1"/>
-    <col min="12" max="16384" width="15.625" customWidth="1"/>
+    <col min="3" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="29.25" customWidth="1"/>
+    <col min="7" max="7" width="29.75" customWidth="1"/>
+    <col min="8" max="8" width="18.5" customWidth="1"/>
+    <col min="9" max="9" width="18.75" customWidth="1"/>
+    <col min="10" max="16382" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1260,306 +1206,256 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:9">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:9">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:11">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+    <row r="4" customHeight="1" spans="1:9">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="7"/>
     </row>
-    <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="4">
+    <row r="5" customHeight="1" spans="1:9">
+      <c r="A5" s="3">
+        <f t="shared" ref="A5:A10" si="0">C5*1000+D5</f>
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:9">
+      <c r="A6" s="3">
+        <f t="shared" si="0"/>
         <v>1001</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
         <v>100</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F6" s="3">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3">
         <v>1000</v>
       </c>
-      <c r="F5" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="H6" s="5">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:9">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
+        <v>1002</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>100</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H7" s="5">
+        <v>30</v>
+      </c>
+      <c r="I7" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:9">
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H8" s="5">
+        <v>40</v>
+      </c>
+      <c r="I8" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:9">
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
+        <v>1004</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H9" s="5">
+        <v>50</v>
+      </c>
+      <c r="I9" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:9">
+      <c r="A10" s="3">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H10" s="5">
         <v>60</v>
       </c>
-      <c r="H5" s="4">
-        <v>90</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="8">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:11">
-      <c r="A6" s="4">
-        <v>1002</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <v>100</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2000</v>
-      </c>
-      <c r="F6" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G6" s="4">
-        <v>65</v>
-      </c>
-      <c r="H6" s="4">
-        <v>80</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="8">
-        <v>20</v>
-      </c>
-      <c r="K6" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="4">
-        <v>1003</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2</v>
-      </c>
-      <c r="D7" s="4">
-        <v>100</v>
-      </c>
-      <c r="E7" s="4">
-        <v>3000</v>
-      </c>
-      <c r="F7" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G7" s="4">
-        <v>70</v>
-      </c>
-      <c r="H7" s="4">
-        <v>75</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="8">
-        <v>30</v>
-      </c>
-      <c r="K7" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="4">
-        <v>1004</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="4">
-        <v>3</v>
-      </c>
-      <c r="D8" s="4">
-        <v>100</v>
-      </c>
-      <c r="E8" s="4">
-        <v>4000</v>
-      </c>
-      <c r="F8" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G8" s="4">
-        <v>75</v>
-      </c>
-      <c r="H8" s="4">
-        <v>70</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="8">
-        <v>40</v>
-      </c>
-      <c r="K8" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="4">
-        <v>1005</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="4">
-        <v>4</v>
-      </c>
-      <c r="D9" s="4">
-        <v>100</v>
-      </c>
-      <c r="E9" s="4">
-        <v>5000</v>
-      </c>
-      <c r="F9" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G9" s="4">
-        <v>80</v>
-      </c>
-      <c r="H9" s="4">
-        <v>60</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="8">
-        <v>50</v>
-      </c>
-      <c r="K9" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="4">
-        <v>1006</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4">
-        <v>5</v>
-      </c>
-      <c r="D10" s="4">
-        <v>100</v>
-      </c>
-      <c r="E10" s="4">
-        <v>6000</v>
-      </c>
-      <c r="F10" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G10" s="4">
-        <v>85</v>
-      </c>
-      <c r="H10" s="4">
-        <v>55</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="8">
-        <v>60</v>
-      </c>
-      <c r="K10" s="6">
+      <c r="I10" s="5">
         <v>120</v>
       </c>
     </row>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
     <t>名称</t>
   </si>
   <si>
-    <t>地区 ID</t>
+    <t>场景 ID</t>
   </si>
   <si>
     <t>等级</t>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -367,16 +367,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -572,7 +572,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -584,6 +584,19 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -719,7 +732,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -731,34 +744,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
@@ -843,7 +856,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -860,6 +873,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1173,7 +1189,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
@@ -1283,7 +1299,7 @@
     </row>
     <row r="5" customHeight="1" spans="1:9">
       <c r="A5" s="3">
-        <f t="shared" ref="A5:A10" si="0">C5*1000+D5</f>
+        <f t="shared" ref="A5:A15" si="0">C5*1000+D5</f>
         <v>1000</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1299,7 +1315,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="5">
@@ -1327,12 +1343,12 @@
         <v>100</v>
       </c>
       <c r="F6" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H6" s="5">
+        <v>115</v>
+      </c>
+      <c r="H6" s="6">
         <v>20</v>
       </c>
       <c r="I6" s="5">
@@ -1357,12 +1373,12 @@
         <v>100</v>
       </c>
       <c r="F7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H7" s="5">
+        <v>440</v>
+      </c>
+      <c r="H7" s="6">
         <v>30</v>
       </c>
       <c r="I7" s="5">
@@ -1387,12 +1403,12 @@
         <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H8" s="5">
+        <v>975</v>
+      </c>
+      <c r="H8" s="6">
         <v>40</v>
       </c>
       <c r="I8" s="5">
@@ -1417,12 +1433,12 @@
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H9" s="5">
+        <v>1720</v>
+      </c>
+      <c r="H9" s="6">
         <v>50</v>
       </c>
       <c r="I9" s="5">
@@ -1447,15 +1463,165 @@
         <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H10" s="5">
+        <v>2675</v>
+      </c>
+      <c r="H10" s="6">
         <v>60</v>
       </c>
       <c r="I10" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:9">
+      <c r="A11" s="3">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3">
+        <v>100</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3840</v>
+      </c>
+      <c r="H11" s="6">
+        <v>70</v>
+      </c>
+      <c r="I11" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:9">
+      <c r="A12" s="3">
+        <f t="shared" si="0"/>
+        <v>1007</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5215</v>
+      </c>
+      <c r="H12" s="6">
+        <v>80</v>
+      </c>
+      <c r="I12" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:9">
+      <c r="A13" s="3">
+        <f t="shared" si="0"/>
+        <v>1008</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3">
+        <v>100</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H13" s="6">
+        <v>90</v>
+      </c>
+      <c r="I13" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:9">
+      <c r="A14" s="3">
+        <f t="shared" si="0"/>
+        <v>1009</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>8595</v>
+      </c>
+      <c r="H14" s="6">
+        <v>100</v>
+      </c>
+      <c r="I14" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="3">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>10600</v>
+      </c>
+      <c r="H15" s="6">
+        <v>110</v>
+      </c>
+      <c r="I15" s="5">
         <v>120</v>
       </c>
     </row>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -99,11 +99,33 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+在刷新时间点到了以后，在生成池中重随5次</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 空值表示不需要道具</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
   <si>
     <t>ID</t>
   </si>
@@ -150,6 +172,9 @@
     <t>游客基础来访间隔(秒)</t>
   </si>
   <si>
+    <t>游客生成数量</t>
+  </si>
+  <si>
     <t>升级消耗数量</t>
   </si>
   <si>
@@ -175,6 +200,9 @@
   </si>
   <si>
     <t>BaseVisitInterval</t>
+  </si>
+  <si>
+    <t>VisitorSpawnCount</t>
   </si>
   <si>
     <t>UpgradeCost</t>
@@ -367,12 +395,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1189,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
@@ -1197,13 +1225,14 @@
     <col min="3" max="4" width="11.875" customWidth="1"/>
     <col min="5" max="5" width="14.5" customWidth="1"/>
     <col min="6" max="6" width="29.25" customWidth="1"/>
-    <col min="7" max="7" width="29.75" customWidth="1"/>
-    <col min="8" max="8" width="18.5" customWidth="1"/>
-    <col min="9" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="16382" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="29.75" customWidth="1"/>
+    <col min="9" max="9" width="18.5" customWidth="1"/>
+    <col min="10" max="10" width="18.75" customWidth="1"/>
+    <col min="11" max="16383" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:9">
+    <row r="1" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1231,62 +1260,71 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:9">
+    <row r="2" customHeight="1" spans="1:10">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:9">
+    <row r="3" customHeight="1" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="I3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" customHeight="1" spans="1:9">
+    <row r="4" customHeight="1" spans="1:10">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1294,16 +1332,17 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
     </row>
-    <row r="5" customHeight="1" spans="1:9">
+    <row r="5" customHeight="1" spans="1:10">
       <c r="A5" s="3">
         <f t="shared" ref="A5:A15" si="0">C5*1000+D5</f>
         <v>1000</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -1315,23 +1354,26 @@
         <v>100</v>
       </c>
       <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="5">
         <v>0</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:9">
+    <row r="6" customHeight="1" spans="1:10">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>1001</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1343,25 +1385,28 @@
         <v>100</v>
       </c>
       <c r="F6" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3">
         <v>115</v>
       </c>
-      <c r="H6" s="6">
+      <c r="I6" s="6">
         <v>20</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:9">
+    <row r="7" customHeight="1" spans="1:10">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -1373,25 +1418,28 @@
         <v>100</v>
       </c>
       <c r="F7" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3">
+        <v>5</v>
+      </c>
+      <c r="H7" s="3">
         <v>440</v>
       </c>
-      <c r="H7" s="6">
+      <c r="I7" s="6">
         <v>30</v>
       </c>
-      <c r="I7" s="5">
+      <c r="J7" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:9">
+    <row r="8" customHeight="1" spans="1:10">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1403,25 +1451,28 @@
         <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="3">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3">
         <v>975</v>
       </c>
-      <c r="H8" s="6">
+      <c r="I8" s="6">
         <v>40</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:9">
+    <row r="9" customHeight="1" spans="1:10">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -1433,25 +1484,28 @@
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3">
         <v>1720</v>
       </c>
-      <c r="H9" s="6">
+      <c r="I9" s="6">
         <v>50</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:9">
+    <row r="10" customHeight="1" spans="1:10">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1463,25 +1517,28 @@
         <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
         <v>2675</v>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <v>60</v>
       </c>
-      <c r="I10" s="5">
+      <c r="J10" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:9">
+    <row r="11" customHeight="1" spans="1:10">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -1493,25 +1550,28 @@
         <v>100</v>
       </c>
       <c r="F11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" s="3">
+        <v>5</v>
+      </c>
+      <c r="H11" s="3">
         <v>3840</v>
       </c>
-      <c r="H11" s="6">
+      <c r="I11" s="6">
         <v>70</v>
       </c>
-      <c r="I11" s="5">
+      <c r="J11" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:9">
+    <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1523,25 +1583,28 @@
         <v>100</v>
       </c>
       <c r="F12" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" s="3">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3">
         <v>5215</v>
       </c>
-      <c r="H12" s="6">
+      <c r="I12" s="6">
         <v>80</v>
       </c>
-      <c r="I12" s="5">
+      <c r="J12" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:9">
+    <row r="13" customHeight="1" spans="1:10">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
@@ -1553,25 +1616,28 @@
         <v>100</v>
       </c>
       <c r="F13" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="3">
+        <v>5</v>
+      </c>
+      <c r="H13" s="3">
         <v>6800</v>
       </c>
-      <c r="H13" s="6">
+      <c r="I13" s="6">
         <v>90</v>
       </c>
-      <c r="I13" s="5">
+      <c r="J13" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:9">
+    <row r="14" customHeight="1" spans="1:10">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>1009</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1583,25 +1649,28 @@
         <v>100</v>
       </c>
       <c r="F14" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>8595</v>
       </c>
-      <c r="H14" s="6">
+      <c r="I14" s="6">
         <v>100</v>
       </c>
-      <c r="I14" s="5">
+      <c r="J14" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
+    <row r="15" customHeight="1" spans="1:10">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>1010</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -1613,15 +1682,18 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="3">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3">
         <v>10600</v>
       </c>
-      <c r="H15" s="6">
+      <c r="I15" s="6">
         <v>110</v>
       </c>
-      <c r="I15" s="5">
+      <c r="J15" s="5">
         <v>120</v>
       </c>
     </row>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="21">
   <si>
     <t>ID</t>
   </si>
@@ -1217,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
@@ -1338,8 +1338,8 @@
     </row>
     <row r="5" customHeight="1" spans="1:10">
       <c r="A5" s="3">
-        <f t="shared" ref="A5:A15" si="0">C5*1000+D5</f>
-        <v>1000</v>
+        <f t="shared" ref="A5:A14" si="0">C5*1000+D5</f>
+        <v>1001</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
@@ -1348,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -1359,9 +1359,11 @@
       <c r="G5" s="3">
         <v>5</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="5">
-        <v>0</v>
+      <c r="H5" s="3">
+        <v>115</v>
+      </c>
+      <c r="I5" s="6">
+        <v>20</v>
       </c>
       <c r="J5" s="5">
         <v>120</v>
@@ -1370,7 +1372,7 @@
     <row r="6" customHeight="1" spans="1:10">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
@@ -1379,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="3">
         <v>100</v>
@@ -1391,10 +1393,10 @@
         <v>5</v>
       </c>
       <c r="H6" s="3">
-        <v>115</v>
+        <v>440</v>
       </c>
       <c r="I6" s="6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J6" s="5">
         <v>120</v>
@@ -1403,7 +1405,7 @@
     <row r="7" customHeight="1" spans="1:10">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -1412,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3">
         <v>100</v>
@@ -1424,10 +1426,10 @@
         <v>5</v>
       </c>
       <c r="H7" s="3">
-        <v>440</v>
+        <v>975</v>
       </c>
       <c r="I7" s="6">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J7" s="5">
         <v>120</v>
@@ -1436,7 +1438,7 @@
     <row r="8" customHeight="1" spans="1:10">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>20</v>
@@ -1445,7 +1447,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -1457,10 +1459,10 @@
         <v>5</v>
       </c>
       <c r="H8" s="3">
-        <v>975</v>
+        <v>1720</v>
       </c>
       <c r="I8" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J8" s="5">
         <v>120</v>
@@ -1469,7 +1471,7 @@
     <row r="9" customHeight="1" spans="1:10">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -1478,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -1490,10 +1492,10 @@
         <v>5</v>
       </c>
       <c r="H9" s="3">
-        <v>1720</v>
+        <v>2675</v>
       </c>
       <c r="I9" s="6">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J9" s="5">
         <v>120</v>
@@ -1502,7 +1504,7 @@
     <row r="10" customHeight="1" spans="1:10">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
@@ -1511,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
@@ -1523,10 +1525,10 @@
         <v>5</v>
       </c>
       <c r="H10" s="3">
-        <v>2675</v>
+        <v>3840</v>
       </c>
       <c r="I10" s="6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J10" s="5">
         <v>120</v>
@@ -1535,7 +1537,7 @@
     <row r="11" customHeight="1" spans="1:10">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>20</v>
@@ -1544,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
@@ -1556,10 +1558,10 @@
         <v>5</v>
       </c>
       <c r="H11" s="3">
-        <v>3840</v>
+        <v>5215</v>
       </c>
       <c r="I11" s="6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J11" s="5">
         <v>120</v>
@@ -1568,7 +1570,7 @@
     <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
@@ -1577,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
@@ -1589,10 +1591,10 @@
         <v>5</v>
       </c>
       <c r="H12" s="3">
-        <v>5215</v>
+        <v>6800</v>
       </c>
       <c r="I12" s="6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J12" s="5">
         <v>120</v>
@@ -1601,7 +1603,7 @@
     <row r="13" customHeight="1" spans="1:10">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
@@ -1610,7 +1612,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3">
         <v>100</v>
@@ -1622,10 +1624,10 @@
         <v>5</v>
       </c>
       <c r="H13" s="3">
-        <v>6800</v>
+        <v>8595</v>
       </c>
       <c r="I13" s="6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J13" s="5">
         <v>120</v>
@@ -1634,7 +1636,7 @@
     <row r="14" customHeight="1" spans="1:10">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -1643,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
@@ -1655,45 +1657,12 @@
         <v>5</v>
       </c>
       <c r="H14" s="3">
-        <v>8595</v>
+        <v>999999</v>
       </c>
       <c r="I14" s="6">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J14" s="5">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:10">
-      <c r="A15" s="3">
-        <f t="shared" si="0"/>
-        <v>1010</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3">
-        <v>10</v>
-      </c>
-      <c r="E15" s="3">
-        <v>100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3">
-        <v>10600</v>
-      </c>
-      <c r="I15" s="6">
-        <v>110</v>
-      </c>
-      <c r="J15" s="5">
         <v>120</v>
       </c>
     </row>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -1360,13 +1360,13 @@
         <v>5</v>
       </c>
       <c r="H5" s="3">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="I5" s="6">
         <v>20</v>
       </c>
       <c r="J5" s="5">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:10">
@@ -1393,13 +1393,13 @@
         <v>5</v>
       </c>
       <c r="H6" s="3">
-        <v>440</v>
+        <v>10</v>
       </c>
       <c r="I6" s="6">
         <v>30</v>
       </c>
       <c r="J6" s="5">
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:10">
@@ -1426,7 +1426,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3">
-        <v>975</v>
+        <v>15</v>
       </c>
       <c r="I7" s="6">
         <v>40</v>
@@ -1459,13 +1459,13 @@
         <v>5</v>
       </c>
       <c r="H8" s="3">
-        <v>1720</v>
+        <v>20</v>
       </c>
       <c r="I8" s="6">
         <v>50</v>
       </c>
       <c r="J8" s="5">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:10">
@@ -1492,13 +1492,13 @@
         <v>5</v>
       </c>
       <c r="H9" s="3">
-        <v>2675</v>
+        <v>25</v>
       </c>
       <c r="I9" s="6">
         <v>60</v>
       </c>
       <c r="J9" s="5">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:10">
@@ -1525,13 +1525,13 @@
         <v>5</v>
       </c>
       <c r="H10" s="3">
-        <v>3840</v>
+        <v>30</v>
       </c>
       <c r="I10" s="6">
         <v>70</v>
       </c>
       <c r="J10" s="5">
-        <v>120</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:10">
@@ -1558,13 +1558,13 @@
         <v>5</v>
       </c>
       <c r="H11" s="3">
-        <v>5215</v>
+        <v>35</v>
       </c>
       <c r="I11" s="6">
         <v>80</v>
       </c>
       <c r="J11" s="5">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:10">
@@ -1591,13 +1591,13 @@
         <v>5</v>
       </c>
       <c r="H12" s="3">
-        <v>6800</v>
+        <v>40</v>
       </c>
       <c r="I12" s="6">
         <v>90</v>
       </c>
       <c r="J12" s="5">
-        <v>120</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:10">
@@ -1624,13 +1624,13 @@
         <v>5</v>
       </c>
       <c r="H13" s="3">
-        <v>8595</v>
+        <v>45</v>
       </c>
       <c r="I13" s="6">
         <v>100</v>
       </c>
       <c r="J13" s="5">
-        <v>120</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:10">
@@ -1663,7 +1663,7 @@
         <v>110</v>
       </c>
       <c r="J14" s="5">
-        <v>120</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -1354,10 +1354,10 @@
         <v>100</v>
       </c>
       <c r="F5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H5" s="3">
         <v>5</v>
@@ -1387,10 +1387,10 @@
         <v>100</v>
       </c>
       <c r="F6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H6" s="3">
         <v>10</v>
@@ -1420,10 +1420,10 @@
         <v>100</v>
       </c>
       <c r="F7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="3">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="H7" s="3">
         <v>15</v>
@@ -1453,10 +1453,10 @@
         <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="3">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3">
         <v>20</v>
@@ -1489,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="3">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3">
         <v>25</v>
@@ -1522,7 +1522,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="3">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="H10" s="3">
         <v>30</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="3">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="H11" s="3">
         <v>35</v>
@@ -1588,7 +1588,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="3">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="H12" s="3">
         <v>40</v>
@@ -1621,7 +1621,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="3">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3">
         <v>45</v>
@@ -1654,7 +1654,7 @@
         <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="H14" s="3">
         <v>999999</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="21">
   <si>
     <t>ID</t>
   </si>
@@ -227,7 +227,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,16 +239,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -754,156 +758,174 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1217,58 +1239,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
-    <col min="2" max="2" width="11.625" customWidth="1"/>
-    <col min="3" max="4" width="11.875" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
-    <col min="6" max="6" width="29.25" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="29.75" customWidth="1"/>
-    <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="18.75" customWidth="1"/>
-    <col min="11" max="16383" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="11.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="29.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="24" style="2" customWidth="1"/>
+    <col min="8" max="8" width="29.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.75" style="2" customWidth="1"/>
+    <col min="11" max="16383" width="15.625" style="2" customWidth="1"/>
+    <col min="16384" max="16384" width="15.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="5"/>
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1294,11 +1317,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="5"/>
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1317,353 +1340,2003 @@
       <c r="H3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:10">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
     </row>
     <row r="5" customHeight="1" spans="1:10">
-      <c r="A5" s="3">
-        <f t="shared" ref="A5:A14" si="0">C5*1000+D5</f>
+      <c r="A5" s="8">
+        <f t="shared" ref="A5:A64" si="0">C5*1000+D5</f>
         <v>1001</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>100</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="B5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>100</v>
+      </c>
+      <c r="F5" s="8">
         <v>2</v>
       </c>
-      <c r="G5" s="3">
-        <v>20</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="G5" s="8">
+        <v>20</v>
+      </c>
+      <c r="H5" s="8">
         <v>5</v>
       </c>
-      <c r="I5" s="6">
-        <v>20</v>
-      </c>
-      <c r="J5" s="5">
+      <c r="I5" s="11">
+        <v>20</v>
+      </c>
+      <c r="J5" s="12">
         <v>60</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:10">
-      <c r="A6" s="3">
+      <c r="A6" s="8">
         <f t="shared" si="0"/>
         <v>1002</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="B6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8">
         <v>2</v>
       </c>
-      <c r="E6" s="3">
-        <v>100</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="E6" s="8">
+        <v>100</v>
+      </c>
+      <c r="F6" s="8">
         <v>2</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="8">
         <v>40</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="8">
         <v>10</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="11">
         <v>30</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:10">
+      <c r="A7" s="8">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>3</v>
+      </c>
+      <c r="E7" s="8">
+        <v>100</v>
+      </c>
+      <c r="F7" s="8">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8">
+        <v>60</v>
+      </c>
+      <c r="H7" s="8">
+        <v>15</v>
+      </c>
+      <c r="I7" s="11">
+        <v>40</v>
+      </c>
+      <c r="J7" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:10">
+      <c r="A8" s="8">
+        <f t="shared" si="0"/>
+        <v>1004</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="8">
+        <v>100</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2</v>
+      </c>
+      <c r="G8" s="8">
+        <v>80</v>
+      </c>
+      <c r="H8" s="8">
+        <v>20</v>
+      </c>
+      <c r="I8" s="11">
+        <v>50</v>
+      </c>
+      <c r="J8" s="12">
         <v>90</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:10">
-      <c r="A7" s="3">
-        <f t="shared" si="0"/>
-        <v>1003</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3">
-        <v>100</v>
-      </c>
-      <c r="F7" s="3">
+    <row r="9" customHeight="1" spans="1:10">
+      <c r="A9" s="8">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>5</v>
+      </c>
+      <c r="E9" s="8">
+        <v>100</v>
+      </c>
+      <c r="F9" s="8">
         <v>2</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G9" s="8">
+        <v>100</v>
+      </c>
+      <c r="H9" s="8">
+        <v>25</v>
+      </c>
+      <c r="I9" s="11">
         <v>60</v>
       </c>
-      <c r="H7" s="3">
+      <c r="J9" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:10">
+      <c r="A10" s="8">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>6</v>
+      </c>
+      <c r="E10" s="8">
+        <v>100</v>
+      </c>
+      <c r="F10" s="8">
+        <v>2</v>
+      </c>
+      <c r="G10" s="8">
+        <v>120</v>
+      </c>
+      <c r="H10" s="8">
+        <v>30</v>
+      </c>
+      <c r="I10" s="11">
+        <v>70</v>
+      </c>
+      <c r="J10" s="12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:10">
+      <c r="A11" s="8">
+        <f t="shared" si="0"/>
+        <v>1007</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
+        <v>7</v>
+      </c>
+      <c r="E11" s="8">
+        <v>100</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8">
+        <v>140</v>
+      </c>
+      <c r="H11" s="8">
+        <v>35</v>
+      </c>
+      <c r="I11" s="11">
+        <v>80</v>
+      </c>
+      <c r="J11" s="12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
+      <c r="A12" s="8">
+        <f t="shared" si="0"/>
+        <v>1008</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8">
+        <v>8</v>
+      </c>
+      <c r="E12" s="8">
+        <v>100</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2</v>
+      </c>
+      <c r="G12" s="8">
+        <v>160</v>
+      </c>
+      <c r="H12" s="8">
+        <v>40</v>
+      </c>
+      <c r="I12" s="11">
+        <v>90</v>
+      </c>
+      <c r="J12" s="12">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="A13" s="8">
+        <f t="shared" si="0"/>
+        <v>1009</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8">
+        <v>9</v>
+      </c>
+      <c r="E13" s="8">
+        <v>100</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2</v>
+      </c>
+      <c r="G13" s="8">
+        <v>180</v>
+      </c>
+      <c r="H13" s="8">
+        <v>45</v>
+      </c>
+      <c r="I13" s="11">
+        <v>100</v>
+      </c>
+      <c r="J13" s="12">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
+      <c r="A14" s="8">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8">
+        <v>10</v>
+      </c>
+      <c r="E14" s="8">
+        <v>100</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2</v>
+      </c>
+      <c r="G14" s="8">
+        <v>200</v>
+      </c>
+      <c r="H14" s="8">
+        <v>50</v>
+      </c>
+      <c r="I14" s="11">
+        <v>110</v>
+      </c>
+      <c r="J14" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A15" s="8">
+        <f t="shared" si="0"/>
+        <v>1011</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8">
+        <v>11</v>
+      </c>
+      <c r="E15" s="8">
+        <v>100</v>
+      </c>
+      <c r="F15" s="8">
+        <v>2</v>
+      </c>
+      <c r="G15" s="8">
+        <v>20</v>
+      </c>
+      <c r="H15" s="8">
+        <v>55</v>
+      </c>
+      <c r="I15" s="11">
+        <v>120</v>
+      </c>
+      <c r="J15" s="12">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A16" s="8">
+        <f t="shared" si="0"/>
+        <v>1012</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="8">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8">
+        <v>12</v>
+      </c>
+      <c r="E16" s="8">
+        <v>100</v>
+      </c>
+      <c r="F16" s="8">
+        <v>2</v>
+      </c>
+      <c r="G16" s="8">
+        <v>40</v>
+      </c>
+      <c r="H16" s="8">
+        <v>60</v>
+      </c>
+      <c r="I16" s="11">
+        <v>130</v>
+      </c>
+      <c r="J16" s="12">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A17" s="8">
+        <f t="shared" si="0"/>
+        <v>1013</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="8">
+        <v>1</v>
+      </c>
+      <c r="D17" s="8">
+        <v>13</v>
+      </c>
+      <c r="E17" s="8">
+        <v>100</v>
+      </c>
+      <c r="F17" s="8">
+        <v>2</v>
+      </c>
+      <c r="G17" s="8">
+        <v>60</v>
+      </c>
+      <c r="H17" s="8">
+        <v>65</v>
+      </c>
+      <c r="I17" s="11">
+        <v>140</v>
+      </c>
+      <c r="J17" s="12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A18" s="8">
+        <f t="shared" si="0"/>
+        <v>1014</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8">
+        <v>14</v>
+      </c>
+      <c r="E18" s="8">
+        <v>100</v>
+      </c>
+      <c r="F18" s="8">
+        <v>2</v>
+      </c>
+      <c r="G18" s="8">
+        <v>80</v>
+      </c>
+      <c r="H18" s="8">
+        <v>70</v>
+      </c>
+      <c r="I18" s="11">
+        <v>150</v>
+      </c>
+      <c r="J18" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A19" s="8">
+        <f t="shared" si="0"/>
+        <v>1015</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="8">
+        <v>1</v>
+      </c>
+      <c r="D19" s="8">
         <v>15</v>
       </c>
-      <c r="I7" s="6">
+      <c r="E19" s="8">
+        <v>100</v>
+      </c>
+      <c r="F19" s="8">
+        <v>2</v>
+      </c>
+      <c r="G19" s="8">
+        <v>100</v>
+      </c>
+      <c r="H19" s="8">
+        <v>75</v>
+      </c>
+      <c r="I19" s="11">
+        <v>160</v>
+      </c>
+      <c r="J19" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A20" s="8">
+        <f t="shared" si="0"/>
+        <v>1016</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="8">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8">
+        <v>16</v>
+      </c>
+      <c r="E20" s="8">
+        <v>100</v>
+      </c>
+      <c r="F20" s="8">
+        <v>2</v>
+      </c>
+      <c r="G20" s="8">
+        <v>120</v>
+      </c>
+      <c r="H20" s="8">
+        <v>80</v>
+      </c>
+      <c r="I20" s="11">
+        <v>170</v>
+      </c>
+      <c r="J20" s="12">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A21" s="8">
+        <f t="shared" si="0"/>
+        <v>1017</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="8">
+        <v>1</v>
+      </c>
+      <c r="D21" s="8">
+        <v>17</v>
+      </c>
+      <c r="E21" s="8">
+        <v>100</v>
+      </c>
+      <c r="F21" s="8">
+        <v>2</v>
+      </c>
+      <c r="G21" s="8">
+        <v>140</v>
+      </c>
+      <c r="H21" s="8">
+        <v>85</v>
+      </c>
+      <c r="I21" s="11">
+        <v>180</v>
+      </c>
+      <c r="J21" s="12">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A22" s="8">
+        <f t="shared" si="0"/>
+        <v>1018</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="8">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8">
+        <v>18</v>
+      </c>
+      <c r="E22" s="8">
+        <v>100</v>
+      </c>
+      <c r="F22" s="8">
+        <v>2</v>
+      </c>
+      <c r="G22" s="8">
+        <v>160</v>
+      </c>
+      <c r="H22" s="8">
+        <v>90</v>
+      </c>
+      <c r="I22" s="11">
+        <v>190</v>
+      </c>
+      <c r="J22" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A23" s="8">
+        <f t="shared" si="0"/>
+        <v>1019</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="8">
+        <v>1</v>
+      </c>
+      <c r="D23" s="8">
+        <v>19</v>
+      </c>
+      <c r="E23" s="8">
+        <v>100</v>
+      </c>
+      <c r="F23" s="8">
+        <v>2</v>
+      </c>
+      <c r="G23" s="8">
+        <v>180</v>
+      </c>
+      <c r="H23" s="8">
+        <v>95</v>
+      </c>
+      <c r="I23" s="11">
+        <v>200</v>
+      </c>
+      <c r="J23" s="12">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A24" s="8">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="8">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8">
+        <v>20</v>
+      </c>
+      <c r="E24" s="8">
+        <v>100</v>
+      </c>
+      <c r="F24" s="8">
+        <v>2</v>
+      </c>
+      <c r="G24" s="8">
+        <v>200</v>
+      </c>
+      <c r="H24" s="8">
+        <v>100</v>
+      </c>
+      <c r="I24" s="11">
+        <v>210</v>
+      </c>
+      <c r="J24" s="12">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A25" s="8">
+        <f t="shared" si="0"/>
+        <v>1021</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="8">
+        <v>1</v>
+      </c>
+      <c r="D25" s="8">
+        <v>21</v>
+      </c>
+      <c r="E25" s="8">
+        <v>100</v>
+      </c>
+      <c r="F25" s="8">
+        <v>3</v>
+      </c>
+      <c r="G25" s="8">
+        <v>20</v>
+      </c>
+      <c r="H25" s="8">
+        <v>105</v>
+      </c>
+      <c r="I25" s="11">
+        <v>220</v>
+      </c>
+      <c r="J25" s="12">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A26" s="8">
+        <f t="shared" si="0"/>
+        <v>1022</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="8">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8">
+        <v>22</v>
+      </c>
+      <c r="E26" s="8">
+        <v>100</v>
+      </c>
+      <c r="F26" s="8">
+        <v>3</v>
+      </c>
+      <c r="G26" s="8">
         <v>40</v>
       </c>
-      <c r="J7" s="5">
+      <c r="H26" s="8">
+        <v>110</v>
+      </c>
+      <c r="I26" s="11">
+        <v>230</v>
+      </c>
+      <c r="J26" s="12">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A27" s="8">
+        <f t="shared" si="0"/>
+        <v>1023</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="8">
+        <v>1</v>
+      </c>
+      <c r="D27" s="8">
+        <v>23</v>
+      </c>
+      <c r="E27" s="8">
+        <v>100</v>
+      </c>
+      <c r="F27" s="8">
+        <v>3</v>
+      </c>
+      <c r="G27" s="8">
+        <v>60</v>
+      </c>
+      <c r="H27" s="8">
+        <v>115</v>
+      </c>
+      <c r="I27" s="11">
+        <v>240</v>
+      </c>
+      <c r="J27" s="12">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A28" s="8">
+        <f t="shared" si="0"/>
+        <v>1024</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="8">
+        <v>1</v>
+      </c>
+      <c r="D28" s="8">
+        <v>24</v>
+      </c>
+      <c r="E28" s="8">
+        <v>100</v>
+      </c>
+      <c r="F28" s="8">
+        <v>3</v>
+      </c>
+      <c r="G28" s="8">
+        <v>80</v>
+      </c>
+      <c r="H28" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:10">
-      <c r="A8" s="3">
-        <f t="shared" si="0"/>
-        <v>1004</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="I28" s="11">
+        <v>250</v>
+      </c>
+      <c r="J28" s="12">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A29" s="8">
+        <f t="shared" si="0"/>
+        <v>1025</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="8">
+        <v>1</v>
+      </c>
+      <c r="D29" s="8">
+        <v>25</v>
+      </c>
+      <c r="E29" s="8">
+        <v>100</v>
+      </c>
+      <c r="F29" s="8">
+        <v>3</v>
+      </c>
+      <c r="G29" s="8">
+        <v>100</v>
+      </c>
+      <c r="H29" s="8">
+        <v>125</v>
+      </c>
+      <c r="I29" s="11">
+        <v>260</v>
+      </c>
+      <c r="J29" s="12">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A30" s="8">
+        <f t="shared" si="0"/>
+        <v>1026</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="8">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8">
+        <v>26</v>
+      </c>
+      <c r="E30" s="8">
+        <v>100</v>
+      </c>
+      <c r="F30" s="8">
+        <v>3</v>
+      </c>
+      <c r="G30" s="8">
+        <v>120</v>
+      </c>
+      <c r="H30" s="8">
+        <v>130</v>
+      </c>
+      <c r="I30" s="11">
+        <v>270</v>
+      </c>
+      <c r="J30" s="12">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A31" s="8">
+        <f t="shared" si="0"/>
+        <v>1027</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="8">
+        <v>1</v>
+      </c>
+      <c r="D31" s="8">
+        <v>27</v>
+      </c>
+      <c r="E31" s="8">
+        <v>100</v>
+      </c>
+      <c r="F31" s="8">
+        <v>3</v>
+      </c>
+      <c r="G31" s="8">
+        <v>140</v>
+      </c>
+      <c r="H31" s="8">
+        <v>135</v>
+      </c>
+      <c r="I31" s="11">
+        <v>280</v>
+      </c>
+      <c r="J31" s="12">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A32" s="8">
+        <f t="shared" si="0"/>
+        <v>1028</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="8">
+        <v>1</v>
+      </c>
+      <c r="D32" s="8">
+        <v>28</v>
+      </c>
+      <c r="E32" s="8">
+        <v>100</v>
+      </c>
+      <c r="F32" s="8">
+        <v>3</v>
+      </c>
+      <c r="G32" s="8">
+        <v>160</v>
+      </c>
+      <c r="H32" s="8">
+        <v>140</v>
+      </c>
+      <c r="I32" s="11">
+        <v>290</v>
+      </c>
+      <c r="J32" s="12">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A33" s="8">
+        <f t="shared" si="0"/>
+        <v>1029</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="8">
+        <v>1</v>
+      </c>
+      <c r="D33" s="8">
+        <v>29</v>
+      </c>
+      <c r="E33" s="8">
+        <v>100</v>
+      </c>
+      <c r="F33" s="8">
+        <v>3</v>
+      </c>
+      <c r="G33" s="8">
+        <v>180</v>
+      </c>
+      <c r="H33" s="8">
+        <v>145</v>
+      </c>
+      <c r="I33" s="11">
+        <v>300</v>
+      </c>
+      <c r="J33" s="12">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A34" s="8">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="8">
+        <v>1</v>
+      </c>
+      <c r="D34" s="8">
+        <v>30</v>
+      </c>
+      <c r="E34" s="8">
+        <v>100</v>
+      </c>
+      <c r="F34" s="8">
+        <v>3</v>
+      </c>
+      <c r="G34" s="8">
+        <v>200</v>
+      </c>
+      <c r="H34" s="8">
+        <v>150</v>
+      </c>
+      <c r="I34" s="11">
+        <v>310</v>
+      </c>
+      <c r="J34" s="12">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A35" s="8">
+        <f t="shared" si="0"/>
+        <v>1031</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+      <c r="D35" s="8">
+        <v>31</v>
+      </c>
+      <c r="E35" s="8">
+        <v>100</v>
+      </c>
+      <c r="F35" s="8">
+        <v>3</v>
+      </c>
+      <c r="G35" s="8">
+        <v>20</v>
+      </c>
+      <c r="H35" s="8">
+        <v>155</v>
+      </c>
+      <c r="I35" s="11">
+        <v>320</v>
+      </c>
+      <c r="J35" s="12">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A36" s="8">
+        <f t="shared" si="0"/>
+        <v>1032</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+      <c r="D36" s="8">
+        <v>32</v>
+      </c>
+      <c r="E36" s="8">
+        <v>100</v>
+      </c>
+      <c r="F36" s="8">
+        <v>3</v>
+      </c>
+      <c r="G36" s="8">
+        <v>40</v>
+      </c>
+      <c r="H36" s="8">
+        <v>160</v>
+      </c>
+      <c r="I36" s="11">
+        <v>330</v>
+      </c>
+      <c r="J36" s="12">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A37" s="8">
+        <f t="shared" si="0"/>
+        <v>1033</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+      <c r="D37" s="8">
+        <v>33</v>
+      </c>
+      <c r="E37" s="8">
+        <v>100</v>
+      </c>
+      <c r="F37" s="8">
+        <v>3</v>
+      </c>
+      <c r="G37" s="8">
+        <v>60</v>
+      </c>
+      <c r="H37" s="8">
+        <v>165</v>
+      </c>
+      <c r="I37" s="11">
+        <v>340</v>
+      </c>
+      <c r="J37" s="12">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A38" s="8">
+        <f t="shared" si="0"/>
+        <v>1034</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+      <c r="D38" s="8">
+        <v>34</v>
+      </c>
+      <c r="E38" s="8">
+        <v>100</v>
+      </c>
+      <c r="F38" s="8">
+        <v>3</v>
+      </c>
+      <c r="G38" s="8">
         <v>80</v>
       </c>
-      <c r="H8" s="3">
-        <v>20</v>
-      </c>
-      <c r="I8" s="6">
+      <c r="H38" s="8">
+        <v>170</v>
+      </c>
+      <c r="I38" s="11">
+        <v>350</v>
+      </c>
+      <c r="J38" s="12">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A39" s="8">
+        <f t="shared" si="0"/>
+        <v>1035</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+      <c r="D39" s="8">
+        <v>35</v>
+      </c>
+      <c r="E39" s="8">
+        <v>100</v>
+      </c>
+      <c r="F39" s="8">
+        <v>3</v>
+      </c>
+      <c r="G39" s="8">
+        <v>100</v>
+      </c>
+      <c r="H39" s="8">
+        <v>175</v>
+      </c>
+      <c r="I39" s="11">
+        <v>360</v>
+      </c>
+      <c r="J39" s="12">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A40" s="8">
+        <f t="shared" si="0"/>
+        <v>1036</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+      <c r="D40" s="8">
+        <v>36</v>
+      </c>
+      <c r="E40" s="8">
+        <v>100</v>
+      </c>
+      <c r="F40" s="8">
+        <v>3</v>
+      </c>
+      <c r="G40" s="8">
+        <v>120</v>
+      </c>
+      <c r="H40" s="8">
+        <v>180</v>
+      </c>
+      <c r="I40" s="11">
+        <v>370</v>
+      </c>
+      <c r="J40" s="12">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A41" s="8">
+        <f t="shared" si="0"/>
+        <v>1037</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+      <c r="D41" s="8">
+        <v>37</v>
+      </c>
+      <c r="E41" s="8">
+        <v>100</v>
+      </c>
+      <c r="F41" s="8">
+        <v>3</v>
+      </c>
+      <c r="G41" s="8">
+        <v>140</v>
+      </c>
+      <c r="H41" s="8">
+        <v>185</v>
+      </c>
+      <c r="I41" s="11">
+        <v>380</v>
+      </c>
+      <c r="J41" s="12">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A42" s="8">
+        <f t="shared" si="0"/>
+        <v>1038</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8">
+        <v>38</v>
+      </c>
+      <c r="E42" s="8">
+        <v>100</v>
+      </c>
+      <c r="F42" s="8">
+        <v>3</v>
+      </c>
+      <c r="G42" s="8">
+        <v>160</v>
+      </c>
+      <c r="H42" s="8">
+        <v>190</v>
+      </c>
+      <c r="I42" s="11">
+        <v>390</v>
+      </c>
+      <c r="J42" s="12">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A43" s="8">
+        <f t="shared" si="0"/>
+        <v>1039</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+      <c r="D43" s="8">
+        <v>39</v>
+      </c>
+      <c r="E43" s="8">
+        <v>100</v>
+      </c>
+      <c r="F43" s="8">
+        <v>3</v>
+      </c>
+      <c r="G43" s="8">
+        <v>180</v>
+      </c>
+      <c r="H43" s="8">
+        <v>195</v>
+      </c>
+      <c r="I43" s="11">
+        <v>400</v>
+      </c>
+      <c r="J43" s="12">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A44" s="8">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+      <c r="D44" s="8">
+        <v>40</v>
+      </c>
+      <c r="E44" s="8">
+        <v>100</v>
+      </c>
+      <c r="F44" s="8">
+        <v>3</v>
+      </c>
+      <c r="G44" s="8">
+        <v>200</v>
+      </c>
+      <c r="H44" s="8">
+        <v>200</v>
+      </c>
+      <c r="I44" s="11">
+        <v>410</v>
+      </c>
+      <c r="J44" s="12">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A45" s="8">
+        <f t="shared" si="0"/>
+        <v>1041</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+      <c r="D45" s="8">
+        <v>41</v>
+      </c>
+      <c r="E45" s="8">
+        <v>100</v>
+      </c>
+      <c r="F45" s="8">
+        <v>3</v>
+      </c>
+      <c r="G45" s="8">
+        <v>20</v>
+      </c>
+      <c r="H45" s="8">
+        <v>205</v>
+      </c>
+      <c r="I45" s="11">
+        <v>420</v>
+      </c>
+      <c r="J45" s="12">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A46" s="8">
+        <f t="shared" si="0"/>
+        <v>1042</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+      <c r="D46" s="8">
+        <v>42</v>
+      </c>
+      <c r="E46" s="8">
+        <v>100</v>
+      </c>
+      <c r="F46" s="8">
+        <v>3</v>
+      </c>
+      <c r="G46" s="8">
+        <v>40</v>
+      </c>
+      <c r="H46" s="8">
+        <v>210</v>
+      </c>
+      <c r="I46" s="11">
+        <v>430</v>
+      </c>
+      <c r="J46" s="12">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A47" s="8">
+        <f t="shared" si="0"/>
+        <v>1043</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+      <c r="D47" s="8">
+        <v>43</v>
+      </c>
+      <c r="E47" s="8">
+        <v>100</v>
+      </c>
+      <c r="F47" s="8">
+        <v>3</v>
+      </c>
+      <c r="G47" s="8">
+        <v>60</v>
+      </c>
+      <c r="H47" s="8">
+        <v>215</v>
+      </c>
+      <c r="I47" s="11">
+        <v>440</v>
+      </c>
+      <c r="J47" s="12">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A48" s="8">
+        <f t="shared" si="0"/>
+        <v>1044</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+      <c r="D48" s="8">
+        <v>44</v>
+      </c>
+      <c r="E48" s="8">
+        <v>100</v>
+      </c>
+      <c r="F48" s="8">
+        <v>3</v>
+      </c>
+      <c r="G48" s="8">
+        <v>80</v>
+      </c>
+      <c r="H48" s="8">
+        <v>220</v>
+      </c>
+      <c r="I48" s="11">
+        <v>450</v>
+      </c>
+      <c r="J48" s="12">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A49" s="8">
+        <f t="shared" si="0"/>
+        <v>1045</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+      <c r="D49" s="8">
+        <v>45</v>
+      </c>
+      <c r="E49" s="8">
+        <v>100</v>
+      </c>
+      <c r="F49" s="8">
+        <v>3</v>
+      </c>
+      <c r="G49" s="8">
+        <v>100</v>
+      </c>
+      <c r="H49" s="8">
+        <v>225</v>
+      </c>
+      <c r="I49" s="11">
+        <v>460</v>
+      </c>
+      <c r="J49" s="12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A50" s="8">
+        <f t="shared" si="0"/>
+        <v>1046</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+      <c r="D50" s="8">
+        <v>46</v>
+      </c>
+      <c r="E50" s="8">
+        <v>100</v>
+      </c>
+      <c r="F50" s="8">
+        <v>3</v>
+      </c>
+      <c r="G50" s="8">
+        <v>120</v>
+      </c>
+      <c r="H50" s="8">
+        <v>230</v>
+      </c>
+      <c r="I50" s="11">
+        <v>470</v>
+      </c>
+      <c r="J50" s="12">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A51" s="8">
+        <f t="shared" si="0"/>
+        <v>1047</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+      <c r="D51" s="8">
+        <v>47</v>
+      </c>
+      <c r="E51" s="8">
+        <v>100</v>
+      </c>
+      <c r="F51" s="8">
+        <v>3</v>
+      </c>
+      <c r="G51" s="8">
+        <v>140</v>
+      </c>
+      <c r="H51" s="8">
+        <v>235</v>
+      </c>
+      <c r="I51" s="11">
+        <v>480</v>
+      </c>
+      <c r="J51" s="12">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A52" s="8">
+        <f t="shared" si="0"/>
+        <v>1048</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1</v>
+      </c>
+      <c r="D52" s="8">
+        <v>48</v>
+      </c>
+      <c r="E52" s="8">
+        <v>100</v>
+      </c>
+      <c r="F52" s="8">
+        <v>3</v>
+      </c>
+      <c r="G52" s="8">
+        <v>160</v>
+      </c>
+      <c r="H52" s="8">
+        <v>240</v>
+      </c>
+      <c r="I52" s="11">
+        <v>490</v>
+      </c>
+      <c r="J52" s="12">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A53" s="8">
+        <f t="shared" si="0"/>
+        <v>1049</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1</v>
+      </c>
+      <c r="D53" s="8">
+        <v>49</v>
+      </c>
+      <c r="E53" s="8">
+        <v>100</v>
+      </c>
+      <c r="F53" s="8">
+        <v>3</v>
+      </c>
+      <c r="G53" s="8">
+        <v>180</v>
+      </c>
+      <c r="H53" s="8">
+        <v>245</v>
+      </c>
+      <c r="I53" s="11">
+        <v>500</v>
+      </c>
+      <c r="J53" s="12">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A54" s="8">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="8">
+        <v>1</v>
+      </c>
+      <c r="D54" s="8">
         <v>50</v>
       </c>
-      <c r="J8" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:10">
-      <c r="A9" s="3">
-        <f t="shared" si="0"/>
-        <v>1005</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3">
-        <v>100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>25</v>
-      </c>
-      <c r="I9" s="6">
+      <c r="E54" s="8">
+        <v>100</v>
+      </c>
+      <c r="F54" s="8">
+        <v>3</v>
+      </c>
+      <c r="G54" s="8">
+        <v>200</v>
+      </c>
+      <c r="H54" s="8">
+        <v>250</v>
+      </c>
+      <c r="I54" s="11">
+        <v>510</v>
+      </c>
+      <c r="J54" s="12">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A55" s="8">
+        <f t="shared" si="0"/>
+        <v>1051</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="8">
+        <v>1</v>
+      </c>
+      <c r="D55" s="8">
+        <v>51</v>
+      </c>
+      <c r="E55" s="8">
+        <v>100</v>
+      </c>
+      <c r="F55" s="8">
+        <v>3</v>
+      </c>
+      <c r="G55" s="8">
+        <v>20</v>
+      </c>
+      <c r="H55" s="8">
+        <v>255</v>
+      </c>
+      <c r="I55" s="11">
+        <v>520</v>
+      </c>
+      <c r="J55" s="12">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A56" s="8">
+        <f t="shared" si="0"/>
+        <v>1052</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="8">
+        <v>1</v>
+      </c>
+      <c r="D56" s="8">
+        <v>52</v>
+      </c>
+      <c r="E56" s="8">
+        <v>100</v>
+      </c>
+      <c r="F56" s="8">
+        <v>3</v>
+      </c>
+      <c r="G56" s="8">
+        <v>40</v>
+      </c>
+      <c r="H56" s="8">
+        <v>260</v>
+      </c>
+      <c r="I56" s="11">
+        <v>530</v>
+      </c>
+      <c r="J56" s="12">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A57" s="8">
+        <f t="shared" si="0"/>
+        <v>1053</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="8">
+        <v>1</v>
+      </c>
+      <c r="D57" s="8">
+        <v>53</v>
+      </c>
+      <c r="E57" s="8">
+        <v>100</v>
+      </c>
+      <c r="F57" s="8">
+        <v>3</v>
+      </c>
+      <c r="G57" s="8">
         <v>60</v>
       </c>
-      <c r="J9" s="5">
+      <c r="H57" s="8">
+        <v>265</v>
+      </c>
+      <c r="I57" s="11">
+        <v>540</v>
+      </c>
+      <c r="J57" s="12">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A58" s="8">
+        <f t="shared" si="0"/>
+        <v>1054</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="8">
+        <v>1</v>
+      </c>
+      <c r="D58" s="8">
+        <v>54</v>
+      </c>
+      <c r="E58" s="8">
+        <v>100</v>
+      </c>
+      <c r="F58" s="8">
+        <v>3</v>
+      </c>
+      <c r="G58" s="8">
+        <v>80</v>
+      </c>
+      <c r="H58" s="8">
+        <v>270</v>
+      </c>
+      <c r="I58" s="11">
+        <v>550</v>
+      </c>
+      <c r="J58" s="12">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A59" s="8">
+        <f t="shared" si="0"/>
+        <v>1055</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="8">
+        <v>1</v>
+      </c>
+      <c r="D59" s="8">
+        <v>55</v>
+      </c>
+      <c r="E59" s="8">
+        <v>100</v>
+      </c>
+      <c r="F59" s="8">
+        <v>3</v>
+      </c>
+      <c r="G59" s="8">
+        <v>100</v>
+      </c>
+      <c r="H59" s="8">
+        <v>275</v>
+      </c>
+      <c r="I59" s="11">
+        <v>560</v>
+      </c>
+      <c r="J59" s="12">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A60" s="8">
+        <f t="shared" si="0"/>
+        <v>1056</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="8">
+        <v>1</v>
+      </c>
+      <c r="D60" s="8">
+        <v>56</v>
+      </c>
+      <c r="E60" s="8">
+        <v>100</v>
+      </c>
+      <c r="F60" s="8">
+        <v>3</v>
+      </c>
+      <c r="G60" s="8">
+        <v>120</v>
+      </c>
+      <c r="H60" s="8">
+        <v>280</v>
+      </c>
+      <c r="I60" s="11">
+        <v>570</v>
+      </c>
+      <c r="J60" s="12">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A61" s="8">
+        <f t="shared" si="0"/>
+        <v>1057</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="8">
+        <v>1</v>
+      </c>
+      <c r="D61" s="8">
+        <v>57</v>
+      </c>
+      <c r="E61" s="8">
+        <v>100</v>
+      </c>
+      <c r="F61" s="8">
+        <v>3</v>
+      </c>
+      <c r="G61" s="8">
+        <v>140</v>
+      </c>
+      <c r="H61" s="8">
+        <v>285</v>
+      </c>
+      <c r="I61" s="11">
+        <v>580</v>
+      </c>
+      <c r="J61" s="12">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A62" s="8">
+        <f t="shared" si="0"/>
+        <v>1058</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="8">
+        <v>1</v>
+      </c>
+      <c r="D62" s="8">
+        <v>58</v>
+      </c>
+      <c r="E62" s="8">
+        <v>100</v>
+      </c>
+      <c r="F62" s="8">
+        <v>3</v>
+      </c>
+      <c r="G62" s="8">
+        <v>160</v>
+      </c>
+      <c r="H62" s="8">
+        <v>290</v>
+      </c>
+      <c r="I62" s="11">
+        <v>590</v>
+      </c>
+      <c r="J62" s="12">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A63" s="8">
+        <f t="shared" si="0"/>
+        <v>1059</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="8">
+        <v>1</v>
+      </c>
+      <c r="D63" s="8">
+        <v>59</v>
+      </c>
+      <c r="E63" s="8">
+        <v>100</v>
+      </c>
+      <c r="F63" s="8">
+        <v>3</v>
+      </c>
+      <c r="G63" s="8">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:10">
-      <c r="A10" s="3">
-        <f t="shared" si="0"/>
-        <v>1006</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3">
-        <v>6</v>
-      </c>
-      <c r="E10" s="3">
-        <v>100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3">
-        <v>120</v>
-      </c>
-      <c r="H10" s="3">
-        <v>30</v>
-      </c>
-      <c r="I10" s="6">
-        <v>70</v>
-      </c>
-      <c r="J10" s="5">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:10">
-      <c r="A11" s="3">
-        <f t="shared" si="0"/>
-        <v>1007</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3">
-        <v>100</v>
-      </c>
-      <c r="F11" s="3">
-        <v>3</v>
-      </c>
-      <c r="G11" s="3">
-        <v>140</v>
-      </c>
-      <c r="H11" s="3">
-        <v>35</v>
-      </c>
-      <c r="I11" s="6">
-        <v>80</v>
-      </c>
-      <c r="J11" s="5">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:10">
-      <c r="A12" s="3">
-        <f t="shared" si="0"/>
-        <v>1008</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3">
-        <v>100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3">
-        <v>160</v>
-      </c>
-      <c r="H12" s="3">
-        <v>40</v>
-      </c>
-      <c r="I12" s="6">
-        <v>90</v>
-      </c>
-      <c r="J12" s="5">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:10">
-      <c r="A13" s="3">
-        <f t="shared" si="0"/>
-        <v>1009</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>9</v>
-      </c>
-      <c r="E13" s="3">
-        <v>100</v>
-      </c>
-      <c r="F13" s="3">
-        <v>3</v>
-      </c>
-      <c r="G13" s="3">
-        <v>180</v>
-      </c>
-      <c r="H13" s="3">
-        <v>45</v>
-      </c>
-      <c r="I13" s="6">
-        <v>100</v>
-      </c>
-      <c r="J13" s="5">
+      <c r="H63" s="8">
+        <v>295</v>
+      </c>
+      <c r="I63" s="11">
+        <v>600</v>
+      </c>
+      <c r="J63" s="12">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A64" s="8">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="8">
+        <v>1</v>
+      </c>
+      <c r="D64" s="8">
+        <v>60</v>
+      </c>
+      <c r="E64" s="8">
+        <v>100</v>
+      </c>
+      <c r="F64" s="8">
+        <v>3</v>
+      </c>
+      <c r="G64" s="8">
+        <v>200</v>
+      </c>
+      <c r="H64" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:10">
-      <c r="A14" s="3">
-        <f t="shared" si="0"/>
-        <v>1010</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3">
-        <v>100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>200</v>
-      </c>
-      <c r="H14" s="3">
-        <v>999999</v>
-      </c>
-      <c r="I14" s="6">
-        <v>110</v>
-      </c>
-      <c r="J14" s="5">
-        <v>360</v>
+      <c r="I64" s="11">
+        <v>610</v>
+      </c>
+      <c r="J64" s="12">
+        <v>650</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -439,12 +439,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1461,7 +1461,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="8">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L5" s="11">
         <v>20</v>
@@ -1503,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="8">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="L6" s="11">
         <v>30</v>
@@ -1545,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="8">
-        <v>15</v>
+        <v>264</v>
       </c>
       <c r="L7" s="11">
         <v>40</v>
@@ -1587,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="8">
-        <v>20</v>
+        <v>468</v>
       </c>
       <c r="L8" s="11">
         <v>50</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="8">
-        <v>25</v>
+        <v>730</v>
       </c>
       <c r="L9" s="11">
         <v>60</v>
@@ -1671,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="8">
-        <v>30</v>
+        <v>1050</v>
       </c>
       <c r="L10" s="11">
         <v>70</v>
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="8">
-        <v>35</v>
+        <v>1428</v>
       </c>
       <c r="L11" s="11">
         <v>80</v>
@@ -1755,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="8">
-        <v>40</v>
+        <v>1864</v>
       </c>
       <c r="L12" s="11">
         <v>90</v>
@@ -1797,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="8">
-        <v>45</v>
+        <v>2358</v>
       </c>
       <c r="L13" s="11">
         <v>100</v>
@@ -1839,7 +1839,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="8">
-        <v>50</v>
+        <v>2910</v>
       </c>
       <c r="L14" s="11">
         <v>110</v>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="8">
-        <v>55</v>
+        <v>3520</v>
       </c>
       <c r="L15" s="11">
         <v>120</v>
@@ -1923,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="8">
-        <v>60</v>
+        <v>4188</v>
       </c>
       <c r="L16" s="11">
         <v>130</v>
@@ -1965,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="8">
-        <v>65</v>
+        <v>4914</v>
       </c>
       <c r="L17" s="11">
         <v>140</v>
@@ -2007,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="8">
-        <v>70</v>
+        <v>5698</v>
       </c>
       <c r="L18" s="11">
         <v>150</v>
@@ -2049,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="8">
-        <v>75</v>
+        <v>6540</v>
       </c>
       <c r="L19" s="11">
         <v>160</v>
@@ -2091,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="8">
-        <v>80</v>
+        <v>7440</v>
       </c>
       <c r="L20" s="11">
         <v>170</v>
@@ -2133,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="8">
-        <v>85</v>
+        <v>8398</v>
       </c>
       <c r="L21" s="11">
         <v>180</v>
@@ -2175,7 +2175,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="8">
-        <v>90</v>
+        <v>9414</v>
       </c>
       <c r="L22" s="11">
         <v>190</v>
@@ -2217,7 +2217,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="8">
-        <v>95</v>
+        <v>10488</v>
       </c>
       <c r="L23" s="11">
         <v>200</v>
@@ -2259,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="8">
-        <v>100</v>
+        <v>11620</v>
       </c>
       <c r="L24" s="11">
         <v>210</v>
@@ -2301,7 +2301,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="8">
-        <v>105</v>
+        <v>12810</v>
       </c>
       <c r="L25" s="11">
         <v>220</v>
@@ -2343,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="8">
-        <v>110</v>
+        <v>14058</v>
       </c>
       <c r="L26" s="11">
         <v>230</v>
@@ -2385,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="8">
-        <v>115</v>
+        <v>15364</v>
       </c>
       <c r="L27" s="11">
         <v>240</v>
@@ -2427,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="8">
-        <v>120</v>
+        <v>16728</v>
       </c>
       <c r="L28" s="11">
         <v>250</v>
@@ -2469,7 +2469,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="8">
-        <v>125</v>
+        <v>18150</v>
       </c>
       <c r="L29" s="11">
         <v>260</v>
@@ -2511,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="8">
-        <v>130</v>
+        <v>19630</v>
       </c>
       <c r="L30" s="11">
         <v>270</v>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="8">
-        <v>135</v>
+        <v>21168</v>
       </c>
       <c r="L31" s="11">
         <v>280</v>
@@ -2595,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="8">
-        <v>140</v>
+        <v>22764</v>
       </c>
       <c r="L32" s="11">
         <v>290</v>
@@ -2637,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="8">
-        <v>145</v>
+        <v>24418</v>
       </c>
       <c r="L33" s="11">
         <v>300</v>
@@ -2679,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="8">
-        <v>150</v>
+        <v>26130</v>
       </c>
       <c r="L34" s="11">
         <v>310</v>
@@ -2721,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="8">
-        <v>155</v>
+        <v>27900</v>
       </c>
       <c r="L35" s="11">
         <v>320</v>
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="8">
-        <v>160</v>
+        <v>29728</v>
       </c>
       <c r="L36" s="11">
         <v>330</v>
@@ -2805,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="8">
-        <v>165</v>
+        <v>31614</v>
       </c>
       <c r="L37" s="11">
         <v>340</v>
@@ -2847,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="8">
-        <v>170</v>
+        <v>33558</v>
       </c>
       <c r="L38" s="11">
         <v>350</v>
@@ -2889,7 +2889,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="8">
-        <v>175</v>
+        <v>35560</v>
       </c>
       <c r="L39" s="11">
         <v>360</v>
@@ -2931,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="8">
-        <v>180</v>
+        <v>37620</v>
       </c>
       <c r="L40" s="11">
         <v>370</v>
@@ -2973,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="8">
-        <v>185</v>
+        <v>39738</v>
       </c>
       <c r="L41" s="11">
         <v>380</v>
@@ -3015,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="8">
-        <v>190</v>
+        <v>41914</v>
       </c>
       <c r="L42" s="11">
         <v>390</v>
@@ -3057,7 +3057,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="8">
-        <v>195</v>
+        <v>44148</v>
       </c>
       <c r="L43" s="11">
         <v>400</v>
@@ -3099,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="8">
-        <v>200</v>
+        <v>46440</v>
       </c>
       <c r="L44" s="11">
         <v>410</v>
@@ -3141,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="8">
-        <v>205</v>
+        <v>48790</v>
       </c>
       <c r="L45" s="11">
         <v>420</v>
@@ -3183,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="8">
-        <v>210</v>
+        <v>51198</v>
       </c>
       <c r="L46" s="11">
         <v>430</v>
@@ -3225,7 +3225,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="8">
-        <v>215</v>
+        <v>53664</v>
       </c>
       <c r="L47" s="11">
         <v>440</v>
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="8">
-        <v>220</v>
+        <v>56188</v>
       </c>
       <c r="L48" s="11">
         <v>450</v>
@@ -3309,7 +3309,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="8">
-        <v>225</v>
+        <v>58770</v>
       </c>
       <c r="L49" s="11">
         <v>460</v>
@@ -3351,7 +3351,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="8">
-        <v>230</v>
+        <v>61410</v>
       </c>
       <c r="L50" s="11">
         <v>470</v>
@@ -3393,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="8">
-        <v>235</v>
+        <v>64108</v>
       </c>
       <c r="L51" s="11">
         <v>480</v>
@@ -3435,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="8">
-        <v>240</v>
+        <v>66864</v>
       </c>
       <c r="L52" s="11">
         <v>490</v>
@@ -3477,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="8">
-        <v>245</v>
+        <v>69678</v>
       </c>
       <c r="L53" s="11">
         <v>500</v>
@@ -3519,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="K54" s="8">
-        <v>250</v>
+        <v>72550</v>
       </c>
       <c r="L54" s="11">
         <v>510</v>
@@ -3561,7 +3561,7 @@
         <v>1</v>
       </c>
       <c r="K55" s="8">
-        <v>255</v>
+        <v>75480</v>
       </c>
       <c r="L55" s="11">
         <v>520</v>
@@ -3603,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="8">
-        <v>260</v>
+        <v>78468</v>
       </c>
       <c r="L56" s="11">
         <v>530</v>
@@ -3645,7 +3645,7 @@
         <v>1</v>
       </c>
       <c r="K57" s="8">
-        <v>265</v>
+        <v>81514</v>
       </c>
       <c r="L57" s="11">
         <v>540</v>
@@ -3687,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="8">
-        <v>270</v>
+        <v>84618</v>
       </c>
       <c r="L58" s="11">
         <v>550</v>
@@ -3729,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="8">
-        <v>275</v>
+        <v>87780</v>
       </c>
       <c r="L59" s="11">
         <v>560</v>
@@ -3771,7 +3771,7 @@
         <v>1</v>
       </c>
       <c r="K60" s="8">
-        <v>280</v>
+        <v>91000</v>
       </c>
       <c r="L60" s="11">
         <v>570</v>
@@ -3813,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="K61" s="8">
-        <v>285</v>
+        <v>94278</v>
       </c>
       <c r="L61" s="11">
         <v>580</v>
@@ -3855,7 +3855,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="8">
-        <v>290</v>
+        <v>97614</v>
       </c>
       <c r="L62" s="11">
         <v>590</v>
@@ -3897,7 +3897,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="8">
-        <v>295</v>
+        <v>101008</v>
       </c>
       <c r="L63" s="11">
         <v>600</v>
@@ -3939,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="8">
-        <v>300</v>
+        <v>104460</v>
       </c>
       <c r="L64" s="11">
         <v>610</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -1455,7 +1455,7 @@
         <v>5</v>
       </c>
       <c r="I5" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J5" s="8">
         <v>1</v>
@@ -1497,7 +1497,7 @@
         <v>5</v>
       </c>
       <c r="I6" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J6" s="8">
         <v>1</v>
@@ -1539,7 +1539,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J7" s="8">
         <v>1</v>
@@ -1581,7 +1581,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J8" s="8">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J9" s="8">
         <v>1</v>
@@ -1665,7 +1665,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J10" s="8">
         <v>1</v>
@@ -1707,7 +1707,7 @@
         <v>5</v>
       </c>
       <c r="I11" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J11" s="8">
         <v>1</v>
@@ -1749,7 +1749,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J12" s="8">
         <v>1</v>
@@ -1791,7 +1791,7 @@
         <v>5</v>
       </c>
       <c r="I13" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J13" s="8">
         <v>1</v>
@@ -1833,7 +1833,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J14" s="8">
         <v>1</v>
@@ -1875,7 +1875,7 @@
         <v>5</v>
       </c>
       <c r="I15" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J15" s="8">
         <v>1</v>
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="I16" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J16" s="8">
         <v>1</v>
@@ -1959,7 +1959,7 @@
         <v>5</v>
       </c>
       <c r="I17" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J17" s="8">
         <v>1</v>
@@ -2001,7 +2001,7 @@
         <v>5</v>
       </c>
       <c r="I18" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J18" s="8">
         <v>1</v>
@@ -2043,7 +2043,7 @@
         <v>5</v>
       </c>
       <c r="I19" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J19" s="8">
         <v>1</v>
@@ -2085,7 +2085,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J20" s="8">
         <v>1</v>
@@ -2127,7 +2127,7 @@
         <v>5</v>
       </c>
       <c r="I21" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J21" s="8">
         <v>1</v>
@@ -2169,7 +2169,7 @@
         <v>5</v>
       </c>
       <c r="I22" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J22" s="8">
         <v>1</v>
@@ -2211,7 +2211,7 @@
         <v>5</v>
       </c>
       <c r="I23" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J23" s="8">
         <v>1</v>
@@ -2253,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="I24" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J24" s="8">
         <v>1</v>
@@ -2295,7 +2295,7 @@
         <v>5</v>
       </c>
       <c r="I25" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J25" s="8">
         <v>1</v>
@@ -2337,7 +2337,7 @@
         <v>5</v>
       </c>
       <c r="I26" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J26" s="8">
         <v>1</v>
@@ -2379,7 +2379,7 @@
         <v>5</v>
       </c>
       <c r="I27" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J27" s="8">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         <v>5</v>
       </c>
       <c r="I28" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J28" s="8">
         <v>1</v>
@@ -2463,7 +2463,7 @@
         <v>5</v>
       </c>
       <c r="I29" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J29" s="8">
         <v>1</v>
@@ -2505,7 +2505,7 @@
         <v>5</v>
       </c>
       <c r="I30" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J30" s="8">
         <v>1</v>
@@ -2547,7 +2547,7 @@
         <v>5</v>
       </c>
       <c r="I31" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J31" s="8">
         <v>1</v>
@@ -2589,7 +2589,7 @@
         <v>5</v>
       </c>
       <c r="I32" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J32" s="8">
         <v>1</v>
@@ -2631,7 +2631,7 @@
         <v>5</v>
       </c>
       <c r="I33" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J33" s="8">
         <v>1</v>
@@ -2673,7 +2673,7 @@
         <v>5</v>
       </c>
       <c r="I34" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J34" s="8">
         <v>1</v>
@@ -2715,7 +2715,7 @@
         <v>5</v>
       </c>
       <c r="I35" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J35" s="8">
         <v>1</v>
@@ -2757,7 +2757,7 @@
         <v>5</v>
       </c>
       <c r="I36" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J36" s="8">
         <v>1</v>
@@ -2799,7 +2799,7 @@
         <v>5</v>
       </c>
       <c r="I37" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J37" s="8">
         <v>1</v>
@@ -2841,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="I38" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J38" s="8">
         <v>1</v>
@@ -2883,7 +2883,7 @@
         <v>5</v>
       </c>
       <c r="I39" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J39" s="8">
         <v>1</v>
@@ -2925,7 +2925,7 @@
         <v>5</v>
       </c>
       <c r="I40" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J40" s="8">
         <v>1</v>
@@ -2967,7 +2967,7 @@
         <v>5</v>
       </c>
       <c r="I41" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J41" s="8">
         <v>1</v>
@@ -3009,7 +3009,7 @@
         <v>5</v>
       </c>
       <c r="I42" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J42" s="8">
         <v>1</v>
@@ -3051,7 +3051,7 @@
         <v>5</v>
       </c>
       <c r="I43" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J43" s="8">
         <v>1</v>
@@ -3093,7 +3093,7 @@
         <v>5</v>
       </c>
       <c r="I44" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J44" s="8">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>5</v>
       </c>
       <c r="I45" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J45" s="8">
         <v>1</v>
@@ -3177,7 +3177,7 @@
         <v>5</v>
       </c>
       <c r="I46" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J46" s="8">
         <v>1</v>
@@ -3219,7 +3219,7 @@
         <v>5</v>
       </c>
       <c r="I47" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J47" s="8">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         <v>5</v>
       </c>
       <c r="I48" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J48" s="8">
         <v>1</v>
@@ -3303,7 +3303,7 @@
         <v>5</v>
       </c>
       <c r="I49" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J49" s="8">
         <v>1</v>
@@ -3345,7 +3345,7 @@
         <v>5</v>
       </c>
       <c r="I50" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J50" s="8">
         <v>1</v>
@@ -3387,7 +3387,7 @@
         <v>5</v>
       </c>
       <c r="I51" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J51" s="8">
         <v>1</v>
@@ -3429,7 +3429,7 @@
         <v>5</v>
       </c>
       <c r="I52" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J52" s="8">
         <v>1</v>
@@ -3471,7 +3471,7 @@
         <v>5</v>
       </c>
       <c r="I53" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J53" s="8">
         <v>1</v>
@@ -3513,7 +3513,7 @@
         <v>5</v>
       </c>
       <c r="I54" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J54" s="8">
         <v>1</v>
@@ -3555,7 +3555,7 @@
         <v>5</v>
       </c>
       <c r="I55" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J55" s="8">
         <v>1</v>
@@ -3597,7 +3597,7 @@
         <v>5</v>
       </c>
       <c r="I56" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J56" s="8">
         <v>1</v>
@@ -3639,7 +3639,7 @@
         <v>5</v>
       </c>
       <c r="I57" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J57" s="8">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>5</v>
       </c>
       <c r="I58" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J58" s="8">
         <v>1</v>
@@ -3723,7 +3723,7 @@
         <v>5</v>
       </c>
       <c r="I59" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J59" s="8">
         <v>1</v>
@@ -3765,7 +3765,7 @@
         <v>5</v>
       </c>
       <c r="I60" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J60" s="8">
         <v>1</v>
@@ -3807,7 +3807,7 @@
         <v>5</v>
       </c>
       <c r="I61" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J61" s="8">
         <v>1</v>
@@ -3849,7 +3849,7 @@
         <v>5</v>
       </c>
       <c r="I62" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J62" s="8">
         <v>1</v>
@@ -3891,7 +3891,7 @@
         <v>5</v>
       </c>
       <c r="I63" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J63" s="8">
         <v>1</v>
@@ -3933,7 +3933,7 @@
         <v>5</v>
       </c>
       <c r="I64" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J64" s="8">
         <v>1</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -1461,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="K5" s="8">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L5" s="11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M5" s="12">
         <v>60</v>
@@ -1503,10 +1503,10 @@
         <v>1</v>
       </c>
       <c r="K6" s="8">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="L6" s="11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M6" s="12">
         <v>70</v>
@@ -1545,10 +1545,10 @@
         <v>1</v>
       </c>
       <c r="K7" s="8">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="L7" s="11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M7" s="12">
         <v>80</v>
@@ -1590,7 +1590,7 @@
         <v>468</v>
       </c>
       <c r="L8" s="11">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M8" s="12">
         <v>90</v>
@@ -1632,7 +1632,7 @@
         <v>730</v>
       </c>
       <c r="L9" s="11">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M9" s="12">
         <v>100</v>
@@ -1674,7 +1674,7 @@
         <v>1050</v>
       </c>
       <c r="L10" s="11">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M10" s="12">
         <v>110</v>
@@ -1716,7 +1716,7 @@
         <v>1428</v>
       </c>
       <c r="L11" s="11">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M11" s="12">
         <v>120</v>
@@ -1758,7 +1758,7 @@
         <v>1864</v>
       </c>
       <c r="L12" s="11">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M12" s="12">
         <v>130</v>
@@ -1800,7 +1800,7 @@
         <v>2358</v>
       </c>
       <c r="L13" s="11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M13" s="12">
         <v>140</v>
@@ -1842,7 +1842,7 @@
         <v>2910</v>
       </c>
       <c r="L14" s="11">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="M14" s="12">
         <v>150</v>
@@ -1884,7 +1884,7 @@
         <v>3520</v>
       </c>
       <c r="L15" s="11">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M15" s="12">
         <v>160</v>
@@ -1926,7 +1926,7 @@
         <v>4188</v>
       </c>
       <c r="L16" s="11">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M16" s="12">
         <v>170</v>
@@ -1968,7 +1968,7 @@
         <v>4914</v>
       </c>
       <c r="L17" s="11">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M17" s="12">
         <v>180</v>
@@ -2010,7 +2010,7 @@
         <v>5698</v>
       </c>
       <c r="L18" s="11">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M18" s="12">
         <v>190</v>
@@ -2052,7 +2052,7 @@
         <v>6540</v>
       </c>
       <c r="L19" s="11">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M19" s="12">
         <v>200</v>
@@ -2094,7 +2094,7 @@
         <v>7440</v>
       </c>
       <c r="L20" s="11">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="M20" s="12">
         <v>210</v>
@@ -2136,7 +2136,7 @@
         <v>8398</v>
       </c>
       <c r="L21" s="11">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M21" s="12">
         <v>220</v>
@@ -2178,7 +2178,7 @@
         <v>9414</v>
       </c>
       <c r="L22" s="11">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="M22" s="12">
         <v>230</v>
@@ -2220,7 +2220,7 @@
         <v>10488</v>
       </c>
       <c r="L23" s="11">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M23" s="12">
         <v>240</v>
@@ -2262,7 +2262,7 @@
         <v>11620</v>
       </c>
       <c r="L24" s="11">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M24" s="12">
         <v>250</v>
@@ -2304,7 +2304,7 @@
         <v>12810</v>
       </c>
       <c r="L25" s="11">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="M25" s="12">
         <v>260</v>
@@ -2346,7 +2346,7 @@
         <v>14058</v>
       </c>
       <c r="L26" s="11">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="M26" s="12">
         <v>270</v>
@@ -2388,7 +2388,7 @@
         <v>15364</v>
       </c>
       <c r="L27" s="11">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="M27" s="12">
         <v>280</v>
@@ -2430,7 +2430,7 @@
         <v>16728</v>
       </c>
       <c r="L28" s="11">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="M28" s="12">
         <v>290</v>
@@ -2472,7 +2472,7 @@
         <v>18150</v>
       </c>
       <c r="L29" s="11">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="M29" s="12">
         <v>300</v>
@@ -2514,7 +2514,7 @@
         <v>19630</v>
       </c>
       <c r="L30" s="11">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M30" s="12">
         <v>310</v>
@@ -2556,7 +2556,7 @@
         <v>21168</v>
       </c>
       <c r="L31" s="11">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="M31" s="12">
         <v>320</v>
@@ -2598,7 +2598,7 @@
         <v>22764</v>
       </c>
       <c r="L32" s="11">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="M32" s="12">
         <v>330</v>
@@ -2640,7 +2640,7 @@
         <v>24418</v>
       </c>
       <c r="L33" s="11">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M33" s="12">
         <v>340</v>
@@ -2682,7 +2682,7 @@
         <v>26130</v>
       </c>
       <c r="L34" s="11">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="M34" s="12">
         <v>350</v>
@@ -2724,7 +2724,7 @@
         <v>27900</v>
       </c>
       <c r="L35" s="11">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="M35" s="12">
         <v>360</v>
@@ -2766,7 +2766,7 @@
         <v>29728</v>
       </c>
       <c r="L36" s="11">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="M36" s="12">
         <v>370</v>
@@ -2808,7 +2808,7 @@
         <v>31614</v>
       </c>
       <c r="L37" s="11">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="M37" s="12">
         <v>380</v>
@@ -2850,7 +2850,7 @@
         <v>33558</v>
       </c>
       <c r="L38" s="11">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="M38" s="12">
         <v>390</v>
@@ -2892,7 +2892,7 @@
         <v>35560</v>
       </c>
       <c r="L39" s="11">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="M39" s="12">
         <v>400</v>
@@ -2934,7 +2934,7 @@
         <v>37620</v>
       </c>
       <c r="L40" s="11">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="M40" s="12">
         <v>410</v>
@@ -2976,7 +2976,7 @@
         <v>39738</v>
       </c>
       <c r="L41" s="11">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="M41" s="12">
         <v>420</v>
@@ -3018,7 +3018,7 @@
         <v>41914</v>
       </c>
       <c r="L42" s="11">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="M42" s="12">
         <v>430</v>
@@ -3060,7 +3060,7 @@
         <v>44148</v>
       </c>
       <c r="L43" s="11">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M43" s="12">
         <v>440</v>
@@ -3102,7 +3102,7 @@
         <v>46440</v>
       </c>
       <c r="L44" s="11">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="M44" s="12">
         <v>450</v>
@@ -3144,7 +3144,7 @@
         <v>48790</v>
       </c>
       <c r="L45" s="11">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="M45" s="12">
         <v>460</v>
@@ -3186,7 +3186,7 @@
         <v>51198</v>
       </c>
       <c r="L46" s="11">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="M46" s="12">
         <v>470</v>
@@ -3228,7 +3228,7 @@
         <v>53664</v>
       </c>
       <c r="L47" s="11">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="M47" s="12">
         <v>480</v>
@@ -3270,7 +3270,7 @@
         <v>56188</v>
       </c>
       <c r="L48" s="11">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="M48" s="12">
         <v>490</v>
@@ -3312,7 +3312,7 @@
         <v>58770</v>
       </c>
       <c r="L49" s="11">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="M49" s="12">
         <v>500</v>
@@ -3354,7 +3354,7 @@
         <v>61410</v>
       </c>
       <c r="L50" s="11">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="M50" s="12">
         <v>510</v>
@@ -3396,7 +3396,7 @@
         <v>64108</v>
       </c>
       <c r="L51" s="11">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="M51" s="12">
         <v>520</v>
@@ -3438,7 +3438,7 @@
         <v>66864</v>
       </c>
       <c r="L52" s="11">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="M52" s="12">
         <v>530</v>
@@ -3480,7 +3480,7 @@
         <v>69678</v>
       </c>
       <c r="L53" s="11">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M53" s="12">
         <v>540</v>
@@ -3522,7 +3522,7 @@
         <v>72550</v>
       </c>
       <c r="L54" s="11">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="M54" s="12">
         <v>550</v>
@@ -3564,7 +3564,7 @@
         <v>75480</v>
       </c>
       <c r="L55" s="11">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="M55" s="12">
         <v>560</v>
@@ -3606,7 +3606,7 @@
         <v>78468</v>
       </c>
       <c r="L56" s="11">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="M56" s="12">
         <v>570</v>
@@ -3648,7 +3648,7 @@
         <v>81514</v>
       </c>
       <c r="L57" s="11">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="M57" s="12">
         <v>580</v>
@@ -3690,7 +3690,7 @@
         <v>84618</v>
       </c>
       <c r="L58" s="11">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="M58" s="12">
         <v>590</v>
@@ -3732,7 +3732,7 @@
         <v>87780</v>
       </c>
       <c r="L59" s="11">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="M59" s="12">
         <v>600</v>
@@ -3774,7 +3774,7 @@
         <v>91000</v>
       </c>
       <c r="L60" s="11">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="M60" s="12">
         <v>610</v>
@@ -3816,7 +3816,7 @@
         <v>94278</v>
       </c>
       <c r="L61" s="11">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="M61" s="12">
         <v>620</v>
@@ -3858,7 +3858,7 @@
         <v>97614</v>
       </c>
       <c r="L62" s="11">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="M62" s="12">
         <v>630</v>
@@ -3900,7 +3900,7 @@
         <v>101008</v>
       </c>
       <c r="L63" s="11">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M63" s="12">
         <v>640</v>
@@ -3942,7 +3942,7 @@
         <v>104460</v>
       </c>
       <c r="L64" s="11">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="M64" s="12">
         <v>650</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -1461,7 +1461,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L5" s="11">
         <v>0</v>
@@ -1503,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L6" s="11">
         <v>0</v>
@@ -1545,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="8">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="L7" s="11">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="8">
-        <v>468</v>
+        <v>80</v>
       </c>
       <c r="L8" s="11">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="8">
-        <v>730</v>
+        <v>200</v>
       </c>
       <c r="L9" s="11">
         <v>0</v>
@@ -1671,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="8">
-        <v>1050</v>
+        <v>500</v>
       </c>
       <c r="L10" s="11">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="8">
-        <v>1428</v>
+        <v>1000</v>
       </c>
       <c r="L11" s="11">
         <v>0</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -1455,7 +1455,7 @@
         <v>5</v>
       </c>
       <c r="I5" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J5" s="8">
         <v>1</v>
@@ -1497,7 +1497,7 @@
         <v>5</v>
       </c>
       <c r="I6" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J6" s="8">
         <v>1</v>
@@ -1539,7 +1539,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J7" s="8">
         <v>1</v>
@@ -1581,7 +1581,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J8" s="8">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J9" s="8">
         <v>1</v>
@@ -1665,7 +1665,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J10" s="8">
         <v>1</v>
@@ -1707,7 +1707,7 @@
         <v>5</v>
       </c>
       <c r="I11" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J11" s="8">
         <v>1</v>
@@ -1749,7 +1749,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J12" s="8">
         <v>1</v>
@@ -1791,7 +1791,7 @@
         <v>5</v>
       </c>
       <c r="I13" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J13" s="8">
         <v>1</v>
@@ -1833,7 +1833,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J14" s="8">
         <v>1</v>
@@ -1875,7 +1875,7 @@
         <v>5</v>
       </c>
       <c r="I15" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J15" s="8">
         <v>1</v>
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="I16" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J16" s="8">
         <v>1</v>
@@ -1959,7 +1959,7 @@
         <v>5</v>
       </c>
       <c r="I17" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J17" s="8">
         <v>1</v>
@@ -2001,7 +2001,7 @@
         <v>5</v>
       </c>
       <c r="I18" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J18" s="8">
         <v>1</v>
@@ -2043,7 +2043,7 @@
         <v>5</v>
       </c>
       <c r="I19" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J19" s="8">
         <v>1</v>
@@ -2085,7 +2085,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J20" s="8">
         <v>1</v>
@@ -2127,7 +2127,7 @@
         <v>5</v>
       </c>
       <c r="I21" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J21" s="8">
         <v>1</v>
@@ -2169,7 +2169,7 @@
         <v>5</v>
       </c>
       <c r="I22" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J22" s="8">
         <v>1</v>
@@ -2211,7 +2211,7 @@
         <v>5</v>
       </c>
       <c r="I23" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J23" s="8">
         <v>1</v>
@@ -2253,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="I24" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J24" s="8">
         <v>1</v>
@@ -2295,7 +2295,7 @@
         <v>5</v>
       </c>
       <c r="I25" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J25" s="8">
         <v>1</v>
@@ -2337,7 +2337,7 @@
         <v>5</v>
       </c>
       <c r="I26" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J26" s="8">
         <v>1</v>
@@ -2379,7 +2379,7 @@
         <v>5</v>
       </c>
       <c r="I27" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J27" s="8">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         <v>5</v>
       </c>
       <c r="I28" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J28" s="8">
         <v>1</v>
@@ -2463,7 +2463,7 @@
         <v>5</v>
       </c>
       <c r="I29" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J29" s="8">
         <v>1</v>
@@ -2505,7 +2505,7 @@
         <v>5</v>
       </c>
       <c r="I30" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J30" s="8">
         <v>1</v>
@@ -2547,7 +2547,7 @@
         <v>5</v>
       </c>
       <c r="I31" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J31" s="8">
         <v>1</v>
@@ -2589,7 +2589,7 @@
         <v>5</v>
       </c>
       <c r="I32" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J32" s="8">
         <v>1</v>
@@ -2631,7 +2631,7 @@
         <v>5</v>
       </c>
       <c r="I33" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J33" s="8">
         <v>1</v>
@@ -2673,7 +2673,7 @@
         <v>5</v>
       </c>
       <c r="I34" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J34" s="8">
         <v>1</v>
@@ -2715,7 +2715,7 @@
         <v>5</v>
       </c>
       <c r="I35" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J35" s="8">
         <v>1</v>
@@ -2757,7 +2757,7 @@
         <v>5</v>
       </c>
       <c r="I36" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J36" s="8">
         <v>1</v>
@@ -2799,7 +2799,7 @@
         <v>5</v>
       </c>
       <c r="I37" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J37" s="8">
         <v>1</v>
@@ -2841,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="I38" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J38" s="8">
         <v>1</v>
@@ -2883,7 +2883,7 @@
         <v>5</v>
       </c>
       <c r="I39" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J39" s="8">
         <v>1</v>
@@ -2925,7 +2925,7 @@
         <v>5</v>
       </c>
       <c r="I40" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J40" s="8">
         <v>1</v>
@@ -2967,7 +2967,7 @@
         <v>5</v>
       </c>
       <c r="I41" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J41" s="8">
         <v>1</v>
@@ -3009,7 +3009,7 @@
         <v>5</v>
       </c>
       <c r="I42" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J42" s="8">
         <v>1</v>
@@ -3051,7 +3051,7 @@
         <v>5</v>
       </c>
       <c r="I43" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J43" s="8">
         <v>1</v>
@@ -3093,7 +3093,7 @@
         <v>5</v>
       </c>
       <c r="I44" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J44" s="8">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>5</v>
       </c>
       <c r="I45" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J45" s="8">
         <v>1</v>
@@ -3177,7 +3177,7 @@
         <v>5</v>
       </c>
       <c r="I46" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J46" s="8">
         <v>1</v>
@@ -3219,7 +3219,7 @@
         <v>5</v>
       </c>
       <c r="I47" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J47" s="8">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         <v>5</v>
       </c>
       <c r="I48" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J48" s="8">
         <v>1</v>
@@ -3303,7 +3303,7 @@
         <v>5</v>
       </c>
       <c r="I49" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J49" s="8">
         <v>1</v>
@@ -3345,7 +3345,7 @@
         <v>5</v>
       </c>
       <c r="I50" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J50" s="8">
         <v>1</v>
@@ -3387,7 +3387,7 @@
         <v>5</v>
       </c>
       <c r="I51" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J51" s="8">
         <v>1</v>
@@ -3429,7 +3429,7 @@
         <v>5</v>
       </c>
       <c r="I52" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J52" s="8">
         <v>1</v>
@@ -3471,7 +3471,7 @@
         <v>5</v>
       </c>
       <c r="I53" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J53" s="8">
         <v>1</v>
@@ -3513,7 +3513,7 @@
         <v>5</v>
       </c>
       <c r="I54" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J54" s="8">
         <v>1</v>
@@ -3555,7 +3555,7 @@
         <v>5</v>
       </c>
       <c r="I55" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J55" s="8">
         <v>1</v>
@@ -3597,7 +3597,7 @@
         <v>5</v>
       </c>
       <c r="I56" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J56" s="8">
         <v>1</v>
@@ -3639,7 +3639,7 @@
         <v>5</v>
       </c>
       <c r="I57" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J57" s="8">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>5</v>
       </c>
       <c r="I58" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J58" s="8">
         <v>1</v>
@@ -3723,7 +3723,7 @@
         <v>5</v>
       </c>
       <c r="I59" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J59" s="8">
         <v>1</v>
@@ -3765,7 +3765,7 @@
         <v>5</v>
       </c>
       <c r="I60" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J60" s="8">
         <v>1</v>
@@ -3807,7 +3807,7 @@
         <v>5</v>
       </c>
       <c r="I61" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J61" s="8">
         <v>1</v>
@@ -3849,7 +3849,7 @@
         <v>5</v>
       </c>
       <c r="I62" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J62" s="8">
         <v>1</v>
@@ -3891,7 +3891,7 @@
         <v>5</v>
       </c>
       <c r="I63" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J63" s="8">
         <v>1</v>
@@ -3933,7 +3933,7 @@
         <v>5</v>
       </c>
       <c r="I64" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J64" s="8">
         <v>1</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M5" s="12">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="9">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="M6" s="12">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="9">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="M7" s="12">
         <v>0</v>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="9">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="M8" s="12">
         <v>0</v>
@@ -1861,7 +1861,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="9">
-        <v>200</v>
+        <v>519</v>
       </c>
       <c r="M9" s="12">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="9">
-        <v>500</v>
+        <v>859</v>
       </c>
       <c r="M10" s="12">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="9">
-        <v>1000</v>
+        <v>1322</v>
       </c>
       <c r="M11" s="12">
         <v>0</v>
@@ -1996,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="9">
-        <v>1864</v>
+        <v>1926</v>
       </c>
       <c r="M12" s="12">
         <v>0</v>
@@ -2041,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="9">
-        <v>2358</v>
+        <v>2691</v>
       </c>
       <c r="M13" s="12">
         <v>0</v>
@@ -2086,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="9">
-        <v>2910</v>
+        <v>3635</v>
       </c>
       <c r="M14" s="12">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="9">
-        <v>3520</v>
+        <v>4777</v>
       </c>
       <c r="M15" s="12">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="9">
-        <v>4188</v>
+        <v>6136</v>
       </c>
       <c r="M16" s="12">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="9">
-        <v>4914</v>
+        <v>7731</v>
       </c>
       <c r="M17" s="12">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="9">
-        <v>5698</v>
+        <v>9581</v>
       </c>
       <c r="M18" s="12">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="9">
-        <v>6540</v>
+        <v>11705</v>
       </c>
       <c r="M19" s="12">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="9">
-        <v>7440</v>
+        <v>14121</v>
       </c>
       <c r="M20" s="12">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="9">
-        <v>8398</v>
+        <v>16849</v>
       </c>
       <c r="M21" s="12">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="9">
-        <v>9414</v>
+        <v>19907</v>
       </c>
       <c r="M22" s="12">
         <v>0</v>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="L23" s="9">
-        <v>10488</v>
+        <v>23315</v>
       </c>
       <c r="M23" s="12">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="9">
-        <v>11620</v>
+        <v>27091</v>
       </c>
       <c r="M24" s="12">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="L25" s="9">
-        <v>12810</v>
+        <v>31254</v>
       </c>
       <c r="M25" s="12">
         <v>0</v>
@@ -2626,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="L26" s="9">
-        <v>14058</v>
+        <v>35823</v>
       </c>
       <c r="M26" s="12">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="L27" s="9">
-        <v>15364</v>
+        <v>40816</v>
       </c>
       <c r="M27" s="12">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="9">
-        <v>16728</v>
+        <v>46253</v>
       </c>
       <c r="M28" s="12">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         <v>1</v>
       </c>
       <c r="L29" s="9">
-        <v>18150</v>
+        <v>52153</v>
       </c>
       <c r="M29" s="12">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="9">
-        <v>19630</v>
+        <v>58534</v>
       </c>
       <c r="M30" s="12">
         <v>0</v>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="9">
-        <v>21168</v>
+        <v>65415</v>
       </c>
       <c r="M31" s="12">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="9">
-        <v>22764</v>
+        <v>72815</v>
       </c>
       <c r="M32" s="12">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="L33" s="9">
-        <v>24418</v>
+        <v>80754</v>
       </c>
       <c r="M33" s="12">
         <v>0</v>
@@ -2986,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="L34" s="9">
-        <v>26130</v>
+        <v>89249</v>
       </c>
       <c r="M34" s="12">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="L35" s="9">
-        <v>27900</v>
+        <v>98320</v>
       </c>
       <c r="M35" s="12">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>1</v>
       </c>
       <c r="L36" s="9">
-        <v>29728</v>
+        <v>107986</v>
       </c>
       <c r="M36" s="12">
         <v>0</v>
@@ -3121,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="9">
-        <v>31614</v>
+        <v>118265</v>
       </c>
       <c r="M37" s="12">
         <v>0</v>
@@ -3166,7 +3166,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="9">
-        <v>33558</v>
+        <v>129177</v>
       </c>
       <c r="M38" s="12">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="L39" s="9">
-        <v>35560</v>
+        <v>140740</v>
       </c>
       <c r="M39" s="12">
         <v>0</v>
@@ -3256,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="9">
-        <v>37620</v>
+        <v>152973</v>
       </c>
       <c r="M40" s="12">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="L41" s="9">
-        <v>39738</v>
+        <v>165896</v>
       </c>
       <c r="M41" s="12">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="L42" s="9">
-        <v>41914</v>
+        <v>179526</v>
       </c>
       <c r="M42" s="12">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="L43" s="9">
-        <v>44148</v>
+        <v>193883</v>
       </c>
       <c r="M43" s="12">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="L44" s="9">
-        <v>46440</v>
+        <v>208986</v>
       </c>
       <c r="M44" s="12">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="L45" s="9">
-        <v>48790</v>
+        <v>224854</v>
       </c>
       <c r="M45" s="12">
         <v>0</v>
@@ -3526,7 +3526,7 @@
         <v>1</v>
       </c>
       <c r="L46" s="9">
-        <v>51198</v>
+        <v>241505</v>
       </c>
       <c r="M46" s="12">
         <v>0</v>
@@ -3571,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="L47" s="9">
-        <v>53664</v>
+        <v>258958</v>
       </c>
       <c r="M47" s="12">
         <v>0</v>
@@ -3616,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="L48" s="9">
-        <v>56188</v>
+        <v>277233</v>
       </c>
       <c r="M48" s="12">
         <v>0</v>
@@ -3661,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="L49" s="9">
-        <v>58770</v>
+        <v>296348</v>
       </c>
       <c r="M49" s="12">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="L50" s="9">
-        <v>61410</v>
+        <v>316322</v>
       </c>
       <c r="M50" s="12">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>1</v>
       </c>
       <c r="L51" s="9">
-        <v>64108</v>
+        <v>337174</v>
       </c>
       <c r="M51" s="12">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="L52" s="9">
-        <v>66864</v>
+        <v>358922</v>
       </c>
       <c r="M52" s="12">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>1</v>
       </c>
       <c r="L53" s="9">
-        <v>69678</v>
+        <v>381586</v>
       </c>
       <c r="M53" s="12">
         <v>0</v>
@@ -3886,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="L54" s="9">
-        <v>72550</v>
+        <v>405184</v>
       </c>
       <c r="M54" s="12">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>1</v>
       </c>
       <c r="L55" s="9">
-        <v>75480</v>
+        <v>429736</v>
       </c>
       <c r="M55" s="12">
         <v>0</v>
@@ -3976,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="L56" s="9">
-        <v>78468</v>
+        <v>455260</v>
       </c>
       <c r="M56" s="12">
         <v>0</v>
@@ -4021,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="L57" s="9">
-        <v>81514</v>
+        <v>481775</v>
       </c>
       <c r="M57" s="12">
         <v>0</v>
@@ -4066,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="L58" s="9">
-        <v>84618</v>
+        <v>509300</v>
       </c>
       <c r="M58" s="12">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>1</v>
       </c>
       <c r="L59" s="9">
-        <v>87780</v>
+        <v>537854</v>
       </c>
       <c r="M59" s="12">
         <v>0</v>
@@ -4156,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="L60" s="9">
-        <v>91000</v>
+        <v>567456</v>
       </c>
       <c r="M60" s="12">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         <v>1</v>
       </c>
       <c r="L61" s="9">
-        <v>94278</v>
+        <v>598125</v>
       </c>
       <c r="M61" s="12">
         <v>0</v>
@@ -4246,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="L62" s="9">
-        <v>97614</v>
+        <v>629879</v>
       </c>
       <c r="M62" s="12">
         <v>0</v>
@@ -4291,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="L63" s="9">
-        <v>101008</v>
+        <v>662738</v>
       </c>
       <c r="M63" s="12">
         <v>0</v>
@@ -4336,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="L64" s="9">
-        <v>104460</v>
+        <v>9999999</v>
       </c>
       <c r="M64" s="12">
         <v>0</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="9">
-        <v>9</v>
+        <v>900</v>
       </c>
       <c r="M5" s="12">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="9">
-        <v>47</v>
+        <v>4700</v>
       </c>
       <c r="M6" s="12">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="9">
-        <v>132</v>
+        <v>13200</v>
       </c>
       <c r="M7" s="12">
         <v>0</v>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="9">
-        <v>283</v>
+        <v>28300</v>
       </c>
       <c r="M8" s="12">
         <v>0</v>
@@ -1861,7 +1861,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="9">
-        <v>519</v>
+        <v>51900</v>
       </c>
       <c r="M9" s="12">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="9">
-        <v>859</v>
+        <v>85900</v>
       </c>
       <c r="M10" s="12">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="9">
-        <v>1322</v>
+        <v>132200</v>
       </c>
       <c r="M11" s="12">
         <v>0</v>
@@ -1996,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="9">
-        <v>1926</v>
+        <v>192600</v>
       </c>
       <c r="M12" s="12">
         <v>0</v>
@@ -2041,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="9">
-        <v>2691</v>
+        <v>269100</v>
       </c>
       <c r="M13" s="12">
         <v>0</v>
@@ -2086,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="9">
-        <v>3635</v>
+        <v>363500</v>
       </c>
       <c r="M14" s="12">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="9">
-        <v>4777</v>
+        <v>477700</v>
       </c>
       <c r="M15" s="12">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="9">
-        <v>6136</v>
+        <v>613600</v>
       </c>
       <c r="M16" s="12">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="9">
-        <v>7731</v>
+        <v>773100</v>
       </c>
       <c r="M17" s="12">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="9">
-        <v>9581</v>
+        <v>958100</v>
       </c>
       <c r="M18" s="12">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="9">
-        <v>11705</v>
+        <v>1170500</v>
       </c>
       <c r="M19" s="12">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="9">
-        <v>14121</v>
+        <v>1412100</v>
       </c>
       <c r="M20" s="12">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="9">
-        <v>16849</v>
+        <v>1684900</v>
       </c>
       <c r="M21" s="12">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="9">
-        <v>19907</v>
+        <v>1990700</v>
       </c>
       <c r="M22" s="12">
         <v>0</v>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="L23" s="9">
-        <v>23315</v>
+        <v>2331500</v>
       </c>
       <c r="M23" s="12">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="9">
-        <v>27091</v>
+        <v>2709100</v>
       </c>
       <c r="M24" s="12">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="L25" s="9">
-        <v>31254</v>
+        <v>3125400</v>
       </c>
       <c r="M25" s="12">
         <v>0</v>
@@ -2626,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="L26" s="9">
-        <v>35823</v>
+        <v>3582300</v>
       </c>
       <c r="M26" s="12">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="L27" s="9">
-        <v>40816</v>
+        <v>4081600</v>
       </c>
       <c r="M27" s="12">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="9">
-        <v>46253</v>
+        <v>4625300</v>
       </c>
       <c r="M28" s="12">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         <v>1</v>
       </c>
       <c r="L29" s="9">
-        <v>52153</v>
+        <v>5215300</v>
       </c>
       <c r="M29" s="12">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="9">
-        <v>58534</v>
+        <v>5853400</v>
       </c>
       <c r="M30" s="12">
         <v>0</v>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="9">
-        <v>65415</v>
+        <v>6541500</v>
       </c>
       <c r="M31" s="12">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="9">
-        <v>72815</v>
+        <v>7281500</v>
       </c>
       <c r="M32" s="12">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="L33" s="9">
-        <v>80754</v>
+        <v>8075400</v>
       </c>
       <c r="M33" s="12">
         <v>0</v>
@@ -2986,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="L34" s="9">
-        <v>89249</v>
+        <v>8924900</v>
       </c>
       <c r="M34" s="12">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="L35" s="9">
-        <v>98320</v>
+        <v>9832000</v>
       </c>
       <c r="M35" s="12">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>1</v>
       </c>
       <c r="L36" s="9">
-        <v>107986</v>
+        <v>10798600</v>
       </c>
       <c r="M36" s="12">
         <v>0</v>
@@ -3121,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="9">
-        <v>118265</v>
+        <v>11826500</v>
       </c>
       <c r="M37" s="12">
         <v>0</v>
@@ -3166,7 +3166,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="9">
-        <v>129177</v>
+        <v>12917700</v>
       </c>
       <c r="M38" s="12">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="L39" s="9">
-        <v>140740</v>
+        <v>14074000</v>
       </c>
       <c r="M39" s="12">
         <v>0</v>
@@ -3256,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="9">
-        <v>152973</v>
+        <v>15297300</v>
       </c>
       <c r="M40" s="12">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="L41" s="9">
-        <v>165896</v>
+        <v>16589600</v>
       </c>
       <c r="M41" s="12">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="L42" s="9">
-        <v>179526</v>
+        <v>17952600</v>
       </c>
       <c r="M42" s="12">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="L43" s="9">
-        <v>193883</v>
+        <v>19388300</v>
       </c>
       <c r="M43" s="12">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="L44" s="9">
-        <v>208986</v>
+        <v>20898600</v>
       </c>
       <c r="M44" s="12">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="L45" s="9">
-        <v>224854</v>
+        <v>22485400</v>
       </c>
       <c r="M45" s="12">
         <v>0</v>
@@ -3526,7 +3526,7 @@
         <v>1</v>
       </c>
       <c r="L46" s="9">
-        <v>241505</v>
+        <v>24150500</v>
       </c>
       <c r="M46" s="12">
         <v>0</v>
@@ -3571,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="L47" s="9">
-        <v>258958</v>
+        <v>25895800</v>
       </c>
       <c r="M47" s="12">
         <v>0</v>
@@ -3616,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="L48" s="9">
-        <v>277233</v>
+        <v>27723300</v>
       </c>
       <c r="M48" s="12">
         <v>0</v>
@@ -3661,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="L49" s="9">
-        <v>296348</v>
+        <v>29634800</v>
       </c>
       <c r="M49" s="12">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="L50" s="9">
-        <v>316322</v>
+        <v>31632200</v>
       </c>
       <c r="M50" s="12">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>1</v>
       </c>
       <c r="L51" s="9">
-        <v>337174</v>
+        <v>33717400</v>
       </c>
       <c r="M51" s="12">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="L52" s="9">
-        <v>358922</v>
+        <v>35892200</v>
       </c>
       <c r="M52" s="12">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>1</v>
       </c>
       <c r="L53" s="9">
-        <v>381586</v>
+        <v>38158600</v>
       </c>
       <c r="M53" s="12">
         <v>0</v>
@@ -3886,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="L54" s="9">
-        <v>405184</v>
+        <v>40518400</v>
       </c>
       <c r="M54" s="12">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>1</v>
       </c>
       <c r="L55" s="9">
-        <v>429736</v>
+        <v>42973600</v>
       </c>
       <c r="M55" s="12">
         <v>0</v>
@@ -3976,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="L56" s="9">
-        <v>455260</v>
+        <v>45526000</v>
       </c>
       <c r="M56" s="12">
         <v>0</v>
@@ -4021,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="L57" s="9">
-        <v>481775</v>
+        <v>48177500</v>
       </c>
       <c r="M57" s="12">
         <v>0</v>
@@ -4066,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="L58" s="9">
-        <v>509300</v>
+        <v>50930000</v>
       </c>
       <c r="M58" s="12">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>1</v>
       </c>
       <c r="L59" s="9">
-        <v>537854</v>
+        <v>53785400</v>
       </c>
       <c r="M59" s="12">
         <v>0</v>
@@ -4156,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="L60" s="9">
-        <v>567456</v>
+        <v>56745600</v>
       </c>
       <c r="M60" s="12">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         <v>1</v>
       </c>
       <c r="L61" s="9">
-        <v>598125</v>
+        <v>59812500</v>
       </c>
       <c r="M61" s="12">
         <v>0</v>
@@ -4246,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="L62" s="9">
-        <v>629879</v>
+        <v>62987900</v>
       </c>
       <c r="M62" s="12">
         <v>0</v>
@@ -4291,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="L63" s="9">
-        <v>662738</v>
+        <v>66273800</v>
       </c>
       <c r="M63" s="12">
         <v>0</v>
@@ -4336,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="L64" s="9">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="M64" s="12">
         <v>0</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -248,7 +248,7 @@
     <t>int</t>
   </si>
   <si>
-    <t xml:space="preserve">map&lt;int{_}int&gt;{|} </t>
+    <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -324,150 +324,6 @@
   </si>
   <si>
     <t>1101_55|1102_55|1110_55|1107_55|1103_55|1104_55|1105_55|1106_55|1111_55|1112_55|1108_55|1109_55</t>
-  </si>
-  <si>
-    <t>1101_1|1102_1|1110_1|1107_1|1103_1|1104_1|1105_1|1106_1|1111_1|1112_1|1108_1|1109_1</t>
-  </si>
-  <si>
-    <t>1101_2|1102_2|1110_2|1107_2|1103_2|1104_2|1105_2|1106_2|1111_2|1112_2|1108_2|1109_2</t>
-  </si>
-  <si>
-    <t>1101_3|1102_3|1110_3|1107_3|1103_3|1104_3|1105_3|1106_3|1111_3|1112_3|1108_3|1109_3</t>
-  </si>
-  <si>
-    <t>1101_4|1102_4|1110_4|1107_4|1103_4|1104_4|1105_4|1106_4|1111_4|1112_4|1108_4|1109_4</t>
-  </si>
-  <si>
-    <t>1101_6|1102_6|1110_6|1107_6|1103_6|1104_6|1105_6|1106_6|1111_6|1112_6|1108_6|1109_6</t>
-  </si>
-  <si>
-    <t>1101_7|1102_7|1110_7|1107_7|1103_7|1104_7|1105_7|1106_7|1111_7|1112_7|1108_7|1109_7</t>
-  </si>
-  <si>
-    <t>1101_8|1102_8|1110_8|1107_8|1103_8|1104_8|1105_8|1106_8|1111_8|1112_8|1108_8|1109_8</t>
-  </si>
-  <si>
-    <t>1101_9|1102_9|1110_9|1107_9|1103_9|1104_9|1105_9|1106_9|1111_9|1112_9|1108_9|1109_9</t>
-  </si>
-  <si>
-    <t>1101_11|1102_11|1110_11|1107_11|1103_11|1104_11|1105_11|1106_11|1111_11|1112_11|1108_11|1109_11</t>
-  </si>
-  <si>
-    <t>1101_12|1102_12|1110_12|1107_12|1103_12|1104_12|1105_12|1106_12|1111_12|1112_12|1108_12|1109_12</t>
-  </si>
-  <si>
-    <t>1101_13|1102_13|1110_13|1107_13|1103_13|1104_13|1105_13|1106_13|1111_13|1112_13|1108_13|1109_13</t>
-  </si>
-  <si>
-    <t>1101_14|1102_14|1110_14|1107_14|1103_14|1104_14|1105_14|1106_14|1111_14|1112_14|1108_14|1109_14</t>
-  </si>
-  <si>
-    <t>1101_16|1102_16|1110_16|1107_16|1103_16|1104_16|1105_16|1106_16|1111_16|1112_16|1108_16|1109_16</t>
-  </si>
-  <si>
-    <t>1101_17|1102_17|1110_17|1107_17|1103_17|1104_17|1105_17|1106_17|1111_17|1112_17|1108_17|1109_17</t>
-  </si>
-  <si>
-    <t>1101_18|1102_18|1110_18|1107_18|1103_18|1104_18|1105_18|1106_18|1111_18|1112_18|1108_18|1109_18</t>
-  </si>
-  <si>
-    <t>1101_19|1102_19|1110_19|1107_19|1103_19|1104_19|1105_19|1106_19|1111_19|1112_19|1108_19|1109_19</t>
-  </si>
-  <si>
-    <t>1101_21|1102_21|1110_21|1107_21|1103_21|1104_21|1105_21|1106_21|1111_21|1112_21|1108_21|1109_21</t>
-  </si>
-  <si>
-    <t>1101_22|1102_22|1110_22|1107_22|1103_22|1104_22|1105_22|1106_22|1111_22|1112_22|1108_22|1109_22</t>
-  </si>
-  <si>
-    <t>1101_23|1102_23|1110_23|1107_23|1103_23|1104_23|1105_23|1106_23|1111_23|1112_23|1108_23|1109_23</t>
-  </si>
-  <si>
-    <t>1101_24|1102_24|1110_24|1107_24|1103_24|1104_24|1105_24|1106_24|1111_24|1112_24|1108_24|1109_24</t>
-  </si>
-  <si>
-    <t>1101_26|1102_26|1110_26|1107_26|1103_26|1104_26|1105_26|1106_26|1111_26|1112_26|1108_26|1109_26</t>
-  </si>
-  <si>
-    <t>1101_27|1102_27|1110_27|1107_27|1103_27|1104_27|1105_27|1106_27|1111_27|1112_27|1108_27|1109_27</t>
-  </si>
-  <si>
-    <t>1101_28|1102_28|1110_28|1107_28|1103_28|1104_28|1105_28|1106_28|1111_28|1112_28|1108_28|1109_28</t>
-  </si>
-  <si>
-    <t>1101_29|1102_29|1110_29|1107_29|1103_29|1104_29|1105_29|1106_29|1111_29|1112_29|1108_29|1109_29</t>
-  </si>
-  <si>
-    <t>1101_31|1102_31|1110_31|1107_31|1103_31|1104_31|1105_31|1106_31|1111_31|1112_31|1108_31|1109_31</t>
-  </si>
-  <si>
-    <t>1101_32|1102_32|1110_32|1107_32|1103_32|1104_32|1105_32|1106_32|1111_32|1112_32|1108_32|1109_32</t>
-  </si>
-  <si>
-    <t>1101_33|1102_33|1110_33|1107_33|1103_33|1104_33|1105_33|1106_33|1111_33|1112_33|1108_33|1109_33</t>
-  </si>
-  <si>
-    <t>1101_34|1102_34|1110_34|1107_34|1103_34|1104_34|1105_34|1106_34|1111_34|1112_34|1108_34|1109_34</t>
-  </si>
-  <si>
-    <t>1101_36|1102_36|1110_36|1107_36|1103_36|1104_36|1105_36|1106_36|1111_36|1112_36|1108_36|1109_36</t>
-  </si>
-  <si>
-    <t>1101_37|1102_37|1110_37|1107_37|1103_37|1104_37|1105_37|1106_37|1111_37|1112_37|1108_37|1109_37</t>
-  </si>
-  <si>
-    <t>1101_38|1102_38|1110_38|1107_38|1103_38|1104_38|1105_38|1106_38|1111_38|1112_38|1108_38|1109_38</t>
-  </si>
-  <si>
-    <t>1101_39|1102_39|1110_39|1107_39|1103_39|1104_39|1105_39|1106_39|1111_39|1112_39|1108_39|1109_39</t>
-  </si>
-  <si>
-    <t>1101_41|1102_41|1110_41|1107_41|1103_41|1104_41|1105_41|1106_41|1111_41|1112_41|1108_41|1109_41</t>
-  </si>
-  <si>
-    <t>1101_42|1102_42|1110_42|1107_42|1103_42|1104_42|1105_42|1106_42|1111_42|1112_42|1108_42|1109_42</t>
-  </si>
-  <si>
-    <t>1101_43|1102_43|1110_43|1107_43|1103_43|1104_43|1105_43|1106_43|1111_43|1112_43|1108_43|1109_43</t>
-  </si>
-  <si>
-    <t>1101_44|1102_44|1110_44|1107_44|1103_44|1104_44|1105_44|1106_44|1111_44|1112_44|1108_44|1109_44</t>
-  </si>
-  <si>
-    <t>1101_46|1102_46|1110_46|1107_46|1103_46|1104_46|1105_46|1106_46|1111_46|1112_46|1108_46|1109_46</t>
-  </si>
-  <si>
-    <t>1101_47|1102_47|1110_47|1107_47|1103_47|1104_47|1105_47|1106_47|1111_47|1112_47|1108_47|1109_47</t>
-  </si>
-  <si>
-    <t>1101_48|1102_48|1110_48|1107_48|1103_48|1104_48|1105_48|1106_48|1111_48|1112_48|1108_48|1109_48</t>
-  </si>
-  <si>
-    <t>1101_49|1102_49|1110_49|1107_49|1103_49|1104_49|1105_49|1106_49|1111_49|1112_49|1108_49|1109_49</t>
-  </si>
-  <si>
-    <t>1101_51|1102_51|1110_51|1107_51|1103_51|1104_51|1105_51|1106_51|1111_51|1112_51|1108_51|1109_51</t>
-  </si>
-  <si>
-    <t>1101_52|1102_52|1110_52|1107_52|1103_52|1104_52|1105_52|1106_52|1111_52|1112_52|1108_52|1109_52</t>
-  </si>
-  <si>
-    <t>1101_53|1102_53|1110_53|1107_53|1103_53|1104_53|1105_53|1106_53|1111_53|1112_53|1108_53|1109_53</t>
-  </si>
-  <si>
-    <t>1101_54|1102_54|1110_54|1107_54|1103_54|1104_54|1105_54|1106_54|1111_54|1112_54|1108_54|1109_54</t>
-  </si>
-  <si>
-    <t>1101_56|1102_56|1110_56|1107_56|1103_56|1104_56|1105_56|1106_56|1111_56|1112_56|1108_56|1109_56</t>
-  </si>
-  <si>
-    <t>1101_57|1102_57|1110_57|1107_57|1103_57|1104_57|1105_57|1106_57|1111_57|1112_57|1108_57|1109_57</t>
-  </si>
-  <si>
-    <t>1101_58|1102_58|1110_58|1107_58|1103_58|1104_58|1105_58|1106_58|1111_58|1112_58|1108_58|1109_58</t>
-  </si>
-  <si>
-    <t>1101_59|1102_59|1110_59|1107_59|1103_59|1104_59|1105_59|1106_59|1111_59|1112_59|1108_59|1109_59</t>
   </si>
 </sst>
 </file>
@@ -1501,7 +1357,7 @@
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="11.625" style="3" customWidth="1"/>
     <col min="3" max="3" width="11.875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="97.35" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.875" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="3" customWidth="1"/>
     <col min="7" max="10" width="29.25" style="3" customWidth="1"/>
@@ -1714,7 +1570,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="9">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G6" s="11">
         <v>110</v>
@@ -1757,7 +1613,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="9">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G7" s="11">
         <v>120</v>
@@ -1800,7 +1656,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="9">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G8" s="11">
         <v>130</v>
@@ -1843,7 +1699,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="9">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G9" s="11">
         <v>140</v>
@@ -1881,14 +1737,12 @@
       <c r="C10" s="9">
         <v>1</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>30</v>
-      </c>
+      <c r="D10" s="9"/>
       <c r="E10" s="9">
         <v>6</v>
       </c>
       <c r="F10" s="9">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G10" s="11">
         <v>150</v>
@@ -1926,9 +1780,7 @@
       <c r="C11" s="9">
         <v>1</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>30</v>
-      </c>
+      <c r="D11" s="9"/>
       <c r="E11" s="9">
         <v>7</v>
       </c>
@@ -1971,9 +1823,7 @@
       <c r="C12" s="9">
         <v>1</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>30</v>
-      </c>
+      <c r="D12" s="9"/>
       <c r="E12" s="9">
         <v>8</v>
       </c>
@@ -1993,7 +1843,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="9">
         <v>192600</v>
@@ -2016,9 +1866,7 @@
       <c r="C13" s="9">
         <v>1</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>30</v>
-      </c>
+      <c r="D13" s="9"/>
       <c r="E13" s="9">
         <v>9</v>
       </c>
@@ -2038,7 +1886,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="9">
         <v>269100</v>
@@ -2061,14 +1909,12 @@
       <c r="C14" s="9">
         <v>1</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>30</v>
-      </c>
+      <c r="D14" s="9"/>
       <c r="E14" s="9">
         <v>10</v>
       </c>
       <c r="F14" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G14" s="11">
         <v>190</v>
@@ -2083,7 +1929,7 @@
         <v>2</v>
       </c>
       <c r="K14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="9">
         <v>363500</v>
@@ -2106,14 +1952,12 @@
       <c r="C15" s="9">
         <v>1</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>31</v>
-      </c>
+      <c r="D15" s="9"/>
       <c r="E15" s="9">
         <v>11</v>
       </c>
       <c r="F15" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G15" s="11">
         <v>200</v>
@@ -2125,10 +1969,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="9">
         <v>477700</v>
@@ -2151,14 +1995,12 @@
       <c r="C16" s="9">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>31</v>
-      </c>
+      <c r="D16" s="9"/>
       <c r="E16" s="9">
         <v>12</v>
       </c>
       <c r="F16" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G16" s="11">
         <v>210</v>
@@ -2170,10 +2012,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K16" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="9">
         <v>613600</v>
@@ -2196,14 +2038,12 @@
       <c r="C17" s="9">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>31</v>
-      </c>
+      <c r="D17" s="9"/>
       <c r="E17" s="9">
         <v>13</v>
       </c>
       <c r="F17" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G17" s="11">
         <v>220</v>
@@ -2215,10 +2055,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K17" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9">
         <v>773100</v>
@@ -2241,14 +2081,12 @@
       <c r="C18" s="9">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>31</v>
-      </c>
+      <c r="D18" s="9"/>
       <c r="E18" s="9">
         <v>14</v>
       </c>
       <c r="F18" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G18" s="11">
         <v>230</v>
@@ -2260,10 +2098,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="9">
         <v>958100</v>
@@ -2286,14 +2124,12 @@
       <c r="C19" s="9">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>31</v>
-      </c>
+      <c r="D19" s="9"/>
       <c r="E19" s="9">
         <v>15</v>
       </c>
       <c r="F19" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G19" s="11">
         <v>240</v>
@@ -2305,10 +2141,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="9">
         <v>1170500</v>
@@ -2331,14 +2167,12 @@
       <c r="C20" s="9">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="D20" s="9"/>
       <c r="E20" s="9">
         <v>16</v>
       </c>
       <c r="F20" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G20" s="11">
         <v>250</v>
@@ -2350,10 +2184,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="9">
         <v>1412100</v>
@@ -2376,14 +2210,12 @@
       <c r="C21" s="9">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="D21" s="9"/>
       <c r="E21" s="9">
         <v>17</v>
       </c>
       <c r="F21" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G21" s="11">
         <v>260</v>
@@ -2395,10 +2227,10 @@
         <v>5</v>
       </c>
       <c r="J21" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K21" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="9">
         <v>1684900</v>
@@ -2421,14 +2253,12 @@
       <c r="C22" s="9">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="D22" s="9"/>
       <c r="E22" s="9">
         <v>18</v>
       </c>
       <c r="F22" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G22" s="11">
         <v>270</v>
@@ -2440,10 +2270,10 @@
         <v>5</v>
       </c>
       <c r="J22" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K22" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="9">
         <v>1990700</v>
@@ -2466,14 +2296,12 @@
       <c r="C23" s="9">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="D23" s="9"/>
       <c r="E23" s="9">
         <v>19</v>
       </c>
       <c r="F23" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G23" s="11">
         <v>280</v>
@@ -2485,10 +2313,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K23" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="9">
         <v>2331500</v>
@@ -2511,14 +2339,12 @@
       <c r="C24" s="9">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="D24" s="9"/>
       <c r="E24" s="9">
         <v>20</v>
       </c>
       <c r="F24" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G24" s="11">
         <v>290</v>
@@ -2530,10 +2356,10 @@
         <v>5</v>
       </c>
       <c r="J24" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K24" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="9">
         <v>2709100</v>
@@ -2556,14 +2382,12 @@
       <c r="C25" s="9">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="D25" s="9"/>
       <c r="E25" s="9">
         <v>21</v>
       </c>
       <c r="F25" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G25" s="11">
         <v>300</v>
@@ -2575,10 +2399,10 @@
         <v>5</v>
       </c>
       <c r="J25" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K25" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="9">
         <v>3125400</v>
@@ -2601,14 +2425,12 @@
       <c r="C26" s="9">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="D26" s="9"/>
       <c r="E26" s="9">
         <v>22</v>
       </c>
       <c r="F26" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G26" s="11">
         <v>310</v>
@@ -2620,10 +2442,10 @@
         <v>5</v>
       </c>
       <c r="J26" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K26" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="9">
         <v>3582300</v>
@@ -2646,14 +2468,12 @@
       <c r="C27" s="9">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="D27" s="9"/>
       <c r="E27" s="9">
         <v>23</v>
       </c>
       <c r="F27" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G27" s="11">
         <v>320</v>
@@ -2665,10 +2485,10 @@
         <v>5</v>
       </c>
       <c r="J27" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K27" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="9">
         <v>4081600</v>
@@ -2691,14 +2511,12 @@
       <c r="C28" s="9">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="D28" s="9"/>
       <c r="E28" s="9">
         <v>24</v>
       </c>
       <c r="F28" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G28" s="11">
         <v>330</v>
@@ -2713,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="K28" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="9">
         <v>4625300</v>
@@ -2736,14 +2554,12 @@
       <c r="C29" s="9">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="D29" s="9"/>
       <c r="E29" s="9">
         <v>25</v>
       </c>
       <c r="F29" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G29" s="11">
         <v>340</v>
@@ -2781,14 +2597,12 @@
       <c r="C30" s="9">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>34</v>
-      </c>
+      <c r="D30" s="9"/>
       <c r="E30" s="9">
         <v>26</v>
       </c>
       <c r="F30" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G30" s="11">
         <v>350</v>
@@ -2826,14 +2640,12 @@
       <c r="C31" s="9">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>34</v>
-      </c>
+      <c r="D31" s="9"/>
       <c r="E31" s="9">
         <v>27</v>
       </c>
       <c r="F31" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G31" s="11">
         <v>360</v>
@@ -2871,14 +2683,12 @@
       <c r="C32" s="9">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>34</v>
-      </c>
+      <c r="D32" s="9"/>
       <c r="E32" s="9">
         <v>28</v>
       </c>
       <c r="F32" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G32" s="11">
         <v>370</v>
@@ -2916,14 +2726,12 @@
       <c r="C33" s="9">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>34</v>
-      </c>
+      <c r="D33" s="9"/>
       <c r="E33" s="9">
         <v>29</v>
       </c>
       <c r="F33" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G33" s="11">
         <v>380</v>
@@ -2961,14 +2769,12 @@
       <c r="C34" s="9">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>34</v>
-      </c>
+      <c r="D34" s="9"/>
       <c r="E34" s="9">
         <v>30</v>
       </c>
       <c r="F34" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G34" s="11">
         <v>390</v>
@@ -3006,14 +2812,12 @@
       <c r="C35" s="9">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>35</v>
-      </c>
+      <c r="D35" s="9"/>
       <c r="E35" s="9">
         <v>31</v>
       </c>
       <c r="F35" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G35" s="11">
         <v>400</v>
@@ -3051,14 +2855,12 @@
       <c r="C36" s="9">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>35</v>
-      </c>
+      <c r="D36" s="9"/>
       <c r="E36" s="9">
         <v>32</v>
       </c>
       <c r="F36" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G36" s="11">
         <v>410</v>
@@ -3096,14 +2898,12 @@
       <c r="C37" s="9">
         <v>1</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>35</v>
-      </c>
+      <c r="D37" s="9"/>
       <c r="E37" s="9">
         <v>33</v>
       </c>
       <c r="F37" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G37" s="11">
         <v>420</v>
@@ -3141,14 +2941,12 @@
       <c r="C38" s="9">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>35</v>
-      </c>
+      <c r="D38" s="9"/>
       <c r="E38" s="9">
         <v>34</v>
       </c>
       <c r="F38" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G38" s="11">
         <v>430</v>
@@ -3186,14 +2984,12 @@
       <c r="C39" s="9">
         <v>1</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>35</v>
-      </c>
+      <c r="D39" s="9"/>
       <c r="E39" s="9">
         <v>35</v>
       </c>
       <c r="F39" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G39" s="11">
         <v>440</v>
@@ -3231,14 +3027,12 @@
       <c r="C40" s="9">
         <v>1</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="D40" s="9"/>
       <c r="E40" s="9">
         <v>36</v>
       </c>
       <c r="F40" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G40" s="11">
         <v>450</v>
@@ -3276,14 +3070,12 @@
       <c r="C41" s="9">
         <v>1</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="D41" s="9"/>
       <c r="E41" s="9">
         <v>37</v>
       </c>
       <c r="F41" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G41" s="11">
         <v>460</v>
@@ -3321,14 +3113,12 @@
       <c r="C42" s="9">
         <v>1</v>
       </c>
-      <c r="D42" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="D42" s="9"/>
       <c r="E42" s="9">
         <v>38</v>
       </c>
       <c r="F42" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G42" s="11">
         <v>470</v>
@@ -3366,14 +3156,12 @@
       <c r="C43" s="9">
         <v>1</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="D43" s="9"/>
       <c r="E43" s="9">
         <v>39</v>
       </c>
       <c r="F43" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G43" s="11">
         <v>480</v>
@@ -3411,14 +3199,12 @@
       <c r="C44" s="9">
         <v>1</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="D44" s="9"/>
       <c r="E44" s="9">
         <v>40</v>
       </c>
       <c r="F44" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G44" s="11">
         <v>490</v>
@@ -3456,14 +3242,12 @@
       <c r="C45" s="9">
         <v>1</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="D45" s="9"/>
       <c r="E45" s="9">
         <v>41</v>
       </c>
       <c r="F45" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G45" s="11">
         <v>500</v>
@@ -3501,14 +3285,12 @@
       <c r="C46" s="9">
         <v>1</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="D46" s="9"/>
       <c r="E46" s="9">
         <v>42</v>
       </c>
       <c r="F46" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G46" s="11">
         <v>510</v>
@@ -3546,14 +3328,12 @@
       <c r="C47" s="9">
         <v>1</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="D47" s="9"/>
       <c r="E47" s="9">
         <v>43</v>
       </c>
       <c r="F47" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G47" s="11">
         <v>520</v>
@@ -3591,14 +3371,12 @@
       <c r="C48" s="9">
         <v>1</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="D48" s="9"/>
       <c r="E48" s="9">
         <v>44</v>
       </c>
       <c r="F48" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G48" s="11">
         <v>530</v>
@@ -3636,14 +3414,12 @@
       <c r="C49" s="9">
         <v>1</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="D49" s="9"/>
       <c r="E49" s="9">
         <v>45</v>
       </c>
       <c r="F49" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G49" s="11">
         <v>540</v>
@@ -3681,14 +3457,12 @@
       <c r="C50" s="9">
         <v>1</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>38</v>
-      </c>
+      <c r="D50" s="9"/>
       <c r="E50" s="9">
         <v>46</v>
       </c>
       <c r="F50" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G50" s="11">
         <v>550</v>
@@ -3726,14 +3500,12 @@
       <c r="C51" s="9">
         <v>1</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>38</v>
-      </c>
+      <c r="D51" s="9"/>
       <c r="E51" s="9">
         <v>47</v>
       </c>
       <c r="F51" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G51" s="11">
         <v>560</v>
@@ -3771,14 +3543,12 @@
       <c r="C52" s="9">
         <v>1</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>38</v>
-      </c>
+      <c r="D52" s="9"/>
       <c r="E52" s="9">
         <v>48</v>
       </c>
       <c r="F52" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G52" s="11">
         <v>570</v>
@@ -3816,14 +3586,12 @@
       <c r="C53" s="9">
         <v>1</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>38</v>
-      </c>
+      <c r="D53" s="9"/>
       <c r="E53" s="9">
         <v>49</v>
       </c>
       <c r="F53" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G53" s="11">
         <v>580</v>
@@ -3861,14 +3629,12 @@
       <c r="C54" s="9">
         <v>1</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>38</v>
-      </c>
+      <c r="D54" s="9"/>
       <c r="E54" s="9">
         <v>50</v>
       </c>
       <c r="F54" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G54" s="11">
         <v>590</v>
@@ -3906,14 +3672,12 @@
       <c r="C55" s="9">
         <v>1</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>39</v>
-      </c>
+      <c r="D55" s="9"/>
       <c r="E55" s="9">
         <v>51</v>
       </c>
       <c r="F55" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G55" s="11">
         <v>600</v>
@@ -3951,14 +3715,12 @@
       <c r="C56" s="9">
         <v>1</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>39</v>
-      </c>
+      <c r="D56" s="9"/>
       <c r="E56" s="9">
         <v>52</v>
       </c>
       <c r="F56" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G56" s="11">
         <v>610</v>
@@ -3996,14 +3758,12 @@
       <c r="C57" s="9">
         <v>1</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>39</v>
-      </c>
+      <c r="D57" s="9"/>
       <c r="E57" s="9">
         <v>53</v>
       </c>
       <c r="F57" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G57" s="11">
         <v>620</v>
@@ -4041,14 +3801,12 @@
       <c r="C58" s="9">
         <v>1</v>
       </c>
-      <c r="D58" s="9" t="s">
-        <v>39</v>
-      </c>
+      <c r="D58" s="9"/>
       <c r="E58" s="9">
         <v>54</v>
       </c>
       <c r="F58" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G58" s="11">
         <v>630</v>
@@ -4086,14 +3844,12 @@
       <c r="C59" s="9">
         <v>1</v>
       </c>
-      <c r="D59" s="9" t="s">
-        <v>39</v>
-      </c>
+      <c r="D59" s="9"/>
       <c r="E59" s="9">
         <v>55</v>
       </c>
       <c r="F59" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G59" s="11">
         <v>640</v>
@@ -4131,14 +3887,12 @@
       <c r="C60" s="9">
         <v>1</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="D60" s="9"/>
       <c r="E60" s="9">
         <v>56</v>
       </c>
       <c r="F60" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G60" s="11">
         <v>650</v>
@@ -4176,14 +3930,12 @@
       <c r="C61" s="9">
         <v>1</v>
       </c>
-      <c r="D61" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="D61" s="9"/>
       <c r="E61" s="9">
         <v>57</v>
       </c>
       <c r="F61" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G61" s="11">
         <v>660</v>
@@ -4221,14 +3973,12 @@
       <c r="C62" s="9">
         <v>1</v>
       </c>
-      <c r="D62" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="D62" s="9"/>
       <c r="E62" s="9">
         <v>58</v>
       </c>
       <c r="F62" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G62" s="11">
         <v>670</v>
@@ -4266,14 +4016,12 @@
       <c r="C63" s="9">
         <v>1</v>
       </c>
-      <c r="D63" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="D63" s="9"/>
       <c r="E63" s="9">
         <v>59</v>
       </c>
       <c r="F63" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G63" s="11">
         <v>680</v>
@@ -4311,14 +4059,12 @@
       <c r="C64" s="9">
         <v>1</v>
       </c>
-      <c r="D64" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="D64" s="9"/>
       <c r="E64" s="9">
         <v>60</v>
       </c>
       <c r="F64" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G64" s="11">
         <v>690</v>
@@ -4356,16 +4102,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="88.675" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4384,9 +4128,7 @@
       <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4405,9 +4147,7 @@
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -4426,9 +4166,7 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -4447,9 +4185,7 @@
       <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -4468,9 +4204,7 @@
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -4490,7 +4224,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -4511,7 +4245,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -4532,7 +4266,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -4553,7 +4287,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -4574,7 +4308,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -4595,7 +4329,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -4616,7 +4350,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -4637,7 +4371,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4658,7 +4392,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4679,7 +4413,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4700,7 +4434,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4721,7 +4455,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4742,7 +4476,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4763,241 +4497,251 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1"/>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="1"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="B31" s="1"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="B32" s="1"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="B33" s="1"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="B34" s="1"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" s="1"/>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1"/>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="B39" s="1"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B41" s="1"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="B42" s="1"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B47" s="1"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="B49" s="1"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B50" s="1"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="B51" s="1"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="B52" s="1"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B53" s="1"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="B54" s="1"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="1"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="B56" s="1"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -1570,7 +1570,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="9">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G6" s="11">
         <v>110</v>
@@ -1613,7 +1613,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="9">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G7" s="11">
         <v>120</v>
@@ -1699,7 +1699,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="9">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G9" s="11">
         <v>140</v>
@@ -1742,7 +1742,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="9">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="G10" s="11">
         <v>150</v>
@@ -1785,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="F11" s="9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G11" s="11">
         <v>160</v>
@@ -1828,7 +1828,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G12" s="11">
         <v>170</v>
@@ -1871,7 +1871,7 @@
         <v>9</v>
       </c>
       <c r="F13" s="9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G13" s="11">
         <v>180</v>
@@ -1914,7 +1914,7 @@
         <v>10</v>
       </c>
       <c r="F14" s="9">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G14" s="11">
         <v>190</v>
@@ -1957,7 +1957,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="9">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G15" s="11">
         <v>200</v>
@@ -2000,7 +2000,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="9">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G16" s="11">
         <v>210</v>
@@ -2043,7 +2043,7 @@
         <v>13</v>
       </c>
       <c r="F17" s="9">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G17" s="11">
         <v>220</v>
@@ -2086,7 +2086,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="9">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G18" s="11">
         <v>230</v>
@@ -2129,7 +2129,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="9">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G19" s="11">
         <v>240</v>
@@ -2430,7 +2430,7 @@
         <v>22</v>
       </c>
       <c r="F26" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G26" s="11">
         <v>310</v>
@@ -2473,7 +2473,7 @@
         <v>23</v>
       </c>
       <c r="F27" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G27" s="11">
         <v>320</v>
@@ -2516,7 +2516,7 @@
         <v>24</v>
       </c>
       <c r="F28" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G28" s="11">
         <v>330</v>
@@ -2559,7 +2559,7 @@
         <v>25</v>
       </c>
       <c r="F29" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G29" s="11">
         <v>340</v>
@@ -2602,7 +2602,7 @@
         <v>26</v>
       </c>
       <c r="F30" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G30" s="11">
         <v>350</v>
@@ -2645,7 +2645,7 @@
         <v>27</v>
       </c>
       <c r="F31" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G31" s="11">
         <v>360</v>
@@ -2688,7 +2688,7 @@
         <v>28</v>
       </c>
       <c r="F32" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G32" s="11">
         <v>370</v>
@@ -2731,7 +2731,7 @@
         <v>29</v>
       </c>
       <c r="F33" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G33" s="11">
         <v>380</v>
@@ -2774,7 +2774,7 @@
         <v>30</v>
       </c>
       <c r="F34" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G34" s="11">
         <v>390</v>
@@ -2817,7 +2817,7 @@
         <v>31</v>
       </c>
       <c r="F35" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G35" s="11">
         <v>400</v>
@@ -2860,7 +2860,7 @@
         <v>32</v>
       </c>
       <c r="F36" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G36" s="11">
         <v>410</v>
@@ -2903,7 +2903,7 @@
         <v>33</v>
       </c>
       <c r="F37" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G37" s="11">
         <v>420</v>
@@ -2946,7 +2946,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G38" s="11">
         <v>430</v>
@@ -2989,7 +2989,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G39" s="11">
         <v>440</v>
@@ -3032,7 +3032,7 @@
         <v>36</v>
       </c>
       <c r="F40" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G40" s="11">
         <v>450</v>
@@ -3075,7 +3075,7 @@
         <v>37</v>
       </c>
       <c r="F41" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G41" s="11">
         <v>460</v>
@@ -3118,7 +3118,7 @@
         <v>38</v>
       </c>
       <c r="F42" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G42" s="11">
         <v>470</v>
@@ -3161,7 +3161,7 @@
         <v>39</v>
       </c>
       <c r="F43" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G43" s="11">
         <v>480</v>
@@ -3204,7 +3204,7 @@
         <v>40</v>
       </c>
       <c r="F44" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G44" s="11">
         <v>490</v>
@@ -3247,7 +3247,7 @@
         <v>41</v>
       </c>
       <c r="F45" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G45" s="11">
         <v>500</v>
@@ -3290,7 +3290,7 @@
         <v>42</v>
       </c>
       <c r="F46" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G46" s="11">
         <v>510</v>
@@ -3333,7 +3333,7 @@
         <v>43</v>
       </c>
       <c r="F47" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G47" s="11">
         <v>520</v>
@@ -3376,7 +3376,7 @@
         <v>44</v>
       </c>
       <c r="F48" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G48" s="11">
         <v>530</v>
@@ -3419,7 +3419,7 @@
         <v>45</v>
       </c>
       <c r="F49" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G49" s="11">
         <v>540</v>
@@ -3462,7 +3462,7 @@
         <v>46</v>
       </c>
       <c r="F50" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G50" s="11">
         <v>550</v>
@@ -3505,7 +3505,7 @@
         <v>47</v>
       </c>
       <c r="F51" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G51" s="11">
         <v>560</v>
@@ -3548,7 +3548,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G52" s="11">
         <v>570</v>
@@ -3591,7 +3591,7 @@
         <v>49</v>
       </c>
       <c r="F53" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G53" s="11">
         <v>580</v>
@@ -3634,7 +3634,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G54" s="11">
         <v>590</v>
@@ -3677,7 +3677,7 @@
         <v>51</v>
       </c>
       <c r="F55" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G55" s="11">
         <v>600</v>
@@ -3720,7 +3720,7 @@
         <v>52</v>
       </c>
       <c r="F56" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G56" s="11">
         <v>610</v>
@@ -3763,7 +3763,7 @@
         <v>53</v>
       </c>
       <c r="F57" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G57" s="11">
         <v>620</v>
@@ -3806,7 +3806,7 @@
         <v>54</v>
       </c>
       <c r="F58" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G58" s="11">
         <v>630</v>
@@ -3849,7 +3849,7 @@
         <v>55</v>
       </c>
       <c r="F59" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G59" s="11">
         <v>640</v>
@@ -3892,7 +3892,7 @@
         <v>56</v>
       </c>
       <c r="F60" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G60" s="11">
         <v>650</v>
@@ -3935,7 +3935,7 @@
         <v>57</v>
       </c>
       <c r="F61" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G61" s="11">
         <v>660</v>
@@ -3978,7 +3978,7 @@
         <v>58</v>
       </c>
       <c r="F62" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G62" s="11">
         <v>670</v>
@@ -4021,7 +4021,7 @@
         <v>59</v>
       </c>
       <c r="F63" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G63" s="11">
         <v>680</v>
@@ -4064,7 +4064,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G64" s="11">
         <v>690</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="53">
   <si>
     <t>ID</t>
   </si>
@@ -291,6 +291,42 @@
   </si>
   <si>
     <t>拉斯维加斯</t>
+  </si>
+  <si>
+    <t>1102_1</t>
+  </si>
+  <si>
+    <t>1202_1|1303_1|1304_1</t>
+  </si>
+  <si>
+    <t>1110_1</t>
+  </si>
+  <si>
+    <t>1107_1</t>
+  </si>
+  <si>
+    <t>1106_1</t>
+  </si>
+  <si>
+    <t>1105_1</t>
+  </si>
+  <si>
+    <t>1104_1</t>
+  </si>
+  <si>
+    <t>1103_1</t>
+  </si>
+  <si>
+    <t>1109_1</t>
+  </si>
+  <si>
+    <t>1108_1</t>
+  </si>
+  <si>
+    <t>1112_1</t>
+  </si>
+  <si>
+    <t>1111_1</t>
   </si>
   <si>
     <t>1101_5|1102_5|1110_5|1107_5|1103_5|1104_5|1105_5|1106_5|1111_5|1112_5|1108_5|1109_5</t>
@@ -508,12 +544,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1613,7 +1649,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="9">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G7" s="11">
         <v>120</v>
@@ -1651,12 +1687,14 @@
       <c r="C8" s="9">
         <v>1</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="E8" s="9">
         <v>4</v>
       </c>
       <c r="F8" s="9">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G8" s="11">
         <v>130</v>
@@ -1694,7 +1732,9 @@
       <c r="C9" s="9">
         <v>1</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="E9" s="9">
         <v>5</v>
       </c>
@@ -1785,7 +1825,7 @@
         <v>7</v>
       </c>
       <c r="F11" s="9">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G11" s="11">
         <v>160</v>
@@ -1823,7 +1863,9 @@
       <c r="C12" s="9">
         <v>1</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="E12" s="9">
         <v>8</v>
       </c>
@@ -1843,7 +1885,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" s="9">
         <v>192600</v>
@@ -1886,7 +1928,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="9">
         <v>269100</v>
@@ -1914,7 +1956,7 @@
         <v>10</v>
       </c>
       <c r="F14" s="9">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G14" s="11">
         <v>190</v>
@@ -1929,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="K14" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="9">
         <v>363500</v>
@@ -1952,7 +1994,9 @@
       <c r="C15" s="9">
         <v>1</v>
       </c>
-      <c r="D15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="E15" s="9">
         <v>11</v>
       </c>
@@ -1972,7 +2016,7 @@
         <v>2</v>
       </c>
       <c r="K15" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="9">
         <v>477700</v>
@@ -2000,7 +2044,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="9">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G16" s="11">
         <v>210</v>
@@ -2015,7 +2059,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" s="9">
         <v>613600</v>
@@ -2038,7 +2082,9 @@
       <c r="C17" s="9">
         <v>1</v>
       </c>
-      <c r="D17" s="9"/>
+      <c r="D17" s="9" t="s">
+        <v>34</v>
+      </c>
       <c r="E17" s="9">
         <v>13</v>
       </c>
@@ -2058,7 +2104,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="9">
         <v>773100</v>
@@ -2101,7 +2147,7 @@
         <v>2</v>
       </c>
       <c r="K18" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" s="9">
         <v>958100</v>
@@ -2124,12 +2170,14 @@
       <c r="C19" s="9">
         <v>1</v>
       </c>
-      <c r="D19" s="9"/>
+      <c r="D19" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="E19" s="9">
         <v>15</v>
       </c>
       <c r="F19" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G19" s="11">
         <v>240</v>
@@ -2144,7 +2192,7 @@
         <v>2</v>
       </c>
       <c r="K19" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="9">
         <v>1170500</v>
@@ -2172,7 +2220,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G20" s="11">
         <v>250</v>
@@ -2187,7 +2235,7 @@
         <v>2</v>
       </c>
       <c r="K20" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="9">
         <v>1412100</v>
@@ -2210,12 +2258,14 @@
       <c r="C21" s="9">
         <v>1</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="E21" s="9">
         <v>17</v>
       </c>
       <c r="F21" s="9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G21" s="11">
         <v>260</v>
@@ -2230,7 +2280,7 @@
         <v>2</v>
       </c>
       <c r="K21" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9">
         <v>1684900</v>
@@ -2258,7 +2308,7 @@
         <v>18</v>
       </c>
       <c r="F22" s="9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G22" s="11">
         <v>270</v>
@@ -2273,7 +2323,7 @@
         <v>2</v>
       </c>
       <c r="K22" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="9">
         <v>1990700</v>
@@ -2296,12 +2346,14 @@
       <c r="C23" s="9">
         <v>1</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="E23" s="9">
         <v>19</v>
       </c>
       <c r="F23" s="9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G23" s="11">
         <v>280</v>
@@ -2316,7 +2368,7 @@
         <v>2</v>
       </c>
       <c r="K23" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" s="9">
         <v>2331500</v>
@@ -2344,7 +2396,7 @@
         <v>20</v>
       </c>
       <c r="F24" s="9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G24" s="11">
         <v>290</v>
@@ -2359,7 +2411,7 @@
         <v>2</v>
       </c>
       <c r="K24" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" s="9">
         <v>2709100</v>
@@ -2382,12 +2434,14 @@
       <c r="C25" s="9">
         <v>1</v>
       </c>
-      <c r="D25" s="9"/>
+      <c r="D25" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="E25" s="9">
         <v>21</v>
       </c>
       <c r="F25" s="9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G25" s="11">
         <v>300</v>
@@ -2402,7 +2456,7 @@
         <v>2</v>
       </c>
       <c r="K25" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="9">
         <v>3125400</v>
@@ -2430,7 +2484,7 @@
         <v>22</v>
       </c>
       <c r="F26" s="9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G26" s="11">
         <v>310</v>
@@ -2445,7 +2499,7 @@
         <v>2</v>
       </c>
       <c r="K26" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="9">
         <v>3582300</v>
@@ -2468,12 +2522,14 @@
       <c r="C27" s="9">
         <v>1</v>
       </c>
-      <c r="D27" s="9"/>
+      <c r="D27" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="E27" s="9">
         <v>23</v>
       </c>
       <c r="F27" s="9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G27" s="11">
         <v>320</v>
@@ -2488,7 +2544,7 @@
         <v>2</v>
       </c>
       <c r="K27" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="9">
         <v>4081600</v>
@@ -2516,7 +2572,7 @@
         <v>24</v>
       </c>
       <c r="F28" s="9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G28" s="11">
         <v>330</v>
@@ -2528,10 +2584,10 @@
         <v>5</v>
       </c>
       <c r="J28" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K28" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="9">
         <v>4625300</v>
@@ -2554,12 +2610,14 @@
       <c r="C29" s="9">
         <v>1</v>
       </c>
-      <c r="D29" s="9"/>
+      <c r="D29" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="E29" s="9">
         <v>25</v>
       </c>
       <c r="F29" s="9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G29" s="11">
         <v>340</v>
@@ -2571,7 +2629,7 @@
         <v>5</v>
       </c>
       <c r="J29" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K29" s="9">
         <v>1</v>
@@ -2602,7 +2660,7 @@
         <v>26</v>
       </c>
       <c r="F30" s="9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G30" s="11">
         <v>350</v>
@@ -2614,7 +2672,7 @@
         <v>5</v>
       </c>
       <c r="J30" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K30" s="9">
         <v>1</v>
@@ -2640,12 +2698,14 @@
       <c r="C31" s="9">
         <v>1</v>
       </c>
-      <c r="D31" s="9"/>
+      <c r="D31" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="E31" s="9">
         <v>27</v>
       </c>
       <c r="F31" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G31" s="11">
         <v>360</v>
@@ -2657,7 +2717,7 @@
         <v>5</v>
       </c>
       <c r="J31" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K31" s="9">
         <v>1</v>
@@ -2688,7 +2748,7 @@
         <v>28</v>
       </c>
       <c r="F32" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G32" s="11">
         <v>370</v>
@@ -2700,7 +2760,7 @@
         <v>5</v>
       </c>
       <c r="J32" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K32" s="9">
         <v>1</v>
@@ -2731,7 +2791,7 @@
         <v>29</v>
       </c>
       <c r="F33" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G33" s="11">
         <v>380</v>
@@ -2743,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="J33" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K33" s="9">
         <v>1</v>
@@ -2774,7 +2834,7 @@
         <v>30</v>
       </c>
       <c r="F34" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G34" s="11">
         <v>390</v>
@@ -2786,7 +2846,7 @@
         <v>5</v>
       </c>
       <c r="J34" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K34" s="9">
         <v>1</v>
@@ -2817,7 +2877,7 @@
         <v>31</v>
       </c>
       <c r="F35" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G35" s="11">
         <v>400</v>
@@ -2829,7 +2889,7 @@
         <v>5</v>
       </c>
       <c r="J35" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K35" s="9">
         <v>1</v>
@@ -2860,7 +2920,7 @@
         <v>32</v>
       </c>
       <c r="F36" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G36" s="11">
         <v>410</v>
@@ -2872,7 +2932,7 @@
         <v>5</v>
       </c>
       <c r="J36" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K36" s="9">
         <v>1</v>
@@ -2903,7 +2963,7 @@
         <v>33</v>
       </c>
       <c r="F37" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G37" s="11">
         <v>420</v>
@@ -2915,7 +2975,7 @@
         <v>5</v>
       </c>
       <c r="J37" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K37" s="9">
         <v>1</v>
@@ -2946,7 +3006,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G38" s="11">
         <v>430</v>
@@ -2958,7 +3018,7 @@
         <v>5</v>
       </c>
       <c r="J38" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K38" s="9">
         <v>1</v>
@@ -2989,7 +3049,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G39" s="11">
         <v>440</v>
@@ -3001,7 +3061,7 @@
         <v>5</v>
       </c>
       <c r="J39" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K39" s="9">
         <v>1</v>
@@ -3032,7 +3092,7 @@
         <v>36</v>
       </c>
       <c r="F40" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G40" s="11">
         <v>450</v>
@@ -3044,7 +3104,7 @@
         <v>5</v>
       </c>
       <c r="J40" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K40" s="9">
         <v>1</v>
@@ -3075,7 +3135,7 @@
         <v>37</v>
       </c>
       <c r="F41" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G41" s="11">
         <v>460</v>
@@ -3087,7 +3147,7 @@
         <v>5</v>
       </c>
       <c r="J41" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K41" s="9">
         <v>1</v>
@@ -3118,7 +3178,7 @@
         <v>38</v>
       </c>
       <c r="F42" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G42" s="11">
         <v>470</v>
@@ -3130,7 +3190,7 @@
         <v>5</v>
       </c>
       <c r="J42" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K42" s="9">
         <v>1</v>
@@ -3161,7 +3221,7 @@
         <v>39</v>
       </c>
       <c r="F43" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G43" s="11">
         <v>480</v>
@@ -3173,7 +3233,7 @@
         <v>5</v>
       </c>
       <c r="J43" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K43" s="9">
         <v>1</v>
@@ -3204,7 +3264,7 @@
         <v>40</v>
       </c>
       <c r="F44" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G44" s="11">
         <v>490</v>
@@ -3216,7 +3276,7 @@
         <v>5</v>
       </c>
       <c r="J44" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K44" s="9">
         <v>1</v>
@@ -3247,7 +3307,7 @@
         <v>41</v>
       </c>
       <c r="F45" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G45" s="11">
         <v>500</v>
@@ -3259,7 +3319,7 @@
         <v>5</v>
       </c>
       <c r="J45" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K45" s="9">
         <v>1</v>
@@ -3290,7 +3350,7 @@
         <v>42</v>
       </c>
       <c r="F46" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G46" s="11">
         <v>510</v>
@@ -3302,7 +3362,7 @@
         <v>5</v>
       </c>
       <c r="J46" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K46" s="9">
         <v>1</v>
@@ -3333,7 +3393,7 @@
         <v>43</v>
       </c>
       <c r="F47" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G47" s="11">
         <v>520</v>
@@ -3345,7 +3405,7 @@
         <v>5</v>
       </c>
       <c r="J47" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K47" s="9">
         <v>1</v>
@@ -3376,7 +3436,7 @@
         <v>44</v>
       </c>
       <c r="F48" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G48" s="11">
         <v>530</v>
@@ -3388,7 +3448,7 @@
         <v>5</v>
       </c>
       <c r="J48" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K48" s="9">
         <v>1</v>
@@ -3419,7 +3479,7 @@
         <v>45</v>
       </c>
       <c r="F49" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G49" s="11">
         <v>540</v>
@@ -3431,7 +3491,7 @@
         <v>5</v>
       </c>
       <c r="J49" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K49" s="9">
         <v>1</v>
@@ -3462,7 +3522,7 @@
         <v>46</v>
       </c>
       <c r="F50" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G50" s="11">
         <v>550</v>
@@ -3474,7 +3534,7 @@
         <v>5</v>
       </c>
       <c r="J50" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K50" s="9">
         <v>1</v>
@@ -3505,7 +3565,7 @@
         <v>47</v>
       </c>
       <c r="F51" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G51" s="11">
         <v>560</v>
@@ -3517,7 +3577,7 @@
         <v>5</v>
       </c>
       <c r="J51" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K51" s="9">
         <v>1</v>
@@ -3548,7 +3608,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G52" s="11">
         <v>570</v>
@@ -3560,7 +3620,7 @@
         <v>5</v>
       </c>
       <c r="J52" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K52" s="9">
         <v>1</v>
@@ -3591,7 +3651,7 @@
         <v>49</v>
       </c>
       <c r="F53" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G53" s="11">
         <v>580</v>
@@ -3603,7 +3663,7 @@
         <v>5</v>
       </c>
       <c r="J53" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K53" s="9">
         <v>1</v>
@@ -3634,7 +3694,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G54" s="11">
         <v>590</v>
@@ -3646,7 +3706,7 @@
         <v>5</v>
       </c>
       <c r="J54" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K54" s="9">
         <v>1</v>
@@ -3677,7 +3737,7 @@
         <v>51</v>
       </c>
       <c r="F55" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G55" s="11">
         <v>600</v>
@@ -3689,7 +3749,7 @@
         <v>5</v>
       </c>
       <c r="J55" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K55" s="9">
         <v>1</v>
@@ -3720,7 +3780,7 @@
         <v>52</v>
       </c>
       <c r="F56" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G56" s="11">
         <v>610</v>
@@ -3732,7 +3792,7 @@
         <v>5</v>
       </c>
       <c r="J56" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K56" s="9">
         <v>1</v>
@@ -3763,7 +3823,7 @@
         <v>53</v>
       </c>
       <c r="F57" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G57" s="11">
         <v>620</v>
@@ -3775,7 +3835,7 @@
         <v>5</v>
       </c>
       <c r="J57" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K57" s="9">
         <v>1</v>
@@ -3806,7 +3866,7 @@
         <v>54</v>
       </c>
       <c r="F58" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G58" s="11">
         <v>630</v>
@@ -3818,7 +3878,7 @@
         <v>5</v>
       </c>
       <c r="J58" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K58" s="9">
         <v>1</v>
@@ -3849,7 +3909,7 @@
         <v>55</v>
       </c>
       <c r="F59" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G59" s="11">
         <v>640</v>
@@ -3861,7 +3921,7 @@
         <v>5</v>
       </c>
       <c r="J59" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K59" s="9">
         <v>1</v>
@@ -3892,7 +3952,7 @@
         <v>56</v>
       </c>
       <c r="F60" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G60" s="11">
         <v>650</v>
@@ -3904,7 +3964,7 @@
         <v>5</v>
       </c>
       <c r="J60" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K60" s="9">
         <v>1</v>
@@ -3935,7 +3995,7 @@
         <v>57</v>
       </c>
       <c r="F61" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G61" s="11">
         <v>660</v>
@@ -3947,7 +4007,7 @@
         <v>5</v>
       </c>
       <c r="J61" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K61" s="9">
         <v>1</v>
@@ -3978,7 +4038,7 @@
         <v>58</v>
       </c>
       <c r="F62" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G62" s="11">
         <v>670</v>
@@ -3990,7 +4050,7 @@
         <v>5</v>
       </c>
       <c r="J62" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K62" s="9">
         <v>1</v>
@@ -4021,7 +4081,7 @@
         <v>59</v>
       </c>
       <c r="F63" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G63" s="11">
         <v>680</v>
@@ -4033,7 +4093,7 @@
         <v>5</v>
       </c>
       <c r="J63" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K63" s="9">
         <v>1</v>
@@ -4064,7 +4124,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G64" s="11">
         <v>690</v>
@@ -4076,7 +4136,7 @@
         <v>5</v>
       </c>
       <c r="J64" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K64" s="9">
         <v>1</v>
@@ -4224,7 +4284,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -4245,7 +4305,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -4266,7 +4326,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -4287,7 +4347,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -4308,7 +4368,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -4329,7 +4389,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -4350,7 +4410,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -4371,7 +4431,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4392,7 +4452,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4413,7 +4473,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4434,7 +4494,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4455,7 +4515,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4476,7 +4536,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4497,251 +4557,251 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B21" s="1"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B22" s="1"/>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B23" s="1"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B24" s="1"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B26" s="1"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B27" s="1"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B28" s="1"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B29" s="1"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B30" s="1"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B31" s="1"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B33" s="1"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B34" s="1"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B35" s="1"/>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B36" s="1"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B37" s="1"/>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B38" s="1"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B39" s="1"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B47" s="1"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B49" s="1"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B50" s="1"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B53" s="1"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B54" s="1"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B55" s="1"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B56" s="1"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -544,12 +544,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1575,10 +1575,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="9">
         <v>900</v>
@@ -1618,10 +1618,10 @@
         <v>5</v>
       </c>
       <c r="J6" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="9">
         <v>4700</v>
@@ -1661,10 +1661,10 @@
         <v>5</v>
       </c>
       <c r="J7" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="9">
         <v>13200</v>
@@ -1706,10 +1706,10 @@
         <v>5</v>
       </c>
       <c r="J8" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="9">
         <v>28300</v>
@@ -1751,10 +1751,10 @@
         <v>5</v>
       </c>
       <c r="J9" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="9">
         <v>51900</v>
@@ -1794,10 +1794,10 @@
         <v>5</v>
       </c>
       <c r="J10" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="9">
         <v>85900</v>
@@ -1837,10 +1837,10 @@
         <v>5</v>
       </c>
       <c r="J11" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="9">
         <v>132200</v>
@@ -1882,10 +1882,10 @@
         <v>5</v>
       </c>
       <c r="J12" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="9">
         <v>192600</v>
@@ -1925,10 +1925,10 @@
         <v>5</v>
       </c>
       <c r="J13" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="9">
         <v>269100</v>
@@ -1968,10 +1968,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="9">
         <v>363500</v>
@@ -2013,10 +2013,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="9">
         <v>477700</v>
@@ -2056,10 +2056,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="9">
         <v>613600</v>
@@ -2101,10 +2101,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9">
         <v>773100</v>
@@ -2144,10 +2144,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="9">
         <v>958100</v>
@@ -2189,10 +2189,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="9">
         <v>1170500</v>
@@ -2232,10 +2232,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="9">
         <v>1412100</v>
@@ -2277,10 +2277,10 @@
         <v>5</v>
       </c>
       <c r="J21" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="9">
         <v>1684900</v>
@@ -2320,10 +2320,10 @@
         <v>5</v>
       </c>
       <c r="J22" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="9">
         <v>1990700</v>
@@ -2365,10 +2365,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="9">
         <v>2331500</v>
@@ -2408,10 +2408,10 @@
         <v>5</v>
       </c>
       <c r="J24" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="9">
         <v>2709100</v>
@@ -2453,10 +2453,10 @@
         <v>5</v>
       </c>
       <c r="J25" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="9">
         <v>3125400</v>
@@ -2496,10 +2496,10 @@
         <v>5</v>
       </c>
       <c r="J26" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="9">
         <v>3582300</v>
@@ -2541,10 +2541,10 @@
         <v>5</v>
       </c>
       <c r="J27" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="9">
         <v>4081600</v>
@@ -2584,10 +2584,10 @@
         <v>5</v>
       </c>
       <c r="J28" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="9">
         <v>4625300</v>
@@ -2629,10 +2629,10 @@
         <v>5</v>
       </c>
       <c r="J29" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="9">
         <v>5215300</v>
@@ -2672,10 +2672,10 @@
         <v>5</v>
       </c>
       <c r="J30" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="9">
         <v>5853400</v>
@@ -2717,10 +2717,10 @@
         <v>5</v>
       </c>
       <c r="J31" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="9">
         <v>6541500</v>
@@ -2760,10 +2760,10 @@
         <v>5</v>
       </c>
       <c r="J32" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="9">
         <v>7281500</v>
@@ -2803,10 +2803,10 @@
         <v>5</v>
       </c>
       <c r="J33" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="9">
         <v>8075400</v>
@@ -2846,10 +2846,10 @@
         <v>5</v>
       </c>
       <c r="J34" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="9">
         <v>8924900</v>
@@ -2889,10 +2889,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="9">
         <v>9832000</v>
@@ -2932,10 +2932,10 @@
         <v>5</v>
       </c>
       <c r="J36" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="9">
         <v>10798600</v>
@@ -2975,10 +2975,10 @@
         <v>5</v>
       </c>
       <c r="J37" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="9">
         <v>11826500</v>
@@ -3018,10 +3018,10 @@
         <v>5</v>
       </c>
       <c r="J38" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" s="9">
         <v>12917700</v>
@@ -3061,10 +3061,10 @@
         <v>5</v>
       </c>
       <c r="J39" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="9">
         <v>14074000</v>
@@ -3104,10 +3104,10 @@
         <v>5</v>
       </c>
       <c r="J40" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="9">
         <v>15297300</v>
@@ -3147,10 +3147,10 @@
         <v>5</v>
       </c>
       <c r="J41" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="9">
         <v>16589600</v>
@@ -3190,10 +3190,10 @@
         <v>5</v>
       </c>
       <c r="J42" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="9">
         <v>17952600</v>
@@ -3233,10 +3233,10 @@
         <v>5</v>
       </c>
       <c r="J43" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" s="9">
         <v>19388300</v>
@@ -3276,10 +3276,10 @@
         <v>5</v>
       </c>
       <c r="J44" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="9">
         <v>20898600</v>
@@ -3319,10 +3319,10 @@
         <v>5</v>
       </c>
       <c r="J45" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="9">
         <v>22485400</v>
@@ -3362,10 +3362,10 @@
         <v>5</v>
       </c>
       <c r="J46" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="9">
         <v>24150500</v>
@@ -3405,10 +3405,10 @@
         <v>5</v>
       </c>
       <c r="J47" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="9">
         <v>25895800</v>
@@ -3448,10 +3448,10 @@
         <v>5</v>
       </c>
       <c r="J48" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="9">
         <v>27723300</v>
@@ -3491,10 +3491,10 @@
         <v>5</v>
       </c>
       <c r="J49" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="9">
         <v>29634800</v>
@@ -3534,10 +3534,10 @@
         <v>5</v>
       </c>
       <c r="J50" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="9">
         <v>31632200</v>
@@ -3577,10 +3577,10 @@
         <v>5</v>
       </c>
       <c r="J51" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" s="9">
         <v>33717400</v>
@@ -3620,10 +3620,10 @@
         <v>5</v>
       </c>
       <c r="J52" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K52" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="9">
         <v>35892200</v>
@@ -3663,10 +3663,10 @@
         <v>5</v>
       </c>
       <c r="J53" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="9">
         <v>38158600</v>
@@ -3706,10 +3706,10 @@
         <v>5</v>
       </c>
       <c r="J54" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="9">
         <v>40518400</v>
@@ -3749,10 +3749,10 @@
         <v>5</v>
       </c>
       <c r="J55" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="9">
         <v>42973600</v>
@@ -3792,10 +3792,10 @@
         <v>5</v>
       </c>
       <c r="J56" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" s="9">
         <v>45526000</v>
@@ -3835,10 +3835,10 @@
         <v>5</v>
       </c>
       <c r="J57" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="9">
         <v>48177500</v>
@@ -3878,10 +3878,10 @@
         <v>5</v>
       </c>
       <c r="J58" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="9">
         <v>50930000</v>
@@ -3921,10 +3921,10 @@
         <v>5</v>
       </c>
       <c r="J59" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="9">
         <v>53785400</v>
@@ -3964,10 +3964,10 @@
         <v>5</v>
       </c>
       <c r="J60" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K60" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="9">
         <v>56745600</v>
@@ -4007,10 +4007,10 @@
         <v>5</v>
       </c>
       <c r="J61" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61" s="9">
         <v>59812500</v>
@@ -4050,10 +4050,10 @@
         <v>5</v>
       </c>
       <c r="J62" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="9">
         <v>62987900</v>
@@ -4093,10 +4093,10 @@
         <v>5</v>
       </c>
       <c r="J63" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K63" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="9">
         <v>66273800</v>
@@ -4136,10 +4136,10 @@
         <v>5</v>
       </c>
       <c r="J64" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="9">
         <v>999999999</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -1994,14 +1994,12 @@
       <c r="C15" s="9">
         <v>1</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="D15" s="9"/>
       <c r="E15" s="9">
         <v>11</v>
       </c>
       <c r="F15" s="9">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G15" s="11">
         <v>200</v>
@@ -2039,12 +2037,14 @@
       <c r="C16" s="9">
         <v>1</v>
       </c>
-      <c r="D16" s="9"/>
+      <c r="D16" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="E16" s="9">
         <v>12</v>
       </c>
       <c r="F16" s="9">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G16" s="11">
         <v>210</v>
@@ -2082,14 +2082,12 @@
       <c r="C17" s="9">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>34</v>
-      </c>
+      <c r="D17" s="9"/>
       <c r="E17" s="9">
         <v>13</v>
       </c>
       <c r="F17" s="9">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="G17" s="11">
         <v>220</v>
@@ -2132,7 +2130,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="9">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="G18" s="11">
         <v>230</v>
@@ -2170,14 +2168,12 @@
       <c r="C19" s="9">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>35</v>
-      </c>
+      <c r="D19" s="9"/>
       <c r="E19" s="9">
         <v>15</v>
       </c>
       <c r="F19" s="9">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="G19" s="11">
         <v>240</v>
@@ -2215,12 +2211,14 @@
       <c r="C20" s="9">
         <v>1</v>
       </c>
-      <c r="D20" s="9"/>
+      <c r="D20" s="9" t="s">
+        <v>34</v>
+      </c>
       <c r="E20" s="9">
         <v>16</v>
       </c>
       <c r="F20" s="9">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G20" s="11">
         <v>250</v>
@@ -2258,14 +2256,12 @@
       <c r="C21" s="9">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="D21" s="9"/>
       <c r="E21" s="9">
         <v>17</v>
       </c>
       <c r="F21" s="9">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="G21" s="11">
         <v>260</v>
@@ -2308,7 +2304,7 @@
         <v>18</v>
       </c>
       <c r="F22" s="9">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="G22" s="11">
         <v>270</v>
@@ -2346,14 +2342,12 @@
       <c r="C23" s="9">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="D23" s="9"/>
       <c r="E23" s="9">
         <v>19</v>
       </c>
       <c r="F23" s="9">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="G23" s="11">
         <v>280</v>
@@ -2391,12 +2385,14 @@
       <c r="C24" s="9">
         <v>1</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="E24" s="9">
         <v>20</v>
       </c>
       <c r="F24" s="9">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G24" s="11">
         <v>290</v>
@@ -2434,14 +2430,12 @@
       <c r="C25" s="9">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>38</v>
-      </c>
+      <c r="D25" s="9"/>
       <c r="E25" s="9">
         <v>21</v>
       </c>
       <c r="F25" s="9">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G25" s="11">
         <v>300</v>
@@ -2484,7 +2478,7 @@
         <v>22</v>
       </c>
       <c r="F26" s="9">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G26" s="11">
         <v>310</v>
@@ -2522,14 +2516,12 @@
       <c r="C27" s="9">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>39</v>
-      </c>
+      <c r="D27" s="9"/>
       <c r="E27" s="9">
         <v>23</v>
       </c>
       <c r="F27" s="9">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G27" s="11">
         <v>320</v>
@@ -2567,12 +2559,14 @@
       <c r="C28" s="9">
         <v>1</v>
       </c>
-      <c r="D28" s="9"/>
+      <c r="D28" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="E28" s="9">
         <v>24</v>
       </c>
       <c r="F28" s="9">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G28" s="11">
         <v>330</v>
@@ -2610,14 +2604,12 @@
       <c r="C29" s="9">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="D29" s="9"/>
       <c r="E29" s="9">
         <v>25</v>
       </c>
       <c r="F29" s="9">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G29" s="11">
         <v>340</v>
@@ -2660,7 +2652,7 @@
         <v>26</v>
       </c>
       <c r="F30" s="9">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G30" s="11">
         <v>350</v>
@@ -2698,14 +2690,12 @@
       <c r="C31" s="9">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>41</v>
-      </c>
+      <c r="D31" s="9"/>
       <c r="E31" s="9">
         <v>27</v>
       </c>
       <c r="F31" s="9">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G31" s="11">
         <v>360</v>
@@ -2743,12 +2733,14 @@
       <c r="C32" s="9">
         <v>1</v>
       </c>
-      <c r="D32" s="9"/>
+      <c r="D32" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="E32" s="9">
         <v>28</v>
       </c>
       <c r="F32" s="9">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G32" s="11">
         <v>370</v>
@@ -2791,7 +2783,7 @@
         <v>29</v>
       </c>
       <c r="F33" s="9">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G33" s="11">
         <v>380</v>
@@ -2834,7 +2826,7 @@
         <v>30</v>
       </c>
       <c r="F34" s="9">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G34" s="11">
         <v>390</v>
@@ -2877,7 +2869,7 @@
         <v>31</v>
       </c>
       <c r="F35" s="9">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G35" s="11">
         <v>400</v>
@@ -2915,12 +2907,14 @@
       <c r="C36" s="9">
         <v>1</v>
       </c>
-      <c r="D36" s="9"/>
+      <c r="D36" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="E36" s="9">
         <v>32</v>
       </c>
       <c r="F36" s="9">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G36" s="11">
         <v>410</v>
@@ -2963,7 +2957,7 @@
         <v>33</v>
       </c>
       <c r="F37" s="9">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G37" s="11">
         <v>420</v>
@@ -3006,7 +3000,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="9">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G38" s="11">
         <v>430</v>
@@ -3049,7 +3043,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="9">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G39" s="11">
         <v>440</v>
@@ -3087,12 +3081,14 @@
       <c r="C40" s="9">
         <v>1</v>
       </c>
-      <c r="D40" s="9"/>
+      <c r="D40" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="E40" s="9">
         <v>36</v>
       </c>
       <c r="F40" s="9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G40" s="11">
         <v>450</v>
@@ -3135,7 +3131,7 @@
         <v>37</v>
       </c>
       <c r="F41" s="9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G41" s="11">
         <v>460</v>
@@ -3178,7 +3174,7 @@
         <v>38</v>
       </c>
       <c r="F42" s="9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G42" s="11">
         <v>470</v>
@@ -3221,7 +3217,7 @@
         <v>39</v>
       </c>
       <c r="F43" s="9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G43" s="11">
         <v>480</v>
@@ -3259,12 +3255,14 @@
       <c r="C44" s="9">
         <v>1</v>
       </c>
-      <c r="D44" s="9"/>
+      <c r="D44" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="E44" s="9">
         <v>40</v>
       </c>
       <c r="F44" s="9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G44" s="11">
         <v>490</v>
@@ -3307,7 +3305,7 @@
         <v>41</v>
       </c>
       <c r="F45" s="9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G45" s="11">
         <v>500</v>
@@ -3350,7 +3348,7 @@
         <v>42</v>
       </c>
       <c r="F46" s="9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G46" s="11">
         <v>510</v>
@@ -3393,7 +3391,7 @@
         <v>43</v>
       </c>
       <c r="F47" s="9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G47" s="11">
         <v>520</v>
@@ -3431,7 +3429,9 @@
       <c r="C48" s="9">
         <v>1</v>
       </c>
-      <c r="D48" s="9"/>
+      <c r="D48" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="E48" s="9">
         <v>44</v>
       </c>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -544,12 +544,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1575,10 +1575,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="9">
         <v>900</v>
@@ -1618,10 +1618,10 @@
         <v>5</v>
       </c>
       <c r="J6" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="9">
         <v>4700</v>
@@ -1661,10 +1661,10 @@
         <v>5</v>
       </c>
       <c r="J7" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="9">
         <v>13200</v>
@@ -1706,10 +1706,10 @@
         <v>5</v>
       </c>
       <c r="J8" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="9">
         <v>28300</v>
@@ -1751,10 +1751,10 @@
         <v>5</v>
       </c>
       <c r="J9" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" s="9">
         <v>51900</v>
@@ -1794,10 +1794,10 @@
         <v>5</v>
       </c>
       <c r="J10" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" s="9">
         <v>85900</v>
@@ -1837,10 +1837,10 @@
         <v>5</v>
       </c>
       <c r="J11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" s="9">
         <v>132200</v>
@@ -1882,10 +1882,10 @@
         <v>5</v>
       </c>
       <c r="J12" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" s="9">
         <v>192600</v>
@@ -1925,10 +1925,10 @@
         <v>5</v>
       </c>
       <c r="J13" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="9">
         <v>269100</v>
@@ -1968,10 +1968,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="9">
         <v>363500</v>
@@ -2011,10 +2011,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="9">
         <v>477700</v>
@@ -2056,10 +2056,10 @@
         <v>5</v>
       </c>
       <c r="J16" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" s="9">
         <v>613600</v>
@@ -2099,10 +2099,10 @@
         <v>5</v>
       </c>
       <c r="J17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="9">
         <v>773100</v>
@@ -2142,10 +2142,10 @@
         <v>5</v>
       </c>
       <c r="J18" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" s="9">
         <v>958100</v>
@@ -2185,10 +2185,10 @@
         <v>5</v>
       </c>
       <c r="J19" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="9">
         <v>1170500</v>
@@ -2230,10 +2230,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="9">
         <v>1412100</v>
@@ -2273,10 +2273,10 @@
         <v>5</v>
       </c>
       <c r="J21" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9">
         <v>1684900</v>
@@ -2316,10 +2316,10 @@
         <v>5</v>
       </c>
       <c r="J22" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="9">
         <v>1990700</v>
@@ -2359,10 +2359,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" s="9">
         <v>2331500</v>
@@ -2404,10 +2404,10 @@
         <v>5</v>
       </c>
       <c r="J24" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" s="9">
         <v>2709100</v>
@@ -2447,10 +2447,10 @@
         <v>5</v>
       </c>
       <c r="J25" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K25" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="9">
         <v>3125400</v>
@@ -2490,10 +2490,10 @@
         <v>5</v>
       </c>
       <c r="J26" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="9">
         <v>3582300</v>
@@ -2533,10 +2533,10 @@
         <v>5</v>
       </c>
       <c r="J27" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="9">
         <v>4081600</v>
@@ -2578,10 +2578,10 @@
         <v>5</v>
       </c>
       <c r="J28" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K28" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="9">
         <v>4625300</v>
@@ -2621,10 +2621,10 @@
         <v>5</v>
       </c>
       <c r="J29" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="9">
         <v>5215300</v>
@@ -2664,10 +2664,10 @@
         <v>5</v>
       </c>
       <c r="J30" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K30" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="9">
         <v>5853400</v>
@@ -2707,10 +2707,10 @@
         <v>5</v>
       </c>
       <c r="J31" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" s="9">
         <v>6541500</v>
@@ -2752,10 +2752,10 @@
         <v>5</v>
       </c>
       <c r="J32" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K32" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="9">
         <v>7281500</v>
@@ -2795,10 +2795,10 @@
         <v>5</v>
       </c>
       <c r="J33" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="9">
         <v>8075400</v>
@@ -2838,10 +2838,10 @@
         <v>5</v>
       </c>
       <c r="J34" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="9">
         <v>8924900</v>
@@ -2881,10 +2881,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" s="9">
         <v>9832000</v>
@@ -2926,10 +2926,10 @@
         <v>5</v>
       </c>
       <c r="J36" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" s="9">
         <v>10798600</v>
@@ -2969,10 +2969,10 @@
         <v>5</v>
       </c>
       <c r="J37" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37" s="9">
         <v>11826500</v>
@@ -3012,10 +3012,10 @@
         <v>5</v>
       </c>
       <c r="J38" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" s="9">
         <v>12917700</v>
@@ -3055,10 +3055,10 @@
         <v>5</v>
       </c>
       <c r="J39" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="9">
         <v>14074000</v>
@@ -3100,10 +3100,10 @@
         <v>5</v>
       </c>
       <c r="J40" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" s="9">
         <v>15297300</v>
@@ -3143,10 +3143,10 @@
         <v>5</v>
       </c>
       <c r="J41" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" s="9">
         <v>16589600</v>
@@ -3186,10 +3186,10 @@
         <v>5</v>
       </c>
       <c r="J42" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K42" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="9">
         <v>17952600</v>
@@ -3229,10 +3229,10 @@
         <v>5</v>
       </c>
       <c r="J43" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K43" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" s="9">
         <v>19388300</v>
@@ -3274,10 +3274,10 @@
         <v>5</v>
       </c>
       <c r="J44" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K44" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="9">
         <v>20898600</v>
@@ -3317,10 +3317,10 @@
         <v>5</v>
       </c>
       <c r="J45" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="9">
         <v>22485400</v>
@@ -3360,10 +3360,10 @@
         <v>5</v>
       </c>
       <c r="J46" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K46" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" s="9">
         <v>24150500</v>
@@ -3403,10 +3403,10 @@
         <v>5</v>
       </c>
       <c r="J47" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K47" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="9">
         <v>25895800</v>
@@ -3448,10 +3448,10 @@
         <v>5</v>
       </c>
       <c r="J48" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K48" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="9">
         <v>27723300</v>
@@ -3491,10 +3491,10 @@
         <v>5</v>
       </c>
       <c r="J49" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K49" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="9">
         <v>29634800</v>
@@ -3534,10 +3534,10 @@
         <v>5</v>
       </c>
       <c r="J50" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" s="9">
         <v>31632200</v>
@@ -3577,10 +3577,10 @@
         <v>5</v>
       </c>
       <c r="J51" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L51" s="9">
         <v>33717400</v>
@@ -3620,10 +3620,10 @@
         <v>5</v>
       </c>
       <c r="J52" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K52" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52" s="9">
         <v>35892200</v>
@@ -3663,10 +3663,10 @@
         <v>5</v>
       </c>
       <c r="J53" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="9">
         <v>38158600</v>
@@ -3706,10 +3706,10 @@
         <v>5</v>
       </c>
       <c r="J54" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="9">
         <v>40518400</v>
@@ -3749,10 +3749,10 @@
         <v>5</v>
       </c>
       <c r="J55" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="9">
         <v>42973600</v>
@@ -3792,10 +3792,10 @@
         <v>5</v>
       </c>
       <c r="J56" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K56" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56" s="9">
         <v>45526000</v>
@@ -3835,10 +3835,10 @@
         <v>5</v>
       </c>
       <c r="J57" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="9">
         <v>48177500</v>
@@ -3878,10 +3878,10 @@
         <v>5</v>
       </c>
       <c r="J58" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K58" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L58" s="9">
         <v>50930000</v>
@@ -3921,10 +3921,10 @@
         <v>5</v>
       </c>
       <c r="J59" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K59" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" s="9">
         <v>53785400</v>
@@ -3964,10 +3964,10 @@
         <v>5</v>
       </c>
       <c r="J60" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K60" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="9">
         <v>56745600</v>
@@ -4007,10 +4007,10 @@
         <v>5</v>
       </c>
       <c r="J61" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K61" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L61" s="9">
         <v>59812500</v>
@@ -4050,10 +4050,10 @@
         <v>5</v>
       </c>
       <c r="J62" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" s="9">
         <v>62987900</v>
@@ -4093,10 +4093,10 @@
         <v>5</v>
       </c>
       <c r="J63" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L63" s="9">
         <v>66273800</v>
@@ -4136,10 +4136,10 @@
         <v>5</v>
       </c>
       <c r="J64" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K64" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" s="9">
         <v>999999999</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -248,6 +248,9 @@
     <t>离线收益时长（分）</t>
   </si>
   <si>
+    <t>预估建筑达成等级</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -296,13 +299,31 @@
     <t>OfflineDuration</t>
   </si>
   <si>
+    <t>ExpectedBuildingLevel</t>
+  </si>
+  <si>
     <t>拉斯维加斯</t>
   </si>
   <si>
+    <t>1301_1|1101_1</t>
+  </si>
+  <si>
+    <t>1301_3|1101_2|1102_2</t>
+  </si>
+  <si>
     <t>1102_1</t>
   </si>
   <si>
+    <t>1301_3|1101_3|1102_3</t>
+  </si>
+  <si>
     <t>1202_1|1303_1|1304_1</t>
+  </si>
+  <si>
+    <t>1301_4|1101_4|1102_4|1202_3</t>
+  </si>
+  <si>
+    <t>1301_5|1101_5|1102_5|1202_4</t>
   </si>
   <si>
     <t>1110_1</t>
@@ -557,12 +578,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1403,7 +1424,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -1419,10 +1440,11 @@
     <col min="13" max="13" width="29.75" style="3" customWidth="1"/>
     <col min="14" max="14" width="18.5" style="3" customWidth="1"/>
     <col min="15" max="15" width="18.75" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="15.625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="30" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="15.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" customHeight="1" spans="1:15">
+    <row r="1" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1468,98 +1490,107 @@
       <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:15">
+        <v>16</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:15">
+        <v>31</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:16">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1576,13 +1607,13 @@
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
     </row>
-    <row r="5" customHeight="1" spans="1:15">
+    <row r="5" customHeight="1" spans="1:16">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A64" si="0">C5*1000+E5</f>
         <v>1001</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" s="10">
         <v>1</v>
@@ -1621,13 +1652,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:15">
+    <row r="6" customHeight="1" spans="1:16">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" s="10">
         <v>1</v>
@@ -1666,14 +1697,17 @@
       <c r="O6" s="14">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:15">
+      <c r="P6" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:16">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" s="10">
         <v>1</v>
@@ -1712,20 +1746,23 @@
       <c r="O7" s="14">
         <v>80</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:15">
+      <c r="P7" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:16">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E8" s="10">
         <v>4</v>
@@ -1760,20 +1797,23 @@
       <c r="O8" s="14">
         <v>90</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:15">
+      <c r="P8" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:16">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="10">
         <v>1</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E9" s="10">
         <v>5</v>
@@ -1808,14 +1848,17 @@
       <c r="O9" s="14">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:15">
+      <c r="P9" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:16">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -1854,14 +1897,17 @@
       <c r="O10" s="14">
         <v>110</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:15">
+      <c r="P10" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:16">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="10">
         <v>1</v>
@@ -1901,19 +1947,19 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:15">
+    <row r="12" customHeight="1" spans="1:16">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="10">
         <v>1</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E12" s="10">
         <v>8</v>
@@ -1949,13 +1995,13 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:15">
+    <row r="13" customHeight="1" spans="1:16">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>1009</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="10">
         <v>1</v>
@@ -1995,13 +2041,13 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:15">
+    <row r="14" customHeight="1" spans="1:16">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>1010</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -2041,13 +2087,13 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:15">
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:16">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>1011</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" s="10">
         <v>1</v>
@@ -2087,19 +2133,19 @@
         <v>160</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:15">
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:16">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
         <v>1012</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C16" s="10">
         <v>1</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E16" s="10">
         <v>12</v>
@@ -2141,7 +2187,7 @@
         <v>1013</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C17" s="10">
         <v>1</v>
@@ -2187,7 +2233,7 @@
         <v>1014</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C18" s="10">
         <v>1</v>
@@ -2233,7 +2279,7 @@
         <v>1015</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -2279,13 +2325,13 @@
         <v>1016</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C20" s="10">
         <v>1</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E20" s="10">
         <v>16</v>
@@ -2327,7 +2373,7 @@
         <v>1017</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C21" s="10">
         <v>1</v>
@@ -2373,7 +2419,7 @@
         <v>1018</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C22" s="10">
         <v>1</v>
@@ -2419,7 +2465,7 @@
         <v>1019</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C23" s="10">
         <v>1</v>
@@ -2465,13 +2511,13 @@
         <v>1020</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C24" s="10">
         <v>1</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E24" s="10">
         <v>20</v>
@@ -2513,7 +2559,7 @@
         <v>1021</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C25" s="10">
         <v>1</v>
@@ -2559,7 +2605,7 @@
         <v>1022</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C26" s="10">
         <v>1</v>
@@ -2605,7 +2651,7 @@
         <v>1023</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C27" s="10">
         <v>1</v>
@@ -2651,13 +2697,13 @@
         <v>1024</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E28" s="10">
         <v>24</v>
@@ -2699,7 +2745,7 @@
         <v>1025</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -2745,7 +2791,7 @@
         <v>1026</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C30" s="10">
         <v>1</v>
@@ -2791,7 +2837,7 @@
         <v>1027</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
@@ -2837,13 +2883,13 @@
         <v>1028</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C32" s="10">
         <v>1</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E32" s="10">
         <v>28</v>
@@ -2885,7 +2931,7 @@
         <v>1029</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C33" s="10">
         <v>1</v>
@@ -2931,7 +2977,7 @@
         <v>1030</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C34" s="10">
         <v>1</v>
@@ -2977,7 +3023,7 @@
         <v>1031</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C35" s="10">
         <v>1</v>
@@ -3023,13 +3069,13 @@
         <v>1032</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C36" s="10">
         <v>1</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E36" s="10">
         <v>32</v>
@@ -3071,7 +3117,7 @@
         <v>1033</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C37" s="10">
         <v>1</v>
@@ -3117,7 +3163,7 @@
         <v>1034</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C38" s="10">
         <v>1</v>
@@ -3163,7 +3209,7 @@
         <v>1035</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C39" s="10">
         <v>1</v>
@@ -3209,13 +3255,13 @@
         <v>1036</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C40" s="10">
         <v>1</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E40" s="10">
         <v>36</v>
@@ -3257,7 +3303,7 @@
         <v>1037</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C41" s="10">
         <v>1</v>
@@ -3303,7 +3349,7 @@
         <v>1038</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C42" s="10">
         <v>1</v>
@@ -3349,7 +3395,7 @@
         <v>1039</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C43" s="10">
         <v>1</v>
@@ -3395,13 +3441,13 @@
         <v>1040</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C44" s="10">
         <v>1</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E44" s="10">
         <v>40</v>
@@ -3443,7 +3489,7 @@
         <v>1041</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C45" s="10">
         <v>1</v>
@@ -3489,7 +3535,7 @@
         <v>1042</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C46" s="10">
         <v>1</v>
@@ -3535,7 +3581,7 @@
         <v>1043</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C47" s="10">
         <v>1</v>
@@ -3581,13 +3627,13 @@
         <v>1044</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E48" s="10">
         <v>44</v>
@@ -3629,7 +3675,7 @@
         <v>1045</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C49" s="10">
         <v>1</v>
@@ -3675,7 +3721,7 @@
         <v>1046</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C50" s="10">
         <v>1</v>
@@ -3721,7 +3767,7 @@
         <v>1047</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C51" s="10">
         <v>1</v>
@@ -3767,7 +3813,7 @@
         <v>1048</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C52" s="10">
         <v>1</v>
@@ -3813,7 +3859,7 @@
         <v>1049</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C53" s="10">
         <v>1</v>
@@ -3859,7 +3905,7 @@
         <v>1050</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C54" s="10">
         <v>1</v>
@@ -3905,7 +3951,7 @@
         <v>1051</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C55" s="10">
         <v>1</v>
@@ -3951,7 +3997,7 @@
         <v>1052</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C56" s="10">
         <v>1</v>
@@ -3997,7 +4043,7 @@
         <v>1053</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C57" s="10">
         <v>1</v>
@@ -4043,7 +4089,7 @@
         <v>1054</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C58" s="10">
         <v>1</v>
@@ -4089,7 +4135,7 @@
         <v>1055</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C59" s="10">
         <v>1</v>
@@ -4135,7 +4181,7 @@
         <v>1056</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C60" s="10">
         <v>1</v>
@@ -4181,7 +4227,7 @@
         <v>1057</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C61" s="10">
         <v>1</v>
@@ -4227,7 +4273,7 @@
         <v>1058</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C62" s="10">
         <v>1</v>
@@ -4273,7 +4319,7 @@
         <v>1059</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C63" s="10">
         <v>1</v>
@@ -4319,7 +4365,7 @@
         <v>1060</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C64" s="10">
         <v>1</v>
@@ -4492,7 +4538,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -4513,7 +4559,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -4534,7 +4580,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -4555,7 +4601,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -4576,7 +4622,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -4597,7 +4643,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -4618,7 +4664,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -4639,7 +4685,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4660,7 +4706,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4681,7 +4727,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4702,7 +4748,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4723,7 +4769,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4744,7 +4790,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4765,251 +4811,251 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1"/>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B26" s="1"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B27" s="1"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B28" s="1"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B29" s="1"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B30" s="1"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B31" s="1"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B32" s="1"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B33" s="1"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B34" s="1"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B35" s="1"/>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B36" s="1"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B37" s="1"/>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B38" s="1"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B39" s="1"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B41" s="1"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B42" s="1"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B47" s="1"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B49" s="1"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B50" s="1"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B51" s="1"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B52" s="1"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B53" s="1"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B54" s="1"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B55" s="1"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B56" s="1"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -251,6 +251,9 @@
     <t>预估建筑达成等级</t>
   </si>
   <si>
+    <t>预估交互次数/人</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -300,6 +303,9 @@
   </si>
   <si>
     <t>ExpectedBuildingLevel</t>
+  </si>
+  <si>
+    <t>InteractCount</t>
   </si>
   <si>
     <t>拉斯维加斯</t>
@@ -1424,7 +1430,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -1444,7 +1450,7 @@
     <col min="17" max="16384" width="15.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" customHeight="1" spans="1:16">
+    <row r="1" s="2" customFormat="1" customHeight="1" spans="1:17">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1493,104 +1499,113 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:16">
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:17">
       <c r="A2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:16">
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:17">
       <c r="A3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:16">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:17">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1607,13 +1622,13 @@
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
     </row>
-    <row r="5" customHeight="1" spans="1:16">
+    <row r="5" customHeight="1" spans="1:17">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A64" si="0">C5*1000+E5</f>
         <v>1001</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="10">
         <v>1</v>
@@ -1651,14 +1666,17 @@
       <c r="O5" s="14">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:16">
+      <c r="Q5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:17">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
         <v>1002</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="10">
         <v>1</v>
@@ -1698,16 +1716,19 @@
         <v>70</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:16">
+        <v>36</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:17">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7" s="10">
         <v>1</v>
@@ -1747,22 +1768,25 @@
         <v>80</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:16">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:17">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8" s="10">
         <v>4</v>
@@ -1798,22 +1822,25 @@
         <v>90</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:16">
+        <v>39</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:17">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" s="10">
         <v>1</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9" s="10">
         <v>5</v>
@@ -1849,16 +1876,19 @@
         <v>100</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:16">
+        <v>41</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:17">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -1898,16 +1928,19 @@
         <v>110</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:17">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11" s="10">
         <v>1</v>
@@ -1946,20 +1979,26 @@
       <c r="O11" s="14">
         <v>120</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:16">
+      <c r="P11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:17">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="10">
         <v>1</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12" s="10">
         <v>8</v>
@@ -1994,14 +2033,20 @@
       <c r="O12" s="14">
         <v>130</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:16">
+      <c r="P12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:17">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>1009</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="10">
         <v>1</v>
@@ -2040,14 +2085,20 @@
       <c r="O13" s="14">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:16">
+      <c r="P13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:17">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>1010</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -2086,14 +2137,20 @@
       <c r="O14" s="14">
         <v>150</v>
       </c>
-    </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>1011</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" s="10">
         <v>1</v>
@@ -2132,20 +2189,26 @@
       <c r="O15" s="14">
         <v>160</v>
       </c>
-    </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
         <v>1012</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" s="10">
         <v>1</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E16" s="10">
         <v>12</v>
@@ -2180,14 +2243,20 @@
       <c r="O16" s="14">
         <v>170</v>
       </c>
-    </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
         <v>1013</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" s="10">
         <v>1</v>
@@ -2226,14 +2295,20 @@
       <c r="O17" s="14">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
         <v>1014</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C18" s="10">
         <v>1</v>
@@ -2272,14 +2347,20 @@
       <c r="O18" s="14">
         <v>190</v>
       </c>
-    </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
         <v>1015</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -2318,20 +2399,26 @@
       <c r="O19" s="14">
         <v>200</v>
       </c>
-    </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
         <v>1016</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C20" s="10">
         <v>1</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E20" s="10">
         <v>16</v>
@@ -2366,14 +2453,20 @@
       <c r="O20" s="14">
         <v>210</v>
       </c>
-    </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
         <v>1017</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C21" s="10">
         <v>1</v>
@@ -2412,14 +2505,20 @@
       <c r="O21" s="14">
         <v>220</v>
       </c>
-    </row>
-    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
         <v>1018</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C22" s="10">
         <v>1</v>
@@ -2458,14 +2557,20 @@
       <c r="O22" s="14">
         <v>230</v>
       </c>
-    </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
         <v>1019</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C23" s="10">
         <v>1</v>
@@ -2504,20 +2609,26 @@
       <c r="O23" s="14">
         <v>240</v>
       </c>
-    </row>
-    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A24" s="10">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C24" s="10">
         <v>1</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E24" s="10">
         <v>20</v>
@@ -2552,14 +2663,20 @@
       <c r="O24" s="14">
         <v>250</v>
       </c>
-    </row>
-    <row r="25" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A25" s="10">
         <f t="shared" si="0"/>
         <v>1021</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" s="10">
         <v>1</v>
@@ -2598,14 +2715,20 @@
       <c r="O25" s="14">
         <v>260</v>
       </c>
-    </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A26" s="10">
         <f t="shared" si="0"/>
         <v>1022</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C26" s="10">
         <v>1</v>
@@ -2644,14 +2767,20 @@
       <c r="O26" s="14">
         <v>270</v>
       </c>
-    </row>
-    <row r="27" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A27" s="10">
         <f t="shared" si="0"/>
         <v>1023</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C27" s="10">
         <v>1</v>
@@ -2690,20 +2819,26 @@
       <c r="O27" s="14">
         <v>280</v>
       </c>
-    </row>
-    <row r="28" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A28" s="10">
         <f t="shared" si="0"/>
         <v>1024</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E28" s="10">
         <v>24</v>
@@ -2738,14 +2873,20 @@
       <c r="O28" s="14">
         <v>290</v>
       </c>
-    </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A29" s="10">
         <f t="shared" si="0"/>
         <v>1025</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -2784,14 +2925,20 @@
       <c r="O29" s="14">
         <v>300</v>
       </c>
-    </row>
-    <row r="30" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A30" s="10">
         <f t="shared" si="0"/>
         <v>1026</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C30" s="10">
         <v>1</v>
@@ -2830,14 +2977,20 @@
       <c r="O30" s="14">
         <v>310</v>
       </c>
-    </row>
-    <row r="31" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A31" s="10">
         <f t="shared" si="0"/>
         <v>1027</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
@@ -2876,20 +3029,26 @@
       <c r="O31" s="14">
         <v>320</v>
       </c>
-    </row>
-    <row r="32" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A32" s="10">
         <f t="shared" si="0"/>
         <v>1028</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C32" s="10">
         <v>1</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E32" s="10">
         <v>28</v>
@@ -2924,14 +3083,20 @@
       <c r="O32" s="14">
         <v>330</v>
       </c>
-    </row>
-    <row r="33" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A33" s="10">
         <f t="shared" si="0"/>
         <v>1029</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C33" s="10">
         <v>1</v>
@@ -2970,14 +3135,20 @@
       <c r="O33" s="14">
         <v>340</v>
       </c>
-    </row>
-    <row r="34" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A34" s="10">
         <f t="shared" si="0"/>
         <v>1030</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C34" s="10">
         <v>1</v>
@@ -3016,14 +3187,20 @@
       <c r="O34" s="14">
         <v>350</v>
       </c>
-    </row>
-    <row r="35" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A35" s="10">
         <f t="shared" si="0"/>
         <v>1031</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C35" s="10">
         <v>1</v>
@@ -3062,20 +3239,26 @@
       <c r="O35" s="14">
         <v>360</v>
       </c>
-    </row>
-    <row r="36" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A36" s="10">
         <f t="shared" si="0"/>
         <v>1032</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C36" s="10">
         <v>1</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E36" s="10">
         <v>32</v>
@@ -3110,14 +3293,20 @@
       <c r="O36" s="14">
         <v>370</v>
       </c>
-    </row>
-    <row r="37" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A37" s="10">
         <f t="shared" si="0"/>
         <v>1033</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C37" s="10">
         <v>1</v>
@@ -3156,14 +3345,20 @@
       <c r="O37" s="14">
         <v>380</v>
       </c>
-    </row>
-    <row r="38" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A38" s="10">
         <f t="shared" si="0"/>
         <v>1034</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C38" s="10">
         <v>1</v>
@@ -3202,14 +3397,20 @@
       <c r="O38" s="14">
         <v>390</v>
       </c>
-    </row>
-    <row r="39" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A39" s="10">
         <f t="shared" si="0"/>
         <v>1035</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C39" s="10">
         <v>1</v>
@@ -3248,20 +3449,26 @@
       <c r="O39" s="14">
         <v>400</v>
       </c>
-    </row>
-    <row r="40" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A40" s="10">
         <f t="shared" si="0"/>
         <v>1036</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C40" s="10">
         <v>1</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E40" s="10">
         <v>36</v>
@@ -3296,14 +3503,20 @@
       <c r="O40" s="14">
         <v>410</v>
       </c>
-    </row>
-    <row r="41" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A41" s="10">
         <f t="shared" si="0"/>
         <v>1037</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C41" s="10">
         <v>1</v>
@@ -3342,14 +3555,20 @@
       <c r="O41" s="14">
         <v>420</v>
       </c>
-    </row>
-    <row r="42" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A42" s="10">
         <f t="shared" si="0"/>
         <v>1038</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C42" s="10">
         <v>1</v>
@@ -3388,14 +3607,20 @@
       <c r="O42" s="14">
         <v>430</v>
       </c>
-    </row>
-    <row r="43" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A43" s="10">
         <f t="shared" si="0"/>
         <v>1039</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C43" s="10">
         <v>1</v>
@@ -3434,20 +3659,26 @@
       <c r="O43" s="14">
         <v>440</v>
       </c>
-    </row>
-    <row r="44" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A44" s="10">
         <f t="shared" si="0"/>
         <v>1040</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C44" s="10">
         <v>1</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E44" s="10">
         <v>40</v>
@@ -3482,14 +3713,20 @@
       <c r="O44" s="14">
         <v>450</v>
       </c>
-    </row>
-    <row r="45" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A45" s="10">
         <f t="shared" si="0"/>
         <v>1041</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C45" s="10">
         <v>1</v>
@@ -3528,14 +3765,20 @@
       <c r="O45" s="14">
         <v>460</v>
       </c>
-    </row>
-    <row r="46" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A46" s="10">
         <f t="shared" si="0"/>
         <v>1042</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C46" s="10">
         <v>1</v>
@@ -3574,14 +3817,20 @@
       <c r="O46" s="14">
         <v>470</v>
       </c>
-    </row>
-    <row r="47" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A47" s="10">
         <f t="shared" si="0"/>
         <v>1043</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C47" s="10">
         <v>1</v>
@@ -3620,20 +3869,26 @@
       <c r="O47" s="14">
         <v>480</v>
       </c>
-    </row>
-    <row r="48" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A48" s="10">
         <f t="shared" si="0"/>
         <v>1044</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E48" s="10">
         <v>44</v>
@@ -3668,14 +3923,20 @@
       <c r="O48" s="14">
         <v>490</v>
       </c>
-    </row>
-    <row r="49" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A49" s="10">
         <f t="shared" si="0"/>
         <v>1045</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C49" s="10">
         <v>1</v>
@@ -3714,14 +3975,20 @@
       <c r="O49" s="14">
         <v>500</v>
       </c>
-    </row>
-    <row r="50" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A50" s="10">
         <f t="shared" si="0"/>
         <v>1046</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C50" s="10">
         <v>1</v>
@@ -3760,14 +4027,20 @@
       <c r="O50" s="14">
         <v>510</v>
       </c>
-    </row>
-    <row r="51" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A51" s="10">
         <f t="shared" si="0"/>
         <v>1047</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C51" s="10">
         <v>1</v>
@@ -3806,14 +4079,20 @@
       <c r="O51" s="14">
         <v>520</v>
       </c>
-    </row>
-    <row r="52" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A52" s="10">
         <f t="shared" si="0"/>
         <v>1048</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C52" s="10">
         <v>1</v>
@@ -3852,14 +4131,20 @@
       <c r="O52" s="14">
         <v>530</v>
       </c>
-    </row>
-    <row r="53" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A53" s="10">
         <f t="shared" si="0"/>
         <v>1049</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C53" s="10">
         <v>1</v>
@@ -3898,14 +4183,20 @@
       <c r="O53" s="14">
         <v>540</v>
       </c>
-    </row>
-    <row r="54" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P53" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A54" s="10">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C54" s="10">
         <v>1</v>
@@ -3944,14 +4235,20 @@
       <c r="O54" s="14">
         <v>550</v>
       </c>
-    </row>
-    <row r="55" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A55" s="10">
         <f t="shared" si="0"/>
         <v>1051</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C55" s="10">
         <v>1</v>
@@ -3990,14 +4287,20 @@
       <c r="O55" s="14">
         <v>560</v>
       </c>
-    </row>
-    <row r="56" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P55" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A56" s="10">
         <f t="shared" si="0"/>
         <v>1052</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C56" s="10">
         <v>1</v>
@@ -4036,14 +4339,20 @@
       <c r="O56" s="14">
         <v>570</v>
       </c>
-    </row>
-    <row r="57" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A57" s="10">
         <f t="shared" si="0"/>
         <v>1053</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C57" s="10">
         <v>1</v>
@@ -4082,14 +4391,20 @@
       <c r="O57" s="14">
         <v>580</v>
       </c>
-    </row>
-    <row r="58" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A58" s="10">
         <f t="shared" si="0"/>
         <v>1054</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C58" s="10">
         <v>1</v>
@@ -4128,14 +4443,20 @@
       <c r="O58" s="14">
         <v>590</v>
       </c>
-    </row>
-    <row r="59" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P58" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A59" s="10">
         <f t="shared" si="0"/>
         <v>1055</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C59" s="10">
         <v>1</v>
@@ -4174,14 +4495,20 @@
       <c r="O59" s="14">
         <v>600</v>
       </c>
-    </row>
-    <row r="60" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P59" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A60" s="10">
         <f t="shared" si="0"/>
         <v>1056</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C60" s="10">
         <v>1</v>
@@ -4220,14 +4547,20 @@
       <c r="O60" s="14">
         <v>610</v>
       </c>
-    </row>
-    <row r="61" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A61" s="10">
         <f t="shared" si="0"/>
         <v>1057</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C61" s="10">
         <v>1</v>
@@ -4266,14 +4599,20 @@
       <c r="O61" s="14">
         <v>620</v>
       </c>
-    </row>
-    <row r="62" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P61" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A62" s="10">
         <f t="shared" si="0"/>
         <v>1058</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C62" s="10">
         <v>1</v>
@@ -4312,14 +4651,20 @@
       <c r="O62" s="14">
         <v>630</v>
       </c>
-    </row>
-    <row r="63" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P62" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A63" s="10">
         <f t="shared" si="0"/>
         <v>1059</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C63" s="10">
         <v>1</v>
@@ -4358,14 +4703,20 @@
       <c r="O63" s="14">
         <v>640</v>
       </c>
-    </row>
-    <row r="64" s="3" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A64" s="10">
         <f t="shared" si="0"/>
         <v>1060</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C64" s="10">
         <v>1</v>
@@ -4403,6 +4754,12 @@
       </c>
       <c r="O64" s="14">
         <v>650</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4538,7 +4895,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -4559,7 +4916,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -4580,7 +4937,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -4601,7 +4958,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -4622,7 +4979,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -4643,7 +5000,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -4664,7 +5021,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -4685,7 +5042,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4706,7 +5063,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4727,7 +5084,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4748,7 +5105,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4769,7 +5126,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4790,7 +5147,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4811,251 +5168,251 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B20" s="1"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1"/>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" s="1"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B27" s="1"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B28" s="1"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B29" s="1"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B30" s="1"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B31" s="1"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B32" s="1"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B33" s="1"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B34" s="1"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B35" s="1"/>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B36" s="1"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B37" s="1"/>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B38" s="1"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B39" s="1"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B41" s="1"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B42" s="1"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B49" s="1"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B51" s="1"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B52" s="1"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B53" s="1"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B54" s="1"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B55" s="1"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -317,16 +317,22 @@
     <t>1301_3|1101_2|1102_2</t>
   </si>
   <si>
-    <t>1301_3|1101_3|1102_3</t>
+    <t>1202_1</t>
   </si>
   <si>
-    <t>1202_1|1303_1|1304_1</t>
+    <t>1301_3|1101_3|1102_3</t>
   </si>
   <si>
     <t>1301_4|1101_4|1102_4|1202_3</t>
   </si>
   <si>
+    <t>1303_1|1304_1</t>
+  </si>
+  <si>
     <t>1301_5|1101_5|1102_5|1202_4</t>
+  </si>
+  <si>
+    <t>1102_1</t>
   </si>
   <si>
     <t>1110_1</t>
@@ -1637,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="11">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="G5" s="13">
         <v>100</v>
@@ -1686,7 +1692,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="11">
-        <v>600</v>
+        <v>940</v>
       </c>
       <c r="G6" s="13">
         <v>110</v>
@@ -1738,7 +1744,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="11">
-        <v>600</v>
+        <v>960</v>
       </c>
       <c r="G7" s="13">
         <v>120</v>
@@ -1785,12 +1791,14 @@
       <c r="C8" s="11">
         <v>1</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="11" t="s">
+        <v>38</v>
+      </c>
       <c r="E8" s="11">
         <v>4</v>
       </c>
       <c r="F8" s="11">
-        <v>300</v>
+        <v>490</v>
       </c>
       <c r="G8" s="13">
         <v>130</v>
@@ -1820,7 +1828,7 @@
         <v>90</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q8" s="4">
         <v>2</v>
@@ -1837,14 +1845,12 @@
       <c r="C9" s="11">
         <v>1</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>39</v>
-      </c>
+      <c r="D9" s="11"/>
       <c r="E9" s="11">
         <v>5</v>
       </c>
       <c r="F9" s="11">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G9" s="13">
         <v>140</v>
@@ -1891,12 +1897,14 @@
       <c r="C10" s="11">
         <v>1</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="E10" s="11">
         <v>6</v>
       </c>
       <c r="F10" s="11">
-        <v>200</v>
+        <v>510</v>
       </c>
       <c r="G10" s="13">
         <v>150</v>
@@ -1926,7 +1934,7 @@
         <v>110</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q10" s="4">
         <v>3</v>
@@ -1943,12 +1951,14 @@
       <c r="C11" s="11">
         <v>1</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="E11" s="11">
         <v>7</v>
       </c>
       <c r="F11" s="11">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G11" s="13">
         <v>160</v>
@@ -1978,7 +1988,7 @@
         <v>120</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q11" s="4">
         <v>3</v>
@@ -1996,13 +2006,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" s="11">
         <v>8</v>
       </c>
       <c r="F12" s="11">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="G12" s="13">
         <v>170</v>
@@ -2032,7 +2042,7 @@
         <v>130</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q12" s="4">
         <v>3</v>
@@ -2054,7 +2064,7 @@
         <v>9</v>
       </c>
       <c r="F13" s="11">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="G13" s="13">
         <v>180</v>
@@ -2084,7 +2094,7 @@
         <v>140</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q13" s="4">
         <v>3</v>
@@ -2106,7 +2116,7 @@
         <v>10</v>
       </c>
       <c r="F14" s="11">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="G14" s="13">
         <v>190</v>
@@ -2136,7 +2146,7 @@
         <v>150</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q14" s="4">
         <v>3</v>
@@ -2158,7 +2168,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="11">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="G15" s="13">
         <v>200</v>
@@ -2188,7 +2198,7 @@
         <v>160</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q15" s="4">
         <v>4</v>
@@ -2206,13 +2216,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E16" s="11">
         <v>12</v>
       </c>
       <c r="F16" s="11">
-        <v>130</v>
+        <v>228</v>
       </c>
       <c r="G16" s="13">
         <v>210</v>
@@ -2242,7 +2252,7 @@
         <v>170</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q16" s="4">
         <v>4</v>
@@ -2264,7 +2274,7 @@
         <v>13</v>
       </c>
       <c r="F17" s="11">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="G17" s="13">
         <v>220</v>
@@ -2294,7 +2304,7 @@
         <v>180</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q17" s="4">
         <v>4</v>
@@ -2316,7 +2326,7 @@
         <v>14</v>
       </c>
       <c r="F18" s="11">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="G18" s="13">
         <v>230</v>
@@ -2346,7 +2356,7 @@
         <v>190</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q18" s="4">
         <v>4</v>
@@ -2368,7 +2378,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="11">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="G19" s="13">
         <v>240</v>
@@ -2398,7 +2408,7 @@
         <v>200</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q19" s="4">
         <v>4</v>
@@ -2416,13 +2426,13 @@
         <v>1</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E20" s="11">
         <v>16</v>
       </c>
       <c r="F20" s="11">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="G20" s="13">
         <v>250</v>
@@ -2452,7 +2462,7 @@
         <v>210</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q20" s="4">
         <v>5</v>
@@ -2474,7 +2484,7 @@
         <v>17</v>
       </c>
       <c r="F21" s="11">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="G21" s="13">
         <v>260</v>
@@ -2504,7 +2514,7 @@
         <v>220</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q21" s="4">
         <v>5</v>
@@ -2526,7 +2536,7 @@
         <v>18</v>
       </c>
       <c r="F22" s="11">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="G22" s="13">
         <v>270</v>
@@ -2556,7 +2566,7 @@
         <v>230</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q22" s="4">
         <v>5</v>
@@ -2578,7 +2588,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="11">
-        <v>120</v>
+        <v>215</v>
       </c>
       <c r="G23" s="13">
         <v>280</v>
@@ -2608,7 +2618,7 @@
         <v>240</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q23" s="4">
         <v>5</v>
@@ -2626,13 +2636,13 @@
         <v>1</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E24" s="11">
         <v>20</v>
       </c>
       <c r="F24" s="11">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="G24" s="13">
         <v>290</v>
@@ -2662,7 +2672,7 @@
         <v>250</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q24" s="4">
         <v>5</v>
@@ -2684,7 +2694,7 @@
         <v>21</v>
       </c>
       <c r="F25" s="11">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="G25" s="13">
         <v>300</v>
@@ -2714,7 +2724,7 @@
         <v>260</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q25" s="4">
         <v>6</v>
@@ -2736,7 +2746,7 @@
         <v>22</v>
       </c>
       <c r="F26" s="11">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="G26" s="13">
         <v>310</v>
@@ -2766,7 +2776,7 @@
         <v>270</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q26" s="4">
         <v>6</v>
@@ -2788,7 +2798,7 @@
         <v>23</v>
       </c>
       <c r="F27" s="11">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="G27" s="13">
         <v>320</v>
@@ -2818,7 +2828,7 @@
         <v>280</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q27" s="4">
         <v>6</v>
@@ -2836,13 +2846,13 @@
         <v>1</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E28" s="11">
         <v>24</v>
       </c>
       <c r="F28" s="11">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="G28" s="13">
         <v>330</v>
@@ -2872,7 +2882,7 @@
         <v>290</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q28" s="4">
         <v>6</v>
@@ -2894,7 +2904,7 @@
         <v>25</v>
       </c>
       <c r="F29" s="11">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="G29" s="13">
         <v>340</v>
@@ -2924,7 +2934,7 @@
         <v>300</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q29" s="4">
         <v>6</v>
@@ -2946,7 +2956,7 @@
         <v>26</v>
       </c>
       <c r="F30" s="11">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="G30" s="13">
         <v>350</v>
@@ -2976,7 +2986,7 @@
         <v>310</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q30" s="4">
         <v>6</v>
@@ -2998,7 +3008,7 @@
         <v>27</v>
       </c>
       <c r="F31" s="11">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="G31" s="13">
         <v>360</v>
@@ -3028,7 +3038,7 @@
         <v>320</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q31" s="4">
         <v>6</v>
@@ -3046,13 +3056,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E32" s="11">
         <v>28</v>
       </c>
       <c r="F32" s="11">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="G32" s="13">
         <v>370</v>
@@ -3082,7 +3092,7 @@
         <v>330</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q32" s="4">
         <v>6</v>
@@ -3104,7 +3114,7 @@
         <v>29</v>
       </c>
       <c r="F33" s="11">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="G33" s="13">
         <v>380</v>
@@ -3134,7 +3144,7 @@
         <v>340</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q33" s="4">
         <v>6</v>
@@ -3156,7 +3166,7 @@
         <v>30</v>
       </c>
       <c r="F34" s="11">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="G34" s="13">
         <v>390</v>
@@ -3186,7 +3196,7 @@
         <v>350</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q34" s="4">
         <v>6</v>
@@ -3208,7 +3218,7 @@
         <v>31</v>
       </c>
       <c r="F35" s="11">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="G35" s="13">
         <v>400</v>
@@ -3238,7 +3248,7 @@
         <v>360</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q35" s="4">
         <v>6</v>
@@ -3256,13 +3266,13 @@
         <v>1</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E36" s="11">
         <v>32</v>
       </c>
       <c r="F36" s="11">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="G36" s="13">
         <v>410</v>
@@ -3292,7 +3302,7 @@
         <v>370</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q36" s="4">
         <v>6</v>
@@ -3314,7 +3324,7 @@
         <v>33</v>
       </c>
       <c r="F37" s="11">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="G37" s="13">
         <v>420</v>
@@ -3344,7 +3354,7 @@
         <v>380</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q37" s="4">
         <v>6</v>
@@ -3366,7 +3376,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="11">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="G38" s="13">
         <v>430</v>
@@ -3396,7 +3406,7 @@
         <v>390</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q38" s="4">
         <v>6</v>
@@ -3418,7 +3428,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="11">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G39" s="13">
         <v>440</v>
@@ -3448,7 +3458,7 @@
         <v>400</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q39" s="4">
         <v>6</v>
@@ -3466,13 +3476,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E40" s="11">
         <v>36</v>
       </c>
       <c r="F40" s="11">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="G40" s="13">
         <v>450</v>
@@ -3502,7 +3512,7 @@
         <v>410</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q40" s="4">
         <v>6</v>
@@ -3524,7 +3534,7 @@
         <v>37</v>
       </c>
       <c r="F41" s="11">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="G41" s="13">
         <v>460</v>
@@ -3554,7 +3564,7 @@
         <v>420</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q41" s="4">
         <v>6</v>
@@ -3576,7 +3586,7 @@
         <v>38</v>
       </c>
       <c r="F42" s="11">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="G42" s="13">
         <v>470</v>
@@ -3606,7 +3616,7 @@
         <v>430</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q42" s="4">
         <v>6</v>
@@ -3628,7 +3638,7 @@
         <v>39</v>
       </c>
       <c r="F43" s="11">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="G43" s="13">
         <v>480</v>
@@ -3658,7 +3668,7 @@
         <v>440</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q43" s="4">
         <v>6</v>
@@ -3676,13 +3686,13 @@
         <v>1</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E44" s="11">
         <v>40</v>
       </c>
       <c r="F44" s="11">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="G44" s="13">
         <v>490</v>
@@ -3712,7 +3722,7 @@
         <v>450</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q44" s="4">
         <v>6</v>
@@ -3734,7 +3744,7 @@
         <v>41</v>
       </c>
       <c r="F45" s="11">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="G45" s="13">
         <v>500</v>
@@ -3764,7 +3774,7 @@
         <v>460</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q45" s="4">
         <v>6</v>
@@ -3786,7 +3796,7 @@
         <v>42</v>
       </c>
       <c r="F46" s="11">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="G46" s="13">
         <v>510</v>
@@ -3816,7 +3826,7 @@
         <v>470</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q46" s="4">
         <v>6</v>
@@ -3838,7 +3848,7 @@
         <v>43</v>
       </c>
       <c r="F47" s="11">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="G47" s="13">
         <v>520</v>
@@ -3868,7 +3878,7 @@
         <v>480</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q47" s="4">
         <v>6</v>
@@ -3886,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E48" s="11">
         <v>44</v>
       </c>
       <c r="F48" s="11">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="G48" s="13">
         <v>530</v>
@@ -3922,7 +3932,7 @@
         <v>490</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q48" s="4">
         <v>6</v>
@@ -3944,7 +3954,7 @@
         <v>45</v>
       </c>
       <c r="F49" s="11">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="G49" s="13">
         <v>540</v>
@@ -3974,7 +3984,7 @@
         <v>500</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q49" s="4">
         <v>6</v>
@@ -3996,7 +4006,7 @@
         <v>46</v>
       </c>
       <c r="F50" s="11">
-        <v>65</v>
+        <v>182</v>
       </c>
       <c r="G50" s="13">
         <v>550</v>
@@ -4026,7 +4036,7 @@
         <v>510</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q50" s="4">
         <v>6</v>
@@ -4048,7 +4058,7 @@
         <v>47</v>
       </c>
       <c r="F51" s="11">
-        <v>65</v>
+        <v>184</v>
       </c>
       <c r="G51" s="13">
         <v>560</v>
@@ -4078,7 +4088,7 @@
         <v>520</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q51" s="4">
         <v>6</v>
@@ -4100,7 +4110,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="11">
-        <v>65</v>
+        <v>186</v>
       </c>
       <c r="G52" s="13">
         <v>570</v>
@@ -4130,7 +4140,7 @@
         <v>530</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q52" s="4">
         <v>6</v>
@@ -4152,7 +4162,7 @@
         <v>49</v>
       </c>
       <c r="F53" s="11">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="G53" s="13">
         <v>580</v>
@@ -4182,7 +4192,7 @@
         <v>540</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q53" s="4">
         <v>6</v>
@@ -4204,7 +4214,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="11">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="G54" s="13">
         <v>590</v>
@@ -4234,7 +4244,7 @@
         <v>550</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q54" s="4">
         <v>6</v>
@@ -4256,7 +4266,7 @@
         <v>51</v>
       </c>
       <c r="F55" s="11">
-        <v>65</v>
+        <v>192</v>
       </c>
       <c r="G55" s="13">
         <v>600</v>
@@ -4286,7 +4296,7 @@
         <v>560</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q55" s="4">
         <v>6</v>
@@ -4308,7 +4318,7 @@
         <v>52</v>
       </c>
       <c r="F56" s="11">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="G56" s="13">
         <v>610</v>
@@ -4338,7 +4348,7 @@
         <v>570</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q56" s="4">
         <v>6</v>
@@ -4360,7 +4370,7 @@
         <v>53</v>
       </c>
       <c r="F57" s="11">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="G57" s="13">
         <v>620</v>
@@ -4390,7 +4400,7 @@
         <v>580</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q57" s="4">
         <v>6</v>
@@ -4412,7 +4422,7 @@
         <v>54</v>
       </c>
       <c r="F58" s="11">
-        <v>65</v>
+        <v>198</v>
       </c>
       <c r="G58" s="13">
         <v>630</v>
@@ -4442,7 +4452,7 @@
         <v>590</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q58" s="4">
         <v>6</v>
@@ -4464,7 +4474,7 @@
         <v>55</v>
       </c>
       <c r="F59" s="11">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="G59" s="13">
         <v>640</v>
@@ -4494,7 +4504,7 @@
         <v>600</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q59" s="4">
         <v>6</v>
@@ -4516,7 +4526,7 @@
         <v>56</v>
       </c>
       <c r="F60" s="11">
-        <v>65</v>
+        <v>202</v>
       </c>
       <c r="G60" s="13">
         <v>650</v>
@@ -4546,7 +4556,7 @@
         <v>610</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q60" s="4">
         <v>6</v>
@@ -4568,7 +4578,7 @@
         <v>57</v>
       </c>
       <c r="F61" s="11">
-        <v>65</v>
+        <v>204</v>
       </c>
       <c r="G61" s="13">
         <v>660</v>
@@ -4598,7 +4608,7 @@
         <v>620</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q61" s="4">
         <v>6</v>
@@ -4620,7 +4630,7 @@
         <v>58</v>
       </c>
       <c r="F62" s="11">
-        <v>65</v>
+        <v>206</v>
       </c>
       <c r="G62" s="13">
         <v>670</v>
@@ -4650,7 +4660,7 @@
         <v>630</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q62" s="4">
         <v>6</v>
@@ -4672,7 +4682,7 @@
         <v>59</v>
       </c>
       <c r="F63" s="11">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="G63" s="13">
         <v>680</v>
@@ -4702,7 +4712,7 @@
         <v>640</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q63" s="4">
         <v>6</v>
@@ -4724,7 +4734,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="11">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="G64" s="13">
         <v>690</v>
@@ -4754,7 +4764,7 @@
         <v>650</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q64" s="4">
         <v>6</v>
@@ -4776,7 +4786,7 @@
         <v>61</v>
       </c>
       <c r="F65" s="11">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="G65" s="13">
         <v>700</v>
@@ -4806,7 +4816,7 @@
         <v>660</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q65" s="4">
         <v>6</v>
@@ -4828,7 +4838,7 @@
         <v>62</v>
       </c>
       <c r="F66" s="11">
-        <v>65</v>
+        <v>214</v>
       </c>
       <c r="G66" s="13">
         <v>710</v>
@@ -4858,7 +4868,7 @@
         <v>670</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q66" s="4">
         <v>6</v>
@@ -4880,7 +4890,7 @@
         <v>63</v>
       </c>
       <c r="F67" s="11">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="G67" s="13">
         <v>720</v>
@@ -4910,7 +4920,7 @@
         <v>680</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q67" s="4">
         <v>6</v>
@@ -4932,7 +4942,7 @@
         <v>64</v>
       </c>
       <c r="F68" s="11">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="G68" s="13">
         <v>730</v>
@@ -4962,7 +4972,7 @@
         <v>690</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q68" s="4">
         <v>6</v>
@@ -4984,7 +4994,7 @@
         <v>65</v>
       </c>
       <c r="F69" s="11">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="G69" s="13">
         <v>740</v>
@@ -5014,7 +5024,7 @@
         <v>700</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q69" s="4">
         <v>6</v>
@@ -5036,7 +5046,7 @@
         <v>66</v>
       </c>
       <c r="F70" s="11">
-        <v>65</v>
+        <v>222</v>
       </c>
       <c r="G70" s="13">
         <v>750</v>
@@ -5066,7 +5076,7 @@
         <v>710</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q70" s="4">
         <v>6</v>
@@ -5088,7 +5098,7 @@
         <v>67</v>
       </c>
       <c r="F71" s="11">
-        <v>65</v>
+        <v>224</v>
       </c>
       <c r="G71" s="13">
         <v>760</v>
@@ -5118,7 +5128,7 @@
         <v>720</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q71" s="4">
         <v>6</v>
@@ -5140,7 +5150,7 @@
         <v>68</v>
       </c>
       <c r="F72" s="11">
-        <v>65</v>
+        <v>226</v>
       </c>
       <c r="G72" s="13">
         <v>770</v>
@@ -5170,7 +5180,7 @@
         <v>730</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q72" s="4">
         <v>6</v>
@@ -5192,7 +5202,7 @@
         <v>69</v>
       </c>
       <c r="F73" s="11">
-        <v>65</v>
+        <v>228</v>
       </c>
       <c r="G73" s="13">
         <v>780</v>
@@ -5222,7 +5232,7 @@
         <v>740</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q73" s="4">
         <v>6</v>
@@ -5244,7 +5254,7 @@
         <v>70</v>
       </c>
       <c r="F74" s="11">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="G74" s="13">
         <v>790</v>
@@ -5274,7 +5284,7 @@
         <v>750</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q74" s="4">
         <v>6</v>
@@ -5296,7 +5306,7 @@
         <v>71</v>
       </c>
       <c r="F75" s="11">
-        <v>65</v>
+        <v>232</v>
       </c>
       <c r="G75" s="13">
         <v>800</v>
@@ -5326,7 +5336,7 @@
         <v>760</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q75" s="4">
         <v>6</v>
@@ -5348,7 +5358,7 @@
         <v>72</v>
       </c>
       <c r="F76" s="11">
-        <v>65</v>
+        <v>234</v>
       </c>
       <c r="G76" s="13">
         <v>810</v>
@@ -5378,7 +5388,7 @@
         <v>770</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q76" s="4">
         <v>6</v>
@@ -5400,7 +5410,7 @@
         <v>73</v>
       </c>
       <c r="F77" s="11">
-        <v>65</v>
+        <v>236</v>
       </c>
       <c r="G77" s="13">
         <v>820</v>
@@ -5430,7 +5440,7 @@
         <v>780</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q77" s="4">
         <v>6</v>
@@ -5452,7 +5462,7 @@
         <v>74</v>
       </c>
       <c r="F78" s="11">
-        <v>65</v>
+        <v>238</v>
       </c>
       <c r="G78" s="13">
         <v>830</v>
@@ -5482,7 +5492,7 @@
         <v>790</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q78" s="4">
         <v>6</v>
@@ -5504,7 +5514,7 @@
         <v>75</v>
       </c>
       <c r="F79" s="11">
-        <v>65</v>
+        <v>240</v>
       </c>
       <c r="G79" s="13">
         <v>840</v>
@@ -5534,7 +5544,7 @@
         <v>800</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q79" s="4">
         <v>6</v>
@@ -5556,7 +5566,7 @@
         <v>76</v>
       </c>
       <c r="F80" s="11">
-        <v>65</v>
+        <v>242</v>
       </c>
       <c r="G80" s="13">
         <v>850</v>
@@ -5586,7 +5596,7 @@
         <v>810</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q80" s="4">
         <v>6</v>
@@ -5608,7 +5618,7 @@
         <v>77</v>
       </c>
       <c r="F81" s="11">
-        <v>65</v>
+        <v>244</v>
       </c>
       <c r="G81" s="13">
         <v>860</v>
@@ -5638,7 +5648,7 @@
         <v>820</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q81" s="4">
         <v>6</v>
@@ -5660,7 +5670,7 @@
         <v>78</v>
       </c>
       <c r="F82" s="11">
-        <v>65</v>
+        <v>246</v>
       </c>
       <c r="G82" s="13">
         <v>870</v>
@@ -5690,7 +5700,7 @@
         <v>830</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q82" s="4">
         <v>6</v>
@@ -5712,7 +5722,7 @@
         <v>79</v>
       </c>
       <c r="F83" s="11">
-        <v>65</v>
+        <v>248</v>
       </c>
       <c r="G83" s="13">
         <v>880</v>
@@ -5742,7 +5752,7 @@
         <v>840</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q83" s="4">
         <v>6</v>
@@ -5764,7 +5774,7 @@
         <v>80</v>
       </c>
       <c r="F84" s="11">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="G84" s="13">
         <v>890</v>
@@ -5794,7 +5804,7 @@
         <v>850</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q84" s="4">
         <v>6</v>
@@ -5816,7 +5826,7 @@
         <v>81</v>
       </c>
       <c r="F85" s="11">
-        <v>65</v>
+        <v>252</v>
       </c>
       <c r="G85" s="13">
         <v>900</v>
@@ -5846,7 +5856,7 @@
         <v>860</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q85" s="4">
         <v>6</v>
@@ -5868,7 +5878,7 @@
         <v>82</v>
       </c>
       <c r="F86" s="11">
-        <v>65</v>
+        <v>254</v>
       </c>
       <c r="G86" s="13">
         <v>910</v>
@@ -5898,7 +5908,7 @@
         <v>870</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q86" s="4">
         <v>6</v>
@@ -5920,7 +5930,7 @@
         <v>83</v>
       </c>
       <c r="F87" s="11">
-        <v>65</v>
+        <v>256</v>
       </c>
       <c r="G87" s="13">
         <v>920</v>
@@ -5950,7 +5960,7 @@
         <v>880</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q87" s="4">
         <v>6</v>
@@ -5972,7 +5982,7 @@
         <v>84</v>
       </c>
       <c r="F88" s="11">
-        <v>65</v>
+        <v>258</v>
       </c>
       <c r="G88" s="13">
         <v>930</v>
@@ -6002,7 +6012,7 @@
         <v>890</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q88" s="4">
         <v>6</v>
@@ -6024,7 +6034,7 @@
         <v>85</v>
       </c>
       <c r="F89" s="11">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="G89" s="13">
         <v>940</v>
@@ -6054,7 +6064,7 @@
         <v>900</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q89" s="4">
         <v>6</v>
@@ -6076,7 +6086,7 @@
         <v>86</v>
       </c>
       <c r="F90" s="11">
-        <v>65</v>
+        <v>262</v>
       </c>
       <c r="G90" s="13">
         <v>950</v>
@@ -6106,7 +6116,7 @@
         <v>910</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q90" s="4">
         <v>6</v>
@@ -6128,7 +6138,7 @@
         <v>87</v>
       </c>
       <c r="F91" s="11">
-        <v>65</v>
+        <v>264</v>
       </c>
       <c r="G91" s="13">
         <v>960</v>
@@ -6158,7 +6168,7 @@
         <v>920</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q91" s="4">
         <v>6</v>
@@ -6180,7 +6190,7 @@
         <v>88</v>
       </c>
       <c r="F92" s="11">
-        <v>65</v>
+        <v>266</v>
       </c>
       <c r="G92" s="13">
         <v>970</v>
@@ -6210,7 +6220,7 @@
         <v>930</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q92" s="4">
         <v>6</v>
@@ -6232,7 +6242,7 @@
         <v>89</v>
       </c>
       <c r="F93" s="11">
-        <v>65</v>
+        <v>268</v>
       </c>
       <c r="G93" s="13">
         <v>980</v>
@@ -6262,7 +6272,7 @@
         <v>940</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q93" s="4">
         <v>6</v>
@@ -6284,7 +6294,7 @@
         <v>90</v>
       </c>
       <c r="F94" s="11">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="G94" s="13">
         <v>990</v>
@@ -6314,7 +6324,7 @@
         <v>950</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q94" s="4">
         <v>6</v>
@@ -6336,7 +6346,7 @@
         <v>91</v>
       </c>
       <c r="F95" s="11">
-        <v>65</v>
+        <v>272</v>
       </c>
       <c r="G95" s="13">
         <v>1000</v>
@@ -6366,7 +6376,7 @@
         <v>960</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q95" s="4">
         <v>6</v>
@@ -6388,7 +6398,7 @@
         <v>92</v>
       </c>
       <c r="F96" s="11">
-        <v>65</v>
+        <v>274</v>
       </c>
       <c r="G96" s="13">
         <v>1010</v>
@@ -6418,7 +6428,7 @@
         <v>970</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q96" s="4">
         <v>6</v>
@@ -6440,7 +6450,7 @@
         <v>93</v>
       </c>
       <c r="F97" s="11">
-        <v>65</v>
+        <v>276</v>
       </c>
       <c r="G97" s="13">
         <v>1020</v>
@@ -6470,7 +6480,7 @@
         <v>980</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q97" s="4">
         <v>6</v>
@@ -6492,7 +6502,7 @@
         <v>94</v>
       </c>
       <c r="F98" s="11">
-        <v>65</v>
+        <v>278</v>
       </c>
       <c r="G98" s="13">
         <v>1030</v>
@@ -6522,7 +6532,7 @@
         <v>990</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q98" s="4">
         <v>6</v>
@@ -6544,7 +6554,7 @@
         <v>95</v>
       </c>
       <c r="F99" s="11">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="G99" s="13">
         <v>1040</v>
@@ -6574,7 +6584,7 @@
         <v>1000</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q99" s="4">
         <v>6</v>
@@ -6596,7 +6606,7 @@
         <v>96</v>
       </c>
       <c r="F100" s="11">
-        <v>65</v>
+        <v>282</v>
       </c>
       <c r="G100" s="13">
         <v>1050</v>
@@ -6626,7 +6636,7 @@
         <v>1010</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q100" s="4">
         <v>6</v>
@@ -6648,7 +6658,7 @@
         <v>97</v>
       </c>
       <c r="F101" s="11">
-        <v>65</v>
+        <v>284</v>
       </c>
       <c r="G101" s="13">
         <v>1060</v>
@@ -6678,7 +6688,7 @@
         <v>1020</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q101" s="4">
         <v>6</v>
@@ -6700,7 +6710,7 @@
         <v>98</v>
       </c>
       <c r="F102" s="11">
-        <v>65</v>
+        <v>286</v>
       </c>
       <c r="G102" s="13">
         <v>1070</v>
@@ -6730,7 +6740,7 @@
         <v>1030</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q102" s="4">
         <v>6</v>
@@ -6752,7 +6762,7 @@
         <v>99</v>
       </c>
       <c r="F103" s="11">
-        <v>65</v>
+        <v>288</v>
       </c>
       <c r="G103" s="13">
         <v>1080</v>
@@ -6782,7 +6792,7 @@
         <v>1040</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q103" s="4">
         <v>6</v>
@@ -6921,7 +6931,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -6942,7 +6952,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -6963,7 +6973,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -6984,7 +6994,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -7005,7 +7015,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7026,7 +7036,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -7047,7 +7057,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -7068,7 +7078,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -7089,7 +7099,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -7110,7 +7120,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7131,7 +7141,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -7152,7 +7162,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -7173,7 +7183,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -7194,251 +7204,251 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B27" s="2"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B29" s="2"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B31" s="2"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B32" s="2"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B34" s="2"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B35" s="2"/>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B36" s="2"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B37" s="2"/>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B38" s="2"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B39" s="2"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B40" s="2"/>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B41" s="2"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B42" s="2"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B44" s="2"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B45" s="2"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B46" s="2"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B47" s="2"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B48" s="2"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B49" s="2"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B50" s="2"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B51" s="2"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B52" s="2"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B53" s="2"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B54" s="2"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B55" s="2"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B56" s="2"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B57" s="2"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -1664,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="11">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="N5" s="14">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="11">
-        <v>1600</v>
+        <v>1120</v>
       </c>
       <c r="N6" s="14">
         <v>0</v>
@@ -1765,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="11">
-        <v>3600</v>
+        <v>2120</v>
       </c>
       <c r="N7" s="14">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="11">
-        <v>6400</v>
+        <v>3000</v>
       </c>
       <c r="N8" s="14">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="11">
-        <v>10100</v>
+        <v>12600</v>
       </c>
       <c r="N9" s="14">
         <v>0</v>
@@ -1925,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="11">
-        <v>14500</v>
+        <v>10800</v>
       </c>
       <c r="N10" s="14">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="11">
-        <v>19700</v>
+        <v>18650</v>
       </c>
       <c r="N11" s="14">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="11">
-        <v>25700</v>
+        <v>22050</v>
       </c>
       <c r="N12" s="14">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="11">
-        <v>32600</v>
+        <v>28925</v>
       </c>
       <c r="N13" s="14">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="11">
-        <v>40200</v>
+        <v>34600</v>
       </c>
       <c r="N14" s="14">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="11">
-        <v>48700</v>
+        <v>59600</v>
       </c>
       <c r="N15" s="14">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="11">
-        <v>57900</v>
+        <v>71600</v>
       </c>
       <c r="N16" s="14">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="11">
-        <v>68000</v>
+        <v>78100</v>
       </c>
       <c r="N17" s="14">
         <v>0</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -2005,9 +2005,7 @@
       <c r="C12" s="11">
         <v>1</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>44</v>
-      </c>
+      <c r="D12" s="11"/>
       <c r="E12" s="11">
         <v>8</v>
       </c>
@@ -2059,7 +2057,9 @@
       <c r="C13" s="11">
         <v>1</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="E13" s="11">
         <v>9</v>
       </c>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -587,12 +587,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1670,13 +1670,13 @@
         <v>5</v>
       </c>
       <c r="J5" s="13">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K5" s="13">
         <v>480</v>
       </c>
       <c r="L5" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M5" s="13">
         <v>250</v>
@@ -1720,13 +1720,13 @@
       </c>
       <c r="J6" s="13">
         <f>J5</f>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K6" s="13">
         <v>480</v>
       </c>
       <c r="L6" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M6" s="13">
         <v>1120</v>
@@ -1773,13 +1773,13 @@
       </c>
       <c r="J7" s="13">
         <f t="shared" ref="J7:J38" si="1">J6</f>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K7" s="13">
         <v>480</v>
       </c>
       <c r="L7" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M7" s="13">
         <v>2120</v>
@@ -1828,13 +1828,13 @@
       </c>
       <c r="J8" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K8" s="13">
         <v>480</v>
       </c>
       <c r="L8" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M8" s="13">
         <v>3000</v>
@@ -1881,13 +1881,13 @@
       </c>
       <c r="J9" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K9" s="13">
         <v>480</v>
       </c>
       <c r="L9" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M9" s="13">
         <v>12600</v>
@@ -1936,13 +1936,13 @@
       </c>
       <c r="J10" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K10" s="13">
         <v>480</v>
       </c>
       <c r="L10" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M10" s="13">
         <v>10800</v>
@@ -1991,13 +1991,13 @@
       </c>
       <c r="J11" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K11" s="13">
         <v>480</v>
       </c>
       <c r="L11" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M11" s="13">
         <v>18650</v>
@@ -2044,13 +2044,13 @@
       </c>
       <c r="J12" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K12" s="13">
         <v>480</v>
       </c>
       <c r="L12" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M12" s="13">
         <v>22050</v>
@@ -2099,13 +2099,13 @@
       </c>
       <c r="J13" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K13" s="13">
         <v>480</v>
       </c>
       <c r="L13" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M13" s="13">
         <v>28925</v>
@@ -2152,13 +2152,13 @@
       </c>
       <c r="J14" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K14" s="13">
         <v>480</v>
       </c>
       <c r="L14" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M14" s="13">
         <v>34600</v>
@@ -2205,13 +2205,13 @@
       </c>
       <c r="J15" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="13">
         <v>480</v>
       </c>
       <c r="L15" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M15" s="13">
         <v>59600</v>
@@ -2260,13 +2260,13 @@
       </c>
       <c r="J16" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K16" s="13">
         <v>480</v>
       </c>
       <c r="L16" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M16" s="13">
         <v>71600</v>
@@ -2313,13 +2313,13 @@
       </c>
       <c r="J17" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K17" s="13">
         <v>480</v>
       </c>
       <c r="L17" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M17" s="13">
         <v>78100</v>
@@ -2366,13 +2366,13 @@
       </c>
       <c r="J18" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K18" s="13">
         <v>480</v>
       </c>
       <c r="L18" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M18" s="13">
         <v>78800</v>
@@ -2419,13 +2419,13 @@
       </c>
       <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K19" s="13">
         <v>480</v>
       </c>
       <c r="L19" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M19" s="13">
         <v>90500</v>
@@ -2474,13 +2474,13 @@
       </c>
       <c r="J20" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K20" s="13">
         <v>480</v>
       </c>
       <c r="L20" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M20" s="13">
         <v>103000</v>
@@ -2527,13 +2527,13 @@
       </c>
       <c r="J21" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K21" s="13">
         <v>480</v>
       </c>
       <c r="L21" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M21" s="13">
         <v>116300</v>
@@ -2580,13 +2580,13 @@
       </c>
       <c r="J22" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="13">
         <v>480</v>
       </c>
       <c r="L22" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M22" s="13">
         <v>130300</v>
@@ -2633,13 +2633,13 @@
       </c>
       <c r="J23" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K23" s="13">
         <v>480</v>
       </c>
       <c r="L23" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M23" s="13">
         <v>145200</v>
@@ -2688,13 +2688,13 @@
       </c>
       <c r="J24" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K24" s="13">
         <v>480</v>
       </c>
       <c r="L24" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M24" s="13">
         <v>160900</v>
@@ -2741,13 +2741,13 @@
       </c>
       <c r="J25" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K25" s="13">
         <v>480</v>
       </c>
       <c r="L25" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M25" s="13">
         <v>177400</v>
@@ -2794,13 +2794,13 @@
       </c>
       <c r="J26" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K26" s="13">
         <v>480</v>
       </c>
       <c r="L26" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M26" s="13">
         <v>194700</v>
@@ -2847,13 +2847,13 @@
       </c>
       <c r="J27" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="13">
         <v>480</v>
       </c>
       <c r="L27" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M27" s="13">
         <v>212800</v>
@@ -2902,13 +2902,13 @@
       </c>
       <c r="J28" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K28" s="13">
         <v>480</v>
       </c>
       <c r="L28" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M28" s="13">
         <v>231700</v>
@@ -2955,13 +2955,13 @@
       </c>
       <c r="J29" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K29" s="13">
         <v>480</v>
       </c>
       <c r="L29" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M29" s="13">
         <v>251400</v>
@@ -3008,13 +3008,13 @@
       </c>
       <c r="J30" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K30" s="13">
         <v>480</v>
       </c>
       <c r="L30" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M30" s="13">
         <v>271900</v>
@@ -3061,13 +3061,13 @@
       </c>
       <c r="J31" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K31" s="13">
         <v>480</v>
       </c>
       <c r="L31" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M31" s="13">
         <v>293300</v>
@@ -3116,13 +3116,13 @@
       </c>
       <c r="J32" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K32" s="13">
         <v>480</v>
       </c>
       <c r="L32" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M32" s="13">
         <v>315400</v>
@@ -3169,13 +3169,13 @@
       </c>
       <c r="J33" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K33" s="13">
         <v>480</v>
       </c>
       <c r="L33" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M33" s="13">
         <v>338300</v>
@@ -3222,13 +3222,13 @@
       </c>
       <c r="J34" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K34" s="13">
         <v>480</v>
       </c>
       <c r="L34" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M34" s="13">
         <v>362100</v>
@@ -3275,13 +3275,13 @@
       </c>
       <c r="J35" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K35" s="13">
         <v>480</v>
       </c>
       <c r="L35" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M35" s="13">
         <v>386600</v>
@@ -3330,13 +3330,13 @@
       </c>
       <c r="J36" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K36" s="13">
         <v>480</v>
       </c>
       <c r="L36" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M36" s="13">
         <v>411900</v>
@@ -3383,13 +3383,13 @@
       </c>
       <c r="J37" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K37" s="13">
         <v>480</v>
       </c>
       <c r="L37" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M37" s="13">
         <v>438100</v>
@@ -3436,13 +3436,13 @@
       </c>
       <c r="J38" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K38" s="13">
         <v>480</v>
       </c>
       <c r="L38" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M38" s="13">
         <v>465000</v>
@@ -3489,13 +3489,13 @@
       </c>
       <c r="J39" s="13">
         <f t="shared" ref="J39:J70" si="2">J38</f>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K39" s="13">
         <v>480</v>
       </c>
       <c r="L39" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M39" s="13">
         <v>492800</v>
@@ -3544,13 +3544,13 @@
       </c>
       <c r="J40" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K40" s="13">
         <v>480</v>
       </c>
       <c r="L40" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M40" s="13">
         <v>521400</v>
@@ -3597,13 +3597,13 @@
       </c>
       <c r="J41" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K41" s="13">
         <v>480</v>
       </c>
       <c r="L41" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M41" s="13">
         <v>550700</v>
@@ -3650,13 +3650,13 @@
       </c>
       <c r="J42" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K42" s="13">
         <v>480</v>
       </c>
       <c r="L42" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M42" s="13">
         <v>580900</v>
@@ -3703,13 +3703,13 @@
       </c>
       <c r="J43" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K43" s="13">
         <v>480</v>
       </c>
       <c r="L43" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M43" s="13">
         <v>611900</v>
@@ -3758,13 +3758,13 @@
       </c>
       <c r="J44" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K44" s="13">
         <v>480</v>
       </c>
       <c r="L44" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M44" s="13">
         <v>643700</v>
@@ -3811,13 +3811,13 @@
       </c>
       <c r="J45" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K45" s="13">
         <v>480</v>
       </c>
       <c r="L45" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M45" s="13">
         <v>676200</v>
@@ -3864,13 +3864,13 @@
       </c>
       <c r="J46" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K46" s="13">
         <v>480</v>
       </c>
       <c r="L46" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M46" s="13">
         <v>709600</v>
@@ -3917,13 +3917,13 @@
       </c>
       <c r="J47" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K47" s="13">
         <v>480</v>
       </c>
       <c r="L47" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M47" s="13">
         <v>743800</v>
@@ -3972,13 +3972,13 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K48" s="13">
         <v>480</v>
       </c>
       <c r="L48" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M48" s="13">
         <v>778800</v>
@@ -4025,13 +4025,13 @@
       </c>
       <c r="J49" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K49" s="13">
         <v>480</v>
       </c>
       <c r="L49" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M49" s="13">
         <v>814600</v>
@@ -4078,13 +4078,13 @@
       </c>
       <c r="J50" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K50" s="13">
         <v>480</v>
       </c>
       <c r="L50" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M50" s="13">
         <v>851200</v>
@@ -4131,13 +4131,13 @@
       </c>
       <c r="J51" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K51" s="13">
         <v>480</v>
       </c>
       <c r="L51" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M51" s="13">
         <v>888700</v>
@@ -4184,13 +4184,13 @@
       </c>
       <c r="J52" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K52" s="13">
         <v>480</v>
       </c>
       <c r="L52" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M52" s="13">
         <v>926900</v>
@@ -4237,13 +4237,13 @@
       </c>
       <c r="J53" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K53" s="13">
         <v>480</v>
       </c>
       <c r="L53" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M53" s="13">
         <v>965900</v>
@@ -4290,13 +4290,13 @@
       </c>
       <c r="J54" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K54" s="13">
         <v>480</v>
       </c>
       <c r="L54" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M54" s="13">
         <v>1005700</v>
@@ -4343,13 +4343,13 @@
       </c>
       <c r="J55" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K55" s="13">
         <v>480</v>
       </c>
       <c r="L55" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M55" s="13">
         <v>1046400</v>
@@ -4396,13 +4396,13 @@
       </c>
       <c r="J56" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K56" s="13">
         <v>480</v>
       </c>
       <c r="L56" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M56" s="13">
         <v>1087800</v>
@@ -4449,13 +4449,13 @@
       </c>
       <c r="J57" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K57" s="13">
         <v>480</v>
       </c>
       <c r="L57" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M57" s="13">
         <v>1130000</v>
@@ -4502,13 +4502,13 @@
       </c>
       <c r="J58" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K58" s="13">
         <v>480</v>
       </c>
       <c r="L58" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M58" s="13">
         <v>1173100</v>
@@ -4555,13 +4555,13 @@
       </c>
       <c r="J59" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K59" s="13">
         <v>480</v>
       </c>
       <c r="L59" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M59" s="13">
         <v>1216900</v>
@@ -4608,13 +4608,13 @@
       </c>
       <c r="J60" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K60" s="13">
         <v>480</v>
       </c>
       <c r="L60" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M60" s="13">
         <v>1261600</v>
@@ -4661,13 +4661,13 @@
       </c>
       <c r="J61" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K61" s="13">
         <v>480</v>
       </c>
       <c r="L61" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M61" s="13">
         <v>1307000</v>
@@ -4714,13 +4714,13 @@
       </c>
       <c r="J62" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K62" s="13">
         <v>480</v>
       </c>
       <c r="L62" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M62" s="13">
         <v>1353300</v>
@@ -4767,13 +4767,13 @@
       </c>
       <c r="J63" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K63" s="13">
         <v>480</v>
       </c>
       <c r="L63" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M63" s="13">
         <v>1400400</v>
@@ -4820,13 +4820,13 @@
       </c>
       <c r="J64" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K64" s="13">
         <v>480</v>
       </c>
       <c r="L64" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M64" s="13">
         <v>1448200</v>
@@ -4874,13 +4874,13 @@
       </c>
       <c r="J65" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K65" s="13">
         <v>480</v>
       </c>
       <c r="L65" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M65" s="13">
         <v>1496900</v>
@@ -4928,13 +4928,13 @@
       </c>
       <c r="J66" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K66" s="13">
         <v>480</v>
       </c>
       <c r="L66" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M66" s="13">
         <v>1546400</v>
@@ -4982,13 +4982,13 @@
       </c>
       <c r="J67" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K67" s="13">
         <v>480</v>
       </c>
       <c r="L67" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M67" s="13">
         <v>1596700</v>
@@ -5036,13 +5036,13 @@
       </c>
       <c r="J68" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K68" s="13">
         <v>480</v>
       </c>
       <c r="L68" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M68" s="13">
         <v>1647800</v>
@@ -5090,13 +5090,13 @@
       </c>
       <c r="J69" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K69" s="13">
         <v>480</v>
       </c>
       <c r="L69" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M69" s="13">
         <v>1699700</v>
@@ -5144,13 +5144,13 @@
       </c>
       <c r="J70" s="13">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K70" s="13">
         <v>480</v>
       </c>
       <c r="L70" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M70" s="13">
         <v>1752400</v>
@@ -5197,14 +5197,14 @@
         <v>5</v>
       </c>
       <c r="J71" s="13">
-        <f t="shared" ref="J71:J102" si="5">J70</f>
-        <v>1.6</v>
+        <f t="shared" ref="J71:J103" si="5">J70</f>
+        <v>8</v>
       </c>
       <c r="K71" s="13">
         <v>480</v>
       </c>
       <c r="L71" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M71" s="13">
         <v>1805900</v>
@@ -5252,13 +5252,13 @@
       </c>
       <c r="J72" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K72" s="13">
         <v>480</v>
       </c>
       <c r="L72" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M72" s="13">
         <v>1860200</v>
@@ -5306,13 +5306,13 @@
       </c>
       <c r="J73" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K73" s="13">
         <v>480</v>
       </c>
       <c r="L73" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M73" s="13">
         <v>1915300</v>
@@ -5360,13 +5360,13 @@
       </c>
       <c r="J74" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K74" s="13">
         <v>480</v>
       </c>
       <c r="L74" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M74" s="13">
         <v>1971200</v>
@@ -5414,13 +5414,13 @@
       </c>
       <c r="J75" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K75" s="13">
         <v>480</v>
       </c>
       <c r="L75" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M75" s="13">
         <v>2027900</v>
@@ -5468,13 +5468,13 @@
       </c>
       <c r="J76" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K76" s="13">
         <v>480</v>
       </c>
       <c r="L76" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M76" s="13">
         <v>2085500</v>
@@ -5522,13 +5522,13 @@
       </c>
       <c r="J77" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K77" s="13">
         <v>480</v>
       </c>
       <c r="L77" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M77" s="13">
         <v>2143800</v>
@@ -5576,13 +5576,13 @@
       </c>
       <c r="J78" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K78" s="13">
         <v>480</v>
       </c>
       <c r="L78" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M78" s="13">
         <v>2202900</v>
@@ -5630,13 +5630,13 @@
       </c>
       <c r="J79" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K79" s="13">
         <v>480</v>
       </c>
       <c r="L79" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M79" s="13">
         <v>2262900</v>
@@ -5684,13 +5684,13 @@
       </c>
       <c r="J80" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K80" s="13">
         <v>480</v>
       </c>
       <c r="L80" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M80" s="13">
         <v>2323600</v>
@@ -5738,13 +5738,13 @@
       </c>
       <c r="J81" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K81" s="13">
         <v>480</v>
       </c>
       <c r="L81" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M81" s="13">
         <v>2385200</v>
@@ -5792,13 +5792,13 @@
       </c>
       <c r="J82" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K82" s="13">
         <v>480</v>
       </c>
       <c r="L82" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M82" s="13">
         <v>2447500</v>
@@ -5846,13 +5846,13 @@
       </c>
       <c r="J83" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K83" s="13">
         <v>480</v>
       </c>
       <c r="L83" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M83" s="13">
         <v>2510700</v>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="J84" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K84" s="13">
         <v>480</v>
       </c>
       <c r="L84" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M84" s="13">
         <v>2574600</v>
@@ -5954,13 +5954,13 @@
       </c>
       <c r="J85" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K85" s="13">
         <v>480</v>
       </c>
       <c r="L85" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M85" s="13">
         <v>2639400</v>
@@ -6008,13 +6008,13 @@
       </c>
       <c r="J86" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K86" s="13">
         <v>480</v>
       </c>
       <c r="L86" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M86" s="13">
         <v>2705000</v>
@@ -6062,13 +6062,13 @@
       </c>
       <c r="J87" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K87" s="13">
         <v>480</v>
       </c>
       <c r="L87" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M87" s="13">
         <v>2771400</v>
@@ -6116,13 +6116,13 @@
       </c>
       <c r="J88" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K88" s="13">
         <v>480</v>
       </c>
       <c r="L88" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M88" s="13">
         <v>2838500</v>
@@ -6170,13 +6170,13 @@
       </c>
       <c r="J89" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K89" s="13">
         <v>480</v>
       </c>
       <c r="L89" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M89" s="13">
         <v>2906500</v>
@@ -6224,13 +6224,13 @@
       </c>
       <c r="J90" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K90" s="13">
         <v>480</v>
       </c>
       <c r="L90" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M90" s="13">
         <v>2975300</v>
@@ -6278,13 +6278,13 @@
       </c>
       <c r="J91" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K91" s="13">
         <v>480</v>
       </c>
       <c r="L91" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M91" s="13">
         <v>3044900</v>
@@ -6332,13 +6332,13 @@
       </c>
       <c r="J92" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K92" s="13">
         <v>480</v>
       </c>
       <c r="L92" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M92" s="13">
         <v>3115300</v>
@@ -6386,13 +6386,13 @@
       </c>
       <c r="J93" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K93" s="13">
         <v>480</v>
       </c>
       <c r="L93" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M93" s="13">
         <v>3186500</v>
@@ -6440,13 +6440,13 @@
       </c>
       <c r="J94" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K94" s="13">
         <v>480</v>
       </c>
       <c r="L94" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M94" s="13">
         <v>3258500</v>
@@ -6494,13 +6494,13 @@
       </c>
       <c r="J95" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K95" s="13">
         <v>480</v>
       </c>
       <c r="L95" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M95" s="13">
         <v>3331300</v>
@@ -6548,13 +6548,13 @@
       </c>
       <c r="J96" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K96" s="13">
         <v>480</v>
       </c>
       <c r="L96" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M96" s="13">
         <v>3405000</v>
@@ -6602,13 +6602,13 @@
       </c>
       <c r="J97" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K97" s="13">
         <v>480</v>
       </c>
       <c r="L97" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M97" s="13">
         <v>3479400</v>
@@ -6656,13 +6656,13 @@
       </c>
       <c r="J98" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K98" s="13">
         <v>480</v>
       </c>
       <c r="L98" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M98" s="13">
         <v>3554600</v>
@@ -6710,13 +6710,13 @@
       </c>
       <c r="J99" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K99" s="13">
         <v>480</v>
       </c>
       <c r="L99" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M99" s="13">
         <v>3630700</v>
@@ -6764,13 +6764,13 @@
       </c>
       <c r="J100" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K100" s="13">
         <v>480</v>
       </c>
       <c r="L100" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M100" s="13">
         <v>3707500</v>
@@ -6818,13 +6818,13 @@
       </c>
       <c r="J101" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K101" s="13">
         <v>480</v>
       </c>
       <c r="L101" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M101" s="13">
         <v>3785100</v>
@@ -6872,13 +6872,13 @@
       </c>
       <c r="J102" s="13">
         <f t="shared" si="5"/>
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="K102" s="13">
         <v>480</v>
       </c>
       <c r="L102" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M102" s="13">
         <v>3863600</v>
@@ -6925,14 +6925,14 @@
         <v>5</v>
       </c>
       <c r="J103" s="13">
-        <f>J102</f>
-        <v>1.6</v>
+        <f t="shared" si="5"/>
+        <v>8</v>
       </c>
       <c r="K103" s="13">
         <v>480</v>
       </c>
       <c r="L103" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M103" s="13">
         <v>99999999</v>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoStatsSheet" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -323,16 +323,22 @@
     <t>1301_3|1101_3|1102_3</t>
   </si>
   <si>
+    <t>1303_1</t>
+  </si>
+  <si>
     <t>1301_4|1101_4|1102_4|1202_3</t>
   </si>
   <si>
-    <t>1303_1|1304_1</t>
+    <t>1304_1</t>
   </si>
   <si>
     <t>1301_5|1101_5|1102_5|1202_4</t>
   </si>
   <si>
     <t>1102_1</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>1110_1</t>
@@ -1863,7 +1869,9 @@
       <c r="C9" s="13">
         <v>1</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="13" t="s">
+        <v>40</v>
+      </c>
       <c r="E9" s="13">
         <v>5</v>
       </c>
@@ -1899,7 +1907,7 @@
         <v>100</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q9" s="4">
         <v>5</v>
@@ -1917,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="13">
         <v>6</v>
@@ -1954,7 +1962,7 @@
         <v>110</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q10" s="4">
         <v>5</v>
@@ -1972,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" s="13">
         <v>7</v>
@@ -2009,7 +2017,7 @@
         <v>120</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q11" s="4">
         <v>6</v>
@@ -2026,7 +2034,9 @@
       <c r="C12" s="13">
         <v>1</v>
       </c>
-      <c r="D12" s="13"/>
+      <c r="D12" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E12" s="13">
         <v>8</v>
       </c>
@@ -2062,7 +2072,7 @@
         <v>130</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q12" s="4">
         <v>6</v>
@@ -2080,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" s="13">
         <v>9</v>
@@ -2117,7 +2127,7 @@
         <v>140</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q13" s="4">
         <v>6</v>
@@ -2134,7 +2144,9 @@
       <c r="C14" s="13">
         <v>1</v>
       </c>
-      <c r="D14" s="13"/>
+      <c r="D14" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E14" s="13">
         <v>10</v>
       </c>
@@ -2170,7 +2182,7 @@
         <v>150</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q14" s="4">
         <v>6</v>
@@ -2187,7 +2199,9 @@
       <c r="C15" s="13">
         <v>1</v>
       </c>
-      <c r="D15" s="13"/>
+      <c r="D15" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E15" s="13">
         <v>11</v>
       </c>
@@ -2223,7 +2237,7 @@
         <v>160</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q15" s="4">
         <v>7</v>
@@ -2241,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" s="13">
         <v>12</v>
@@ -2278,7 +2292,7 @@
         <v>170</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q16" s="4">
         <v>7</v>
@@ -2295,7 +2309,9 @@
       <c r="C17" s="13">
         <v>1</v>
       </c>
-      <c r="D17" s="13"/>
+      <c r="D17" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E17" s="13">
         <v>13</v>
       </c>
@@ -2331,7 +2347,7 @@
         <v>180</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q17" s="4">
         <v>7</v>
@@ -2348,7 +2364,9 @@
       <c r="C18" s="13">
         <v>1</v>
       </c>
-      <c r="D18" s="13"/>
+      <c r="D18" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E18" s="13">
         <v>14</v>
       </c>
@@ -2384,7 +2402,7 @@
         <v>190</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q18" s="4">
         <v>7</v>
@@ -2401,7 +2419,9 @@
       <c r="C19" s="13">
         <v>1</v>
       </c>
-      <c r="D19" s="13"/>
+      <c r="D19" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E19" s="13">
         <v>15</v>
       </c>
@@ -2437,7 +2457,7 @@
         <v>200</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q19" s="4">
         <v>7</v>
@@ -2455,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="13">
         <v>16</v>
@@ -2492,7 +2512,7 @@
         <v>210</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q20" s="4">
         <v>7</v>
@@ -2509,7 +2529,9 @@
       <c r="C21" s="13">
         <v>1</v>
       </c>
-      <c r="D21" s="13"/>
+      <c r="D21" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="E21" s="13">
         <v>17</v>
       </c>
@@ -2545,7 +2567,7 @@
         <v>220</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q21" s="4">
         <v>8</v>
@@ -2562,7 +2584,9 @@
       <c r="C22" s="13">
         <v>1</v>
       </c>
-      <c r="D22" s="13"/>
+      <c r="D22" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E22" s="13">
         <v>18</v>
       </c>
@@ -2598,7 +2622,7 @@
         <v>230</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q22" s="4">
         <v>8</v>
@@ -2615,7 +2639,9 @@
       <c r="C23" s="13">
         <v>1</v>
       </c>
-      <c r="D23" s="13"/>
+      <c r="D23" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E23" s="13">
         <v>19</v>
       </c>
@@ -2651,7 +2677,7 @@
         <v>240</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q23" s="4">
         <v>8</v>
@@ -2669,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E24" s="13">
         <v>20</v>
@@ -2706,7 +2732,7 @@
         <v>250</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q24" s="4">
         <v>8</v>
@@ -2723,7 +2749,9 @@
       <c r="C25" s="13">
         <v>1</v>
       </c>
-      <c r="D25" s="13"/>
+      <c r="D25" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E25" s="13">
         <v>21</v>
       </c>
@@ -2759,7 +2787,7 @@
         <v>260</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q25" s="4">
         <v>8</v>
@@ -2776,7 +2804,9 @@
       <c r="C26" s="13">
         <v>1</v>
       </c>
-      <c r="D26" s="13"/>
+      <c r="D26" s="13" t="s">
+        <v>48</v>
+      </c>
       <c r="E26" s="13">
         <v>22</v>
       </c>
@@ -2812,7 +2842,7 @@
         <v>270</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q26" s="4">
         <v>8</v>
@@ -2829,7 +2859,9 @@
       <c r="C27" s="13">
         <v>1</v>
       </c>
-      <c r="D27" s="13"/>
+      <c r="D27" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E27" s="13">
         <v>23</v>
       </c>
@@ -2865,7 +2897,7 @@
         <v>280</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q27" s="4">
         <v>9</v>
@@ -2883,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E28" s="13">
         <v>24</v>
@@ -2920,7 +2952,7 @@
         <v>290</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q28" s="4">
         <v>9</v>
@@ -2937,7 +2969,9 @@
       <c r="C29" s="13">
         <v>1</v>
       </c>
-      <c r="D29" s="13"/>
+      <c r="D29" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E29" s="13">
         <v>25</v>
       </c>
@@ -2973,7 +3007,7 @@
         <v>300</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q29" s="4">
         <v>9</v>
@@ -2990,7 +3024,9 @@
       <c r="C30" s="13">
         <v>1</v>
       </c>
-      <c r="D30" s="13"/>
+      <c r="D30" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E30" s="13">
         <v>26</v>
       </c>
@@ -3026,7 +3062,7 @@
         <v>310</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q30" s="4">
         <v>9</v>
@@ -3043,7 +3079,9 @@
       <c r="C31" s="13">
         <v>1</v>
       </c>
-      <c r="D31" s="13"/>
+      <c r="D31" s="13" t="s">
+        <v>49</v>
+      </c>
       <c r="E31" s="13">
         <v>27</v>
       </c>
@@ -3079,7 +3117,7 @@
         <v>320</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q31" s="4">
         <v>9</v>
@@ -3097,7 +3135,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E32" s="13">
         <v>28</v>
@@ -3134,7 +3172,7 @@
         <v>330</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q32" s="4">
         <v>9</v>
@@ -3151,7 +3189,9 @@
       <c r="C33" s="13">
         <v>1</v>
       </c>
-      <c r="D33" s="13"/>
+      <c r="D33" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E33" s="13">
         <v>29</v>
       </c>
@@ -3187,7 +3227,7 @@
         <v>340</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q33" s="4">
         <v>9</v>
@@ -3204,7 +3244,9 @@
       <c r="C34" s="13">
         <v>1</v>
       </c>
-      <c r="D34" s="13"/>
+      <c r="D34" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E34" s="13">
         <v>30</v>
       </c>
@@ -3240,7 +3282,7 @@
         <v>350</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q34" s="4">
         <v>10</v>
@@ -3257,7 +3299,9 @@
       <c r="C35" s="13">
         <v>1</v>
       </c>
-      <c r="D35" s="13"/>
+      <c r="D35" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E35" s="13">
         <v>31</v>
       </c>
@@ -3293,7 +3337,7 @@
         <v>360</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q35" s="4">
         <v>10</v>
@@ -3348,7 +3392,7 @@
         <v>370</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q36" s="4">
         <v>10</v>
@@ -3365,7 +3409,9 @@
       <c r="C37" s="13">
         <v>1</v>
       </c>
-      <c r="D37" s="13"/>
+      <c r="D37" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E37" s="13">
         <v>33</v>
       </c>
@@ -3401,7 +3447,7 @@
         <v>380</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q37" s="4">
         <v>10</v>
@@ -3418,7 +3464,9 @@
       <c r="C38" s="13">
         <v>1</v>
       </c>
-      <c r="D38" s="13"/>
+      <c r="D38" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E38" s="13">
         <v>34</v>
       </c>
@@ -3454,7 +3502,7 @@
         <v>390</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q38" s="4">
         <v>10</v>
@@ -3471,7 +3519,9 @@
       <c r="C39" s="13">
         <v>1</v>
       </c>
-      <c r="D39" s="13"/>
+      <c r="D39" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E39" s="13">
         <v>35</v>
       </c>
@@ -3507,7 +3557,7 @@
         <v>400</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q39" s="4">
         <v>10</v>
@@ -3525,7 +3575,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E40" s="13">
         <v>36</v>
@@ -3562,7 +3612,7 @@
         <v>410</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q40" s="4">
         <v>10</v>
@@ -3579,7 +3629,9 @@
       <c r="C41" s="13">
         <v>1</v>
       </c>
-      <c r="D41" s="13"/>
+      <c r="D41" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="E41" s="13">
         <v>37</v>
       </c>
@@ -3615,7 +3667,7 @@
         <v>420</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q41" s="4">
         <v>11</v>
@@ -3632,7 +3684,9 @@
       <c r="C42" s="13">
         <v>1</v>
       </c>
-      <c r="D42" s="13"/>
+      <c r="D42" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E42" s="13">
         <v>38</v>
       </c>
@@ -3668,7 +3722,7 @@
         <v>430</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q42" s="4">
         <v>11</v>
@@ -3685,7 +3739,9 @@
       <c r="C43" s="13">
         <v>1</v>
       </c>
-      <c r="D43" s="13"/>
+      <c r="D43" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E43" s="13">
         <v>39</v>
       </c>
@@ -3721,7 +3777,7 @@
         <v>440</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q43" s="4">
         <v>11</v>
@@ -3739,7 +3795,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E44" s="13">
         <v>40</v>
@@ -3776,7 +3832,7 @@
         <v>450</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q44" s="4">
         <v>11</v>
@@ -3793,7 +3849,9 @@
       <c r="C45" s="13">
         <v>1</v>
       </c>
-      <c r="D45" s="13"/>
+      <c r="D45" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E45" s="13">
         <v>41</v>
       </c>
@@ -3829,7 +3887,7 @@
         <v>460</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q45" s="4">
         <v>11</v>
@@ -3846,7 +3904,9 @@
       <c r="C46" s="13">
         <v>1</v>
       </c>
-      <c r="D46" s="13"/>
+      <c r="D46" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="E46" s="13">
         <v>42</v>
       </c>
@@ -3882,7 +3942,7 @@
         <v>470</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q46" s="4">
         <v>11</v>
@@ -3899,7 +3959,9 @@
       <c r="C47" s="13">
         <v>1</v>
       </c>
-      <c r="D47" s="13"/>
+      <c r="D47" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E47" s="13">
         <v>43</v>
       </c>
@@ -3935,7 +3997,7 @@
         <v>480</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q47" s="4">
         <v>12</v>
@@ -3953,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E48" s="13">
         <v>44</v>
@@ -3990,7 +4052,7 @@
         <v>490</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q48" s="4">
         <v>12</v>
@@ -4007,7 +4069,9 @@
       <c r="C49" s="13">
         <v>1</v>
       </c>
-      <c r="D49" s="13"/>
+      <c r="D49" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E49" s="13">
         <v>45</v>
       </c>
@@ -4043,7 +4107,7 @@
         <v>500</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q49" s="4">
         <v>12</v>
@@ -4060,7 +4124,9 @@
       <c r="C50" s="13">
         <v>1</v>
       </c>
-      <c r="D50" s="13"/>
+      <c r="D50" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E50" s="13">
         <v>46</v>
       </c>
@@ -4096,7 +4162,7 @@
         <v>510</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q50" s="4">
         <v>12</v>
@@ -4113,7 +4179,9 @@
       <c r="C51" s="13">
         <v>1</v>
       </c>
-      <c r="D51" s="13"/>
+      <c r="D51" s="13" t="s">
+        <v>53</v>
+      </c>
       <c r="E51" s="13">
         <v>47</v>
       </c>
@@ -4149,7 +4217,7 @@
         <v>520</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q51" s="4">
         <v>12</v>
@@ -4166,7 +4234,9 @@
       <c r="C52" s="13">
         <v>1</v>
       </c>
-      <c r="D52" s="13"/>
+      <c r="D52" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E52" s="13">
         <v>48</v>
       </c>
@@ -4202,7 +4272,7 @@
         <v>530</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q52" s="4">
         <v>12</v>
@@ -4219,7 +4289,9 @@
       <c r="C53" s="13">
         <v>1</v>
       </c>
-      <c r="D53" s="13"/>
+      <c r="D53" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E53" s="13">
         <v>49</v>
       </c>
@@ -4255,7 +4327,7 @@
         <v>540</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q53" s="4">
         <v>12</v>
@@ -4272,7 +4344,9 @@
       <c r="C54" s="13">
         <v>1</v>
       </c>
-      <c r="D54" s="13"/>
+      <c r="D54" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E54" s="13">
         <v>50</v>
       </c>
@@ -4308,7 +4382,7 @@
         <v>550</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q54" s="4">
         <v>12</v>
@@ -4325,7 +4399,9 @@
       <c r="C55" s="13">
         <v>1</v>
       </c>
-      <c r="D55" s="13"/>
+      <c r="D55" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E55" s="13">
         <v>51</v>
       </c>
@@ -4361,7 +4437,7 @@
         <v>560</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q55" s="4">
         <v>13</v>
@@ -4378,7 +4454,9 @@
       <c r="C56" s="13">
         <v>1</v>
       </c>
-      <c r="D56" s="13"/>
+      <c r="D56" s="13" t="s">
+        <v>54</v>
+      </c>
       <c r="E56" s="13">
         <v>52</v>
       </c>
@@ -4414,7 +4492,7 @@
         <v>570</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q56" s="4">
         <v>13</v>
@@ -4431,7 +4509,9 @@
       <c r="C57" s="13">
         <v>1</v>
       </c>
-      <c r="D57" s="13"/>
+      <c r="D57" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E57" s="13">
         <v>53</v>
       </c>
@@ -4467,7 +4547,7 @@
         <v>580</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q57" s="4">
         <v>13</v>
@@ -4484,7 +4564,9 @@
       <c r="C58" s="13">
         <v>1</v>
       </c>
-      <c r="D58" s="13"/>
+      <c r="D58" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E58" s="13">
         <v>54</v>
       </c>
@@ -4520,7 +4602,7 @@
         <v>590</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q58" s="4">
         <v>13</v>
@@ -4537,7 +4619,9 @@
       <c r="C59" s="13">
         <v>1</v>
       </c>
-      <c r="D59" s="13"/>
+      <c r="D59" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E59" s="13">
         <v>55</v>
       </c>
@@ -4573,7 +4657,7 @@
         <v>600</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q59" s="4">
         <v>13</v>
@@ -4590,7 +4674,9 @@
       <c r="C60" s="13">
         <v>1</v>
       </c>
-      <c r="D60" s="13"/>
+      <c r="D60" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E60" s="13">
         <v>56</v>
       </c>
@@ -4626,7 +4712,7 @@
         <v>610</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q60" s="4">
         <v>14</v>
@@ -4643,7 +4729,9 @@
       <c r="C61" s="13">
         <v>1</v>
       </c>
-      <c r="D61" s="13"/>
+      <c r="D61" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="E61" s="13">
         <v>57</v>
       </c>
@@ -4679,7 +4767,7 @@
         <v>620</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q61" s="4">
         <v>14</v>
@@ -4732,7 +4820,7 @@
         <v>630</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q62" s="4">
         <v>14</v>
@@ -4785,7 +4873,7 @@
         <v>640</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q63" s="4">
         <v>14</v>
@@ -4838,7 +4926,7 @@
         <v>650</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q64" s="4">
         <v>14</v>
@@ -4892,7 +4980,7 @@
         <v>660</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q65" s="4">
         <v>14</v>
@@ -4946,7 +5034,7 @@
         <v>670</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q66" s="4">
         <v>14</v>
@@ -5000,7 +5088,7 @@
         <v>680</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q67" s="4">
         <v>14</v>
@@ -5054,7 +5142,7 @@
         <v>690</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q68" s="4">
         <v>14</v>
@@ -5108,7 +5196,7 @@
         <v>700</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q69" s="4">
         <v>14</v>
@@ -5162,7 +5250,7 @@
         <v>710</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q70" s="4">
         <v>14</v>
@@ -5216,7 +5304,7 @@
         <v>720</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q71" s="4">
         <v>14</v>
@@ -5270,7 +5358,7 @@
         <v>730</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q72" s="4">
         <v>14</v>
@@ -5324,7 +5412,7 @@
         <v>740</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q73" s="4">
         <v>14</v>
@@ -5378,7 +5466,7 @@
         <v>750</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q74" s="4">
         <v>14</v>
@@ -5432,7 +5520,7 @@
         <v>760</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q75" s="4">
         <v>14</v>
@@ -5486,7 +5574,7 @@
         <v>770</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q76" s="4">
         <v>14</v>
@@ -5540,7 +5628,7 @@
         <v>780</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q77" s="4">
         <v>14</v>
@@ -5594,7 +5682,7 @@
         <v>790</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q78" s="4">
         <v>14</v>
@@ -5648,7 +5736,7 @@
         <v>800</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q79" s="4">
         <v>14</v>
@@ -5702,7 +5790,7 @@
         <v>810</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q80" s="4">
         <v>14</v>
@@ -5756,7 +5844,7 @@
         <v>820</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q81" s="4">
         <v>14</v>
@@ -5810,7 +5898,7 @@
         <v>830</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q82" s="4">
         <v>14</v>
@@ -5864,7 +5952,7 @@
         <v>840</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q83" s="4">
         <v>14</v>
@@ -5918,7 +6006,7 @@
         <v>850</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q84" s="4">
         <v>14</v>
@@ -5972,7 +6060,7 @@
         <v>860</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q85" s="4">
         <v>14</v>
@@ -6026,7 +6114,7 @@
         <v>870</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q86" s="4">
         <v>14</v>
@@ -6080,7 +6168,7 @@
         <v>880</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q87" s="4">
         <v>14</v>
@@ -6134,7 +6222,7 @@
         <v>890</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q88" s="4">
         <v>14</v>
@@ -6188,7 +6276,7 @@
         <v>900</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q89" s="4">
         <v>14</v>
@@ -6242,7 +6330,7 @@
         <v>910</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q90" s="4">
         <v>14</v>
@@ -6296,7 +6384,7 @@
         <v>920</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q91" s="4">
         <v>14</v>
@@ -6350,7 +6438,7 @@
         <v>930</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q92" s="4">
         <v>14</v>
@@ -6404,7 +6492,7 @@
         <v>940</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q93" s="4">
         <v>14</v>
@@ -6458,7 +6546,7 @@
         <v>950</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q94" s="4">
         <v>14</v>
@@ -6512,7 +6600,7 @@
         <v>960</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q95" s="4">
         <v>14</v>
@@ -6566,7 +6654,7 @@
         <v>970</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q96" s="4">
         <v>14</v>
@@ -6620,7 +6708,7 @@
         <v>980</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q97" s="4">
         <v>14</v>
@@ -6674,7 +6762,7 @@
         <v>990</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q98" s="4">
         <v>14</v>
@@ -6728,7 +6816,7 @@
         <v>1000</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q99" s="4">
         <v>14</v>
@@ -6782,7 +6870,7 @@
         <v>1010</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q100" s="4">
         <v>14</v>
@@ -6836,7 +6924,7 @@
         <v>1020</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q101" s="4">
         <v>14</v>
@@ -6890,7 +6978,7 @@
         <v>1030</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q102" s="4">
         <v>14</v>
@@ -6944,7 +7032,7 @@
         <v>1040</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q103" s="4">
         <v>14</v>
@@ -7083,7 +7171,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -7104,7 +7192,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -7125,7 +7213,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -7146,7 +7234,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -7167,7 +7255,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7188,7 +7276,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -7209,7 +7297,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -7230,7 +7318,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -7251,7 +7339,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -7272,7 +7360,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7293,7 +7381,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -7314,7 +7402,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -7335,7 +7423,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -7356,251 +7444,251 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B23" s="2"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" s="2"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B28" s="2"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B29" s="2"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B31" s="2"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B32" s="2"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B34" s="2"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B35" s="2"/>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B36" s="2"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B37" s="2"/>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B38" s="2"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B39" s="2"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B40" s="2"/>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B41" s="2"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B42" s="2"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B44" s="2"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B45" s="2"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B46" s="2"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B47" s="2"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B48" s="2"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B49" s="2"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B50" s="2"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B51" s="2"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B52" s="2"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B53" s="2"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B54" s="2"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B55" s="2"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B56" s="2"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B57" s="2"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/CasinoStatsSheet.xlsx
+++ b/hall/resources/sample/CasinoStatsSheet.xlsx
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="115">
   <si>
     <t>ID</t>
   </si>
@@ -311,64 +311,208 @@
     <t>拉斯维加斯</t>
   </si>
   <si>
-    <t>1301_1|1101_1</t>
-  </si>
-  <si>
-    <t>1301_3|1101_2|1102_2</t>
+    <t/>
+  </si>
+  <si>
+    <t>1101_4</t>
   </si>
   <si>
     <t>1202_1</t>
   </si>
   <si>
-    <t>1301_3|1101_3|1102_3</t>
-  </si>
-  <si>
     <t>1303_1</t>
   </si>
   <si>
-    <t>1301_4|1101_4|1102_4|1202_3</t>
+    <t>1101_8</t>
   </si>
   <si>
     <t>1304_1</t>
   </si>
   <si>
-    <t>1301_5|1101_5|1102_5|1202_4</t>
+    <t>1202_3|1101_8</t>
   </si>
   <si>
     <t>1102_1</t>
   </si>
   <si>
-    <t/>
+    <t>1202_3|1101_12</t>
+  </si>
+  <si>
+    <t>1202_3|1303_4|1101_12|1102_4</t>
+  </si>
+  <si>
+    <t>1202_3|1303_4|1101_16|1102_4</t>
+  </si>
+  <si>
+    <t>1202_3|1303_4|1304_5|1101_16|1102_8</t>
+  </si>
+  <si>
+    <t>1301_7|1202_3|1303_4|1304_5|1101_16|1102_8</t>
   </si>
   <si>
     <t>1110_1</t>
   </si>
   <si>
+    <t>1301_7|1202_3|1303_4|1304_5|1101_16|1102_12</t>
+  </si>
+  <si>
+    <t>1301_7|1202_8|1303_4|1304_5|1101_16|1102_12|1110_4</t>
+  </si>
+  <si>
+    <t>1301_7|1202_8|1303_4|1304_5|1101_16|1102_16|1110_4</t>
+  </si>
+  <si>
+    <t>1301_7|1202_8|1303_9|1304_5|1101_16|1102_16|1110_8</t>
+  </si>
+  <si>
     <t>1107_1</t>
   </si>
   <si>
+    <t>1301_7|1202_8|1303_9|1304_10|1101_16|1102_16|1110_12</t>
+  </si>
+  <si>
+    <t>1301_7|1202_8|1303_9|1304_10|1101_16|1102_16|1107_4|1110_12</t>
+  </si>
+  <si>
+    <t>1301_12|1202_8|1303_9|1304_10|1101_16|1102_16|1107_4|1110_16</t>
+  </si>
+  <si>
+    <t>1301_12|1202_8|1303_9|1304_10|1101_16|1102_16|1107_8|1110_16</t>
+  </si>
+  <si>
+    <t>1301_12|1202_13|1303_9|1304_10|1101_16|1102_16|1107_8|1110_16</t>
+  </si>
+  <si>
     <t>1106_1</t>
   </si>
   <si>
+    <t>1301_12|1202_13|1303_9|1304_10|1101_16|1102_16|1107_12|1110_16</t>
+  </si>
+  <si>
+    <t>1301_12|1202_13|1303_14|1304_10|1101_16|1102_16|1106_4|1107_12|1110_16</t>
+  </si>
+  <si>
+    <t>1301_12|1202_13|1303_14|1304_10|1101_16|1102_16|1106_4|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_12|1202_13|1303_14|1304_15|1101_16|1102_16|1106_8|1107_16|1110_16</t>
+  </si>
+  <si>
     <t>1105_1</t>
   </si>
   <si>
+    <t>1301_17|1202_13|1303_14|1304_15|1101_16|1102_16|1106_12|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_17|1202_13|1303_14|1304_15|1101_16|1102_16|1105_4|1106_12|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_17|1202_18|1303_14|1304_15|1101_16|1102_16|1105_4|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_17|1202_18|1303_14|1304_15|1101_16|1102_16|1105_8|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_17|1202_18|1303_19|1304_15|1101_16|1102_16|1105_8|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
     <t>1104_1</t>
   </si>
   <si>
+    <t>1301_17|1202_18|1303_19|1304_15|1101_16|1102_16|1105_12|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_17|1202_18|1303_19|1304_20|1101_16|1102_16|1104_4|1105_12|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_22|1202_18|1303_19|1304_20|1101_16|1102_16|1104_4|1105_16|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_22|1202_18|1303_19|1304_20|1101_16|1102_16|1104_8|1105_16|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_22|1202_23|1303_19|1304_20|1101_16|1102_16|1104_8|1105_16|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
     <t>1103_1</t>
   </si>
   <si>
+    <t>1301_22|1202_23|1303_19|1304_20|1101_16|1102_16|1104_12|1105_16|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_22|1202_23|1303_24|1304_20|1101_16|1102_16|1103_4|1104_12|1105_16|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_22|1202_23|1303_24|1304_20|1101_16|1102_16|1103_4|1104_16|1105_16|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_22|1202_23|1303_24|1304_25|1101_16|1102_16|1103_8|1104_16|1105_16|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
     <t>1109_1</t>
   </si>
   <si>
+    <t>1301_27|1202_23|1303_24|1304_25|1101_16|1102_16|1103_12|1104_16|1105_16|1106_16|1107_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_27|1202_23|1303_24|1304_25|1101_16|1102_16|1103_12|1104_16|1105_16|1106_16|1107_16|1109_4|1110_16</t>
+  </si>
+  <si>
+    <t>1301_27|1202_28|1303_24|1304_25|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1109_4|1110_16</t>
+  </si>
+  <si>
+    <t>1301_27|1202_28|1303_24|1304_25|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1109_8|1110_16</t>
+  </si>
+  <si>
+    <t>1301_27|1202_28|1303_29|1304_25|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1109_8|1110_16</t>
+  </si>
+  <si>
     <t>1108_1</t>
   </si>
   <si>
+    <t>1301_27|1202_28|1303_29|1304_25|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1109_12|1110_16</t>
+  </si>
+  <si>
+    <t>1301_27|1202_28|1303_29|1304_30|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_4|1109_12|1110_16</t>
+  </si>
+  <si>
+    <t>1301_32|1202_28|1303_29|1304_30|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_4|1109_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_32|1202_28|1303_29|1304_30|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_8|1109_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_32|1202_33|1303_29|1304_30|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_8|1109_16|1110_16</t>
+  </si>
+  <si>
     <t>1112_1</t>
   </si>
   <si>
+    <t>1301_32|1202_33|1303_29|1304_30|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_12|1109_16|1110_16</t>
+  </si>
+  <si>
+    <t>1301_32|1202_33|1303_34|1304_30|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_12|1109_16|1110_16|1112_4</t>
+  </si>
+  <si>
+    <t>1301_32|1202_33|1303_34|1304_30|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_16|1109_16|1110_16|1112_4</t>
+  </si>
+  <si>
+    <t>1301_32|1202_33|1303_34|1304_35|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_16|1109_16|1110_16|1112_8</t>
+  </si>
+  <si>
     <t>1111_1</t>
+  </si>
+  <si>
+    <t>1301_37|1202_33|1303_34|1304_35|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_16|1109_16|1110_16|1112_12</t>
+  </si>
+  <si>
+    <t>1301_37|1202_33|1303_34|1304_35|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_16|1109_16|1110_16|1111_4|1112_12</t>
+  </si>
+  <si>
+    <t>1301_37|1202_38|1303_34|1304_35|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_16|1109_16|1110_16|1111_4|1112_16</t>
+  </si>
+  <si>
+    <t>1301_37|1202_38|1303_39|1304_35|1101_16|1102_16|1103_16|1104_16|1105_16|1106_16|1107_16|1108_16|1109_16|1110_16|1111_8|1112_16</t>
   </si>
   <si>
     <t>1101_5|1102_5|1110_5|1107_5|1103_5|1104_5|1105_5|1106_5|1111_5|1112_5|1108_5|1109_5</t>
@@ -1685,7 +1829,7 @@
         <v>5</v>
       </c>
       <c r="M5" s="13">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="N5" s="17">
         <v>0</v>
@@ -1735,7 +1879,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="13">
-        <v>1120</v>
+        <v>1500</v>
       </c>
       <c r="N6" s="17">
         <v>0</v>
@@ -1788,7 +1932,7 @@
         <v>5</v>
       </c>
       <c r="M7" s="13">
-        <v>2120</v>
+        <v>5400</v>
       </c>
       <c r="N7" s="17">
         <v>0</v>
@@ -1843,7 +1987,7 @@
         <v>5</v>
       </c>
       <c r="M8" s="13">
-        <v>3000</v>
+        <v>10800</v>
       </c>
       <c r="N8" s="17">
         <v>0</v>
@@ -1852,7 +1996,7 @@
         <v>90</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="4">
         <v>4</v>
@@ -1870,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="13">
         <v>5</v>
@@ -1898,7 +2042,7 @@
         <v>5</v>
       </c>
       <c r="M9" s="13">
-        <v>12600</v>
+        <v>10000</v>
       </c>
       <c r="N9" s="17">
         <v>0</v>
@@ -1907,7 +2051,7 @@
         <v>100</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q9" s="4">
         <v>5</v>
@@ -1925,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" s="13">
         <v>6</v>
@@ -1953,7 +2097,7 @@
         <v>5</v>
       </c>
       <c r="M10" s="13">
-        <v>10800</v>
+        <v>31000</v>
       </c>
       <c r="N10" s="17">
         <v>0</v>
@@ -1962,7 +2106,7 @@
         <v>110</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q10" s="4">
         <v>5</v>
@@ -1980,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" s="13">
         <v>7</v>
@@ -2008,7 +2152,7 @@
         <v>5</v>
       </c>
       <c r="M11" s="13">
-        <v>18650</v>
+        <v>36200</v>
       </c>
       <c r="N11" s="17">
         <v>0</v>
@@ -2017,7 +2161,7 @@
         <v>120</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q11" s="4">
         <v>6</v>
@@ -2035,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E12" s="13">
         <v>8</v>
@@ -2063,7 +2207,7 @@
         <v>5</v>
       </c>
       <c r="M12" s="13">
-        <v>22050</v>
+        <v>61200</v>
       </c>
       <c r="N12" s="17">
         <v>0</v>
@@ -2072,7 +2216,7 @@
         <v>130</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q12" s="4">
         <v>6</v>
@@ -2090,7 +2234,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E13" s="13">
         <v>9</v>
@@ -2118,7 +2262,7 @@
         <v>5</v>
       </c>
       <c r="M13" s="13">
-        <v>28925</v>
+        <v>66500</v>
       </c>
       <c r="N13" s="17">
         <v>0</v>
@@ -2127,7 +2271,7 @@
         <v>140</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q13" s="4">
         <v>6</v>
@@ -2145,7 +2289,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E14" s="13">
         <v>10</v>
@@ -2173,7 +2317,7 @@
         <v>5</v>
       </c>
       <c r="M14" s="13">
-        <v>34600</v>
+        <v>104000</v>
       </c>
       <c r="N14" s="17">
         <v>0</v>
@@ -2182,7 +2326,7 @@
         <v>150</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q14" s="4">
         <v>6</v>
@@ -2200,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E15" s="13">
         <v>11</v>
@@ -2228,7 +2372,7 @@
         <v>5</v>
       </c>
       <c r="M15" s="13">
-        <v>59600</v>
+        <v>195500</v>
       </c>
       <c r="N15" s="17">
         <v>0</v>
@@ -2237,7 +2381,7 @@
         <v>160</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Q15" s="4">
         <v>7</v>
@@ -2255,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E16" s="13">
         <v>12</v>
@@ -2283,7 +2427,7 @@
         <v>5</v>
       </c>
       <c r="M16" s="13">
-        <v>71600</v>
+        <v>240300</v>
       </c>
       <c r="N16" s="17">
         <v>0</v>
@@ -2292,7 +2436,7 @@
         <v>170</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="4">
         <v>7</v>
@@ -2310,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E17" s="13">
         <v>13</v>
@@ -2338,7 +2482,7 @@
         <v>5</v>
       </c>
       <c r="M17" s="13">
-        <v>78100</v>
+        <v>291400</v>
       </c>
       <c r="N17" s="17">
         <v>0</v>
@@ -2347,7 +2491,7 @@
         <v>180</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="Q17" s="4">
         <v>7</v>
@@ -2365,7 +2509,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E18" s="13">
         <v>14</v>
@@ -2393,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="M18" s="13">
-        <v>78800</v>
+        <v>294600</v>
       </c>
       <c r="N18" s="17">
         <v>0</v>
@@ -2402,7 +2546,7 @@
         <v>190</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="Q18" s="4">
         <v>7</v>
@@ -2420,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E19" s="13">
         <v>15</v>
@@ -2448,7 +2592,7 @@
         <v>5</v>
       </c>
       <c r="M19" s="13">
-        <v>90500</v>
+        <v>414200</v>
       </c>
       <c r="N19" s="17">
         <v>0</v>
@@ -2457,7 +2601,7 @@
         <v>200</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q19" s="4">
         <v>7</v>
@@ -2475,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E20" s="13">
         <v>16</v>
@@ -2503,7 +2647,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="13">
-        <v>103000</v>
+        <v>559300</v>
       </c>
       <c r="N20" s="17">
         <v>0</v>
@@ -2512,7 +2656,7 @@
         <v>210</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q20" s="4">
         <v>7</v>
@@ -2530,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E21" s="13">
         <v>17</v>
@@ -2558,7 +2702,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="13">
-        <v>116300</v>
+        <v>759900</v>
       </c>
       <c r="N21" s="17">
         <v>0</v>
@@ -2567,7 +2711,7 @@
         <v>220</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="Q21" s="4">
         <v>8</v>
@@ -2585,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E22" s="13">
         <v>18</v>
@@ -2613,7 +2757,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="13">
-        <v>130300</v>
+        <v>752000</v>
       </c>
       <c r="N22" s="17">
         <v>0</v>
@@ -2622,7 +2766,7 @@
         <v>230</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="Q22" s="4">
         <v>8</v>
@@ -2640,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E23" s="13">
         <v>19</v>
@@ -2668,7 +2812,7 @@
         <v>5</v>
       </c>
       <c r="M23" s="13">
-        <v>145200</v>
+        <v>999500</v>
       </c>
       <c r="N23" s="17">
         <v>0</v>
@@ -2677,7 +2821,7 @@
         <v>240</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Q23" s="4">
         <v>8</v>
@@ -2695,7 +2839,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E24" s="13">
         <v>20</v>
@@ -2723,7 +2867,7 @@
         <v>5</v>
       </c>
       <c r="M24" s="13">
-        <v>160900</v>
+        <v>983100</v>
       </c>
       <c r="N24" s="17">
         <v>0</v>
@@ -2732,7 +2876,7 @@
         <v>250</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="Q24" s="4">
         <v>8</v>
@@ -2750,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E25" s="13">
         <v>21</v>
@@ -2778,7 +2922,7 @@
         <v>5</v>
       </c>
       <c r="M25" s="13">
-        <v>177400</v>
+        <v>1637200</v>
       </c>
       <c r="N25" s="17">
         <v>0</v>
@@ -2787,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="Q25" s="4">
         <v>8</v>
@@ -2805,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E26" s="13">
         <v>22</v>
@@ -2833,7 +2977,7 @@
         <v>5</v>
       </c>
       <c r="M26" s="13">
-        <v>194700</v>
+        <v>1607900</v>
       </c>
       <c r="N26" s="17">
         <v>0</v>
@@ -2842,7 +2986,7 @@
         <v>270</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="Q26" s="4">
         <v>8</v>
@@ -2860,7 +3004,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E27" s="13">
         <v>23</v>
@@ -2888,7 +3032,7 @@
         <v>5</v>
       </c>
       <c r="M27" s="13">
-        <v>212800</v>
+        <v>2057900</v>
       </c>
       <c r="N27" s="17">
         <v>0</v>
@@ -2897,7 +3041,7 @@
         <v>280</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="Q27" s="4">
         <v>9</v>
@@ -2915,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E28" s="13">
         <v>24</v>
@@ -2943,7 +3087,7 @@
         <v>5</v>
       </c>
       <c r="M28" s="13">
-        <v>231700</v>
+        <v>2018500</v>
       </c>
       <c r="N28" s="17">
         <v>0</v>
@@ -2952,7 +3096,7 @@
         <v>290</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="Q28" s="4">
         <v>9</v>
@@ -2970,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E29" s="13">
         <v>25</v>
@@ -2998,7 +3142,7 @@
         <v>5</v>
       </c>
       <c r="M29" s="13">
-        <v>251400</v>
+        <v>2549600</v>
       </c>
       <c r="N29" s="17">
         <v>0</v>
@@ -3007,7 +3151,7 @@
         <v>300</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="Q29" s="4">
         <v>9</v>
@@ -3025,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E30" s="13">
         <v>26</v>
@@ -3053,7 +3197,7 @@
         <v>5</v>
       </c>
       <c r="M30" s="13">
-        <v>271900</v>
+        <v>3090000</v>
       </c>
       <c r="N30" s="17">
         <v>0</v>
@@ -3062,7 +3206,7 @@
         <v>310</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="Q30" s="4">
         <v>9</v>
@@ -3080,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E31" s="13">
         <v>27</v>
@@ -3108,7 +3252,7 @@
         <v>5</v>
       </c>
       <c r="M31" s="13">
-        <v>293300</v>
+        <v>3834500</v>
       </c>
       <c r="N31" s="17">
         <v>0</v>
@@ -3117,7 +3261,7 @@
         <v>320</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="Q31" s="4">
         <v>9</v>
@@ -3135,7 +3279,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E32" s="13">
         <v>28</v>
@@ -3163,7 +3307,7 @@
         <v>5</v>
       </c>
       <c r="M32" s="13">
-        <v>315400</v>
+        <v>3758300</v>
       </c>
       <c r="N32" s="17">
         <v>0</v>
@@ -3172,7 +3316,7 @@
         <v>330</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="Q32" s="4">
         <v>9</v>
@@ -3190,7 +3334,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E33" s="13">
         <v>29</v>
@@ -3218,7 +3362,7 @@
         <v>5</v>
       </c>
       <c r="M33" s="13">
-        <v>338300</v>
+        <v>4613400</v>
       </c>
       <c r="N33" s="17">
         <v>0</v>
@@ -3227,7 +3371,7 @@
         <v>340</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Q33" s="4">
         <v>9</v>
@@ -3245,7 +3389,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E34" s="13">
         <v>30</v>
@@ -3273,7 +3417,7 @@
         <v>5</v>
       </c>
       <c r="M34" s="13">
-        <v>362100</v>
+        <v>4516900</v>
       </c>
       <c r="N34" s="17">
         <v>0</v>
@@ -3282,7 +3426,7 @@
         <v>350</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="Q34" s="4">
         <v>10</v>
@@ -3300,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E35" s="13">
         <v>31</v>
@@ -3328,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="M35" s="13">
-        <v>386600</v>
+        <v>6611700</v>
       </c>
       <c r="N35" s="17">
         <v>0</v>
@@ -3337,7 +3481,7 @@
         <v>360</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="Q35" s="4">
         <v>10</v>
@@ -3355,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E36" s="13">
         <v>32</v>
@@ -3383,7 +3527,7 @@
         <v>5</v>
       </c>
       <c r="M36" s="13">
-        <v>411900</v>
+        <v>6489900</v>
       </c>
       <c r="N36" s="17">
         <v>0</v>
@@ -3392,7 +3536,7 @@
         <v>370</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="Q36" s="4">
         <v>10</v>
@@ -3410,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E37" s="13">
         <v>33</v>
@@ -3438,7 +3582,7 @@
         <v>5</v>
       </c>
       <c r="M37" s="13">
-        <v>438100</v>
+        <v>7792700</v>
       </c>
       <c r="N37" s="17">
         <v>0</v>
@@ -3447,7 +3591,7 @@
         <v>380</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="Q37" s="4">
         <v>10</v>
@@ -3465,7 +3609,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E38" s="13">
         <v>34</v>
@@ -3493,7 +3637,7 @@
         <v>5</v>
       </c>
       <c r="M38" s="13">
-        <v>465000</v>
+        <v>8436900</v>
       </c>
       <c r="N38" s="17">
         <v>0</v>
@@ -3502,7 +3646,7 @@
         <v>390</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="Q38" s="4">
         <v>10</v>
@@ -3520,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E39" s="13">
         <v>35</v>
@@ -3548,7 +3692,7 @@
         <v>5</v>
       </c>
       <c r="M39" s="13">
-        <v>492800</v>
+        <v>9117900</v>
       </c>
       <c r="N39" s="17">
         <v>0</v>
@@ -3557,7 +3701,7 @@
         <v>400</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="Q39" s="4">
         <v>10</v>
@@ -3575,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E40" s="13">
         <v>36</v>
@@ -3603,7 +3747,7 @@
         <v>5</v>
       </c>
       <c r="M40" s="13">
-        <v>521400</v>
+        <v>11631700</v>
       </c>
       <c r="N40" s="17">
         <v>0</v>
@@ -3612,7 +3756,7 @@
         <v>410</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="Q40" s="4">
         <v>10</v>
@@ -3630,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E41" s="13">
         <v>37</v>
@@ -3658,7 +3802,7 @@
         <v>5</v>
       </c>
       <c r="M41" s="13">
-        <v>550700</v>
+        <v>11449200</v>
       </c>
       <c r="N41" s="17">
         <v>0</v>
@@ -3667,7 +3811,7 @@
         <v>420</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="Q41" s="4">
         <v>11</v>
@@ -3685,7 +3829,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E42" s="13">
         <v>38</v>
@@ -3713,7 +3857,7 @@
         <v>5</v>
       </c>
       <c r="M42" s="13">
-        <v>580900</v>
+        <v>13442600</v>
       </c>
       <c r="N42" s="17">
         <v>0</v>
@@ -3722,7 +3866,7 @@
         <v>430</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="Q42" s="4">
         <v>11</v>
@@ -3740,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E43" s="13">
         <v>39</v>
@@ -3768,7 +3912,7 @@
         <v>5</v>
       </c>
       <c r="M43" s="13">
-        <v>611900</v>
+        <v>13229700</v>
       </c>
       <c r="N43" s="17">
         <v>0</v>
@@ -3777,7 +3921,7 @@
         <v>440</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="Q43" s="4">
         <v>11</v>
@@ -3795,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E44" s="13">
         <v>40</v>
@@ -3823,7 +3967,7 @@
         <v>5</v>
       </c>
       <c r="M44" s="13">
-        <v>643700</v>
+        <v>15434300</v>
       </c>
       <c r="N44" s="17">
         <v>0</v>
@@ -3832,7 +3976,7 @@
         <v>450</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="Q44" s="4">
         <v>11</v>
@@ -3850,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E45" s="13">
         <v>41</v>
@@ -3878,7 +4022,7 @@
         <v>5</v>
       </c>
       <c r="M45" s="13">
-        <v>676200</v>
+        <v>17769300</v>
       </c>
       <c r="N45" s="17">
         <v>0</v>
@@ -3887,7 +4031,7 @@
         <v>460</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="Q45" s="4">
         <v>11</v>
@@ -3905,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E46" s="13">
         <v>42</v>
@@ -3933,7 +4077,7 @@
         <v>5</v>
       </c>
       <c r="M46" s="13">
-        <v>709600</v>
+        <v>20542800</v>
       </c>
       <c r="N46" s="17">
         <v>0</v>
@@ -3942,7 +4086,7 @@
         <v>470</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="Q46" s="4">
         <v>11</v>
@@ -3960,7 +4104,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E47" s="13">
         <v>43</v>
@@ -3988,7 +4132,7 @@
         <v>5</v>
       </c>
       <c r="M47" s="13">
-        <v>743800</v>
+        <v>20277200</v>
       </c>
       <c r="N47" s="17">
         <v>0</v>
@@ -3997,7 +4141,7 @@
         <v>480</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="Q47" s="4">
         <v>12</v>
@@ -4015,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E48" s="13">
         <v>44</v>
@@ -4043,7 +4187,7 @@
         <v>5</v>
       </c>
       <c r="M48" s="13">
-        <v>778800</v>
+        <v>23326500</v>
       </c>
       <c r="N48" s="17">
         <v>0</v>
@@ -4052,7 +4196,7 @@
         <v>490</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="Q48" s="4">
         <v>12</v>
@@ -4070,7 +4214,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E49" s="13">
         <v>45</v>
@@ -4098,7 +4242,7 @@
         <v>5</v>
       </c>
       <c r="M49" s="13">
-        <v>814600</v>
+        <v>23032600</v>
       </c>
       <c r="N49" s="17">
         <v>0</v>
@@ -4107,7 +4251,7 @@
         <v>500</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="Q49" s="4">
         <v>12</v>
@@ -4125,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E50" s="13">
         <v>46</v>
@@ -4153,7 +4297,7 @@
         <v>5</v>
       </c>
       <c r="M50" s="13">
-        <v>851200</v>
+        <v>30396800</v>
       </c>
       <c r="N50" s="17">
         <v>0</v>
@@ -4162,7 +4306,7 @@
         <v>510</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="Q50" s="4">
         <v>12</v>
@@ -4180,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="E51" s="13">
         <v>47</v>
@@ -4208,7 +4352,7 @@
         <v>5</v>
       </c>
       <c r="M51" s="13">
-        <v>888700</v>
+        <v>30084400</v>
       </c>
       <c r="N51" s="17">
         <v>0</v>
@@ -4217,7 +4361,7 @@
         <v>520</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="Q51" s="4">
         <v>12</v>
@@ -4235,7 +4379,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E52" s="13">
         <v>48</v>
@@ -4263,7 +4407,7 @@
         <v>5</v>
       </c>
       <c r="M52" s="13">
-        <v>926900</v>
+        <v>34172100</v>
       </c>
       <c r="N52" s="17">
         <v>0</v>
@@ -4272,7 +4416,7 @@
         <v>530</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="Q52" s="4">
         <v>12</v>
@@ -4290,7 +4434,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E53" s="13">
         <v>49</v>
@@ -4318,7 +4462,7 @@
         <v>5</v>
       </c>
       <c r="M53" s="13">
-        <v>965900</v>
+        <v>36173900</v>
       </c>
       <c r="N53" s="17">
         <v>0</v>
@@ -4327,7 +4471,7 @@
         <v>540</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="Q53" s="4">
         <v>12</v>
@@ -4345,7 +4489,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E54" s="13">
         <v>50</v>
@@ -4373,7 +4517,7 @@
         <v>5</v>
       </c>
       <c r="M54" s="13">
-        <v>1005700</v>
+        <v>38253200</v>
       </c>
       <c r="N54" s="17">
         <v>0</v>
@@ -4382,7 +4526,7 @@
         <v>550</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="Q54" s="4">
         <v>12</v>
@@ -4400,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E55" s="13">
         <v>51</v>
@@ -4428,7 +4572,7 @@
         <v>5</v>
       </c>
       <c r="M55" s="13">
-        <v>1046400</v>
+        <v>46145600</v>
       </c>
       <c r="N55" s="17">
         <v>0</v>
@@ -4437,7 +4581,7 @@
         <v>560</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="Q55" s="4">
         <v>13</v>
@@ -4455,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="E56" s="13">
         <v>52</v>
@@ -4483,7 +4627,7 @@
         <v>5</v>
       </c>
       <c r="M56" s="13">
-        <v>1087800</v>
+        <v>45780900</v>
       </c>
       <c r="N56" s="17">
         <v>0</v>
@@ -4492,7 +4636,7 @@
         <v>570</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="Q56" s="4">
         <v>13</v>
@@ -4510,7 +4654,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E57" s="13">
         <v>53</v>
@@ -4538,7 +4682,7 @@
         <v>5</v>
       </c>
       <c r="M57" s="13">
-        <v>1130000</v>
+        <v>51352500</v>
       </c>
       <c r="N57" s="17">
         <v>0</v>
@@ -4547,7 +4691,7 @@
         <v>580</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="Q57" s="4">
         <v>13</v>
@@ -4565,7 +4709,7 @@
         <v>1</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E58" s="13">
         <v>54</v>
@@ -4593,7 +4737,7 @@
         <v>5</v>
       </c>
       <c r="M58" s="13">
-        <v>1173100</v>
+        <v>50960700</v>
       </c>
       <c r="N58" s="17">
         <v>0</v>
@@ -4602,7 +4746,7 @@
         <v>590</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="Q58" s="4">
         <v>13</v>
@@ -4620,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E59" s="13">
         <v>55</v>
@@ -4648,7 +4792,7 @@
         <v>5</v>
       </c>
       <c r="M59" s="13">
-        <v>1216900</v>
+        <v>56969400</v>
       </c>
       <c r="N59" s="17">
         <v>0</v>
@@ -4657,7 +4801,7 @@
         <v>600</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="Q59" s="4">
         <v>13</v>
@@ -4675,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E60" s="13">
         <v>56</v>
@@ -4703,7 +4847,7 @@
         <v>5</v>
       </c>
       <c r="M60" s="13">
-        <v>1261600</v>
+        <v>64165800</v>
       </c>
       <c r="N60" s="17">
         <v>0</v>
@@ -4712,7 +4856,7 @@
         <v>610</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="Q60" s="4">
         <v>14</v>
@@ -4730,7 +4874,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="E61" s="13">
         <v>57</v>
@@ -4758,7 +4902,7 @@
         <v>5</v>
       </c>
       <c r="M61" s="13">
-        <v>1307000</v>
+        <v>71313200</v>
       </c>
       <c r="N61" s="17">
         <v>0</v>
@@ -4767,7 +4911,7 @@
         <v>620</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="4">
         <v>14</v>
@@ -4811,7 +4955,7 @@
         <v>5</v>
       </c>
       <c r="M62" s="13">
-        <v>1353300</v>
+        <v>70915300</v>
       </c>
       <c r="N62" s="17">
         <v>0</v>
@@ -4820,7 +4964,7 @@
         <v>630</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="Q62" s="4">
         <v>14</v>
@@ -4864,7 +5008,7 @@
         <v>5</v>
       </c>
       <c r="M63" s="13">
-        <v>1400400</v>
+        <v>74465300</v>
       </c>
       <c r="N63" s="17">
         <v>0</v>
@@ -4873,7 +5017,7 @@
         <v>640</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="Q63" s="4">
         <v>14</v>
@@ -4917,7 +5061,7 @@
         <v>5</v>
       </c>
       <c r="M64" s="13">
-        <v>1448200</v>
+        <v>78133700</v>
       </c>
       <c r="N64" s="17">
         <v>0</v>
@@ -4926,7 +5070,7 @@
         <v>650</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q64" s="4">
         <v>14</v>
@@ -4971,7 +5115,7 @@
         <v>5</v>
       </c>
       <c r="M65" s="13">
-        <v>1496900</v>
+        <v>73802600</v>
       </c>
       <c r="N65" s="17">
         <v>0</v>
@@ -4980,7 +5124,7 @@
         <v>660</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q65" s="4">
         <v>14</v>
@@ -5025,7 +5169,7 @@
         <v>5</v>
       </c>
       <c r="M66" s="13">
-        <v>1546400</v>
+        <v>77303100</v>
       </c>
       <c r="N66" s="17">
         <v>0</v>
@@ -5034,7 +5178,7 @@
         <v>670</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q66" s="4">
         <v>14</v>
@@ -5079,7 +5223,7 @@
         <v>5</v>
       </c>
       <c r="M67" s="13">
-        <v>1596700</v>
+        <v>80920800</v>
       </c>
       <c r="N67" s="17">
         <v>0</v>
@@ -5088,7 +5232,7 @@
         <v>680</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q67" s="4">
         <v>14</v>
@@ -5133,7 +5277,7 @@
         <v>5</v>
       </c>
       <c r="M68" s="13">
-        <v>1647800</v>
+        <v>84656500</v>
       </c>
       <c r="N68" s="17">
         <v>0</v>
@@ -5142,7 +5286,7 @@
         <v>690</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q68" s="4">
         <v>14</v>
@@ -5187,7 +5331,7 @@
         <v>5</v>
       </c>
       <c r="M69" s="13">
-        <v>1699700</v>
+        <v>88510800</v>
       </c>
       <c r="N69" s="17">
         <v>0</v>
@@ -5196,7 +5340,7 @@
         <v>700</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q69" s="4">
         <v>14</v>
@@ -5241,7 +5385,7 @@
         <v>5</v>
       </c>
       <c r="M70" s="13">
-        <v>1752400</v>
+        <v>92086600</v>
       </c>
       <c r="N70" s="17">
         <v>0</v>
@@ -5250,7 +5394,7 @@
         <v>710</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q70" s="4">
         <v>14</v>
@@ -5295,7 +5439,7 @@
         <v>5</v>
       </c>
       <c r="M71" s="13">
-        <v>1805900</v>
+        <v>95806900</v>
       </c>
       <c r="N71" s="17">
         <v>0</v>
@@ -5304,7 +5448,7 @@
         <v>720</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q71" s="4">
         <v>14</v>
@@ -5349,7 +5493,7 @@
         <v>5</v>
       </c>
       <c r="M72" s="13">
-        <v>1860200</v>
+        <v>99677500</v>
       </c>
       <c r="N72" s="17">
         <v>0</v>
@@ -5358,7 +5502,7 @@
         <v>730</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q72" s="4">
         <v>14</v>
@@ -5403,7 +5547,7 @@
         <v>5</v>
       </c>
       <c r="M73" s="13">
-        <v>1915300</v>
+        <v>103704500</v>
       </c>
       <c r="N73" s="17">
         <v>0</v>
@@ -5412,7 +5556,7 @@
         <v>740</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q73" s="4">
         <v>14</v>
@@ -5457,7 +5601,7 @@
         <v>5</v>
       </c>
       <c r="M74" s="13">
-        <v>1971200</v>
+        <v>107894100</v>
       </c>
       <c r="N74" s="17">
         <v>0</v>
@@ -5466,7 +5610,7 @@
         <v>750</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q74" s="4">
         <v>14</v>
@@ -5511,7 +5655,7 @@
         <v>5</v>
       </c>
       <c r="M75" s="13">
-        <v>2027900</v>
+        <v>112253100</v>
       </c>
       <c r="N75" s="17">
         <v>0</v>
@@ -5520,7 +5664,7 @@
         <v>760</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q75" s="4">
         <v>14</v>
@@ -5565,7 +5709,7 @@
         <v>5</v>
       </c>
       <c r="M76" s="13">
-        <v>2085500</v>
+        <v>116788100</v>
       </c>
       <c r="N76" s="17">
         <v>0</v>
@@ -5574,7 +5718,7 @@
         <v>770</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q76" s="4">
         <v>14</v>
@@ -5619,7 +5763,7 @@
         <v>5</v>
       </c>
       <c r="M77" s="13">
-        <v>2143800</v>
+        <v>121506300</v>
       </c>
       <c r="N77" s="17">
         <v>0</v>
@@ -5628,7 +5772,7 @@
         <v>780</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q77" s="4">
         <v>14</v>
@@ -5673,7 +5817,7 @@
         <v>5</v>
       </c>
       <c r="M78" s="13">
-        <v>2202900</v>
+        <v>126415200</v>
       </c>
       <c r="N78" s="17">
         <v>0</v>
@@ -5682,7 +5826,7 @@
         <v>790</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q78" s="4">
         <v>14</v>
@@ -5727,7 +5871,7 @@
         <v>5</v>
       </c>
       <c r="M79" s="13">
-        <v>2262900</v>
+        <v>131522400</v>
       </c>
       <c r="N79" s="17">
         <v>0</v>
@@ -5736,7 +5880,7 @@
         <v>800</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q79" s="4">
         <v>14</v>
@@ -5781,7 +5925,7 @@
         <v>5</v>
       </c>
       <c r="M80" s="13">
-        <v>2323600</v>
+        <v>136835900</v>
       </c>
       <c r="N80" s="17">
         <v>0</v>
@@ -5790,7 +5934,7 @@
         <v>810</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q80" s="4">
         <v>14</v>
@@ -5835,7 +5979,7 @@
         <v>5</v>
       </c>
       <c r="M81" s="13">
-        <v>2385200</v>
+        <v>142364000</v>
       </c>
       <c r="N81" s="17">
         <v>0</v>
@@ -5844,7 +5988,7 @@
         <v>820</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q81" s="4">
         <v>14</v>
@@ -5889,7 +6033,7 @@
         <v>5</v>
       </c>
       <c r="M82" s="13">
-        <v>2447500</v>
+        <v>148115500</v>
       </c>
       <c r="N82" s="17">
         <v>0</v>
@@ -5898,7 +6042,7 @@
         <v>830</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q82" s="4">
         <v>14</v>
@@ -5943,7 +6087,7 @@
         <v>5</v>
       </c>
       <c r="M83" s="13">
-        <v>2510700</v>
+        <v>154099400</v>
       </c>
       <c r="N83" s="17">
         <v>0</v>
@@ -5952,7 +6096,7 @@
         <v>840</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q83" s="4">
         <v>14</v>
@@ -5997,7 +6141,7 @@
         <v>5</v>
       </c>
       <c r="M84" s="13">
-        <v>2574600</v>
+        <v>160325000</v>
       </c>
       <c r="N84" s="17">
         <v>0</v>
@@ -6006,7 +6150,7 @@
         <v>850</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q84" s="4">
         <v>14</v>
@@ -6051,7 +6195,7 @@
         <v>5</v>
       </c>
       <c r="M85" s="13">
-        <v>2639400</v>
+        <v>166802100</v>
       </c>
       <c r="N85" s="17">
         <v>0</v>
@@ -6060,7 +6204,7 @@
         <v>860</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q85" s="4">
         <v>14</v>
@@ -6105,7 +6249,7 @@
         <v>5</v>
       </c>
       <c r="M86" s="13">
-        <v>2705000</v>
+        <v>173541000</v>
       </c>
       <c r="N86" s="17">
         <v>0</v>
@@ -6114,7 +6258,7 @@
         <v>870</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q86" s="4">
         <v>14</v>
@@ -6159,7 +6303,7 @@
         <v>5</v>
       </c>
       <c r="M87" s="13">
-        <v>2771400</v>
+        <v>180552000</v>
       </c>
       <c r="N87" s="17">
         <v>0</v>
@@ -6168,7 +6312,7 @@
         <v>880</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q87" s="4">
         <v>14</v>
@@ -6213,7 +6357,7 @@
         <v>5</v>
       </c>
       <c r="M88" s="13">
-        <v>2838500</v>
+        <v>187846300</v>
       </c>
       <c r="N88" s="17">
         <v>0</v>
@@ -6222,7 +6366,7 @@
         <v>890</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q88" s="4">
         <v>14</v>
@@ -6267,7 +6411,7 @@
         <v>5</v>
       </c>
       <c r="M89" s="13">
-        <v>2906500</v>
+        <v>195435300</v>
       </c>
       <c r="N89" s="17">
         <v>0</v>
@@ -6276,7 +6420,7 @@
         <v>900</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q89" s="4">
         <v>14</v>
@@ -6321,7 +6465,7 @@
         <v>5</v>
       </c>
       <c r="M90" s="13">
-        <v>2975300</v>
+        <v>203330900</v>
       </c>
       <c r="N90" s="17">
         <v>0</v>
@@ -6330,7 +6474,7 @@
         <v>910</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q90" s="4">
         <v>14</v>
@@ -6375,7 +6519,7 @@
         <v>5</v>
       </c>
       <c r="M91" s="13">
-        <v>3044900</v>
+        <v>211545500</v>
       </c>
       <c r="N91" s="17">
         <v>0</v>
@@ -6384,7 +6528,7 @@
         <v>920</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q91" s="4">
         <v>14</v>
@@ -6429,7 +6573,7 @@
         <v>5</v>
       </c>
       <c r="M92" s="13">
-        <v>3115300</v>
+        <v>220091900</v>
       </c>
       <c r="N92" s="17">
         <v>0</v>
@@ -6438,7 +6582,7 @@
         <v>930</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q92" s="4">
         <v>14</v>
@@ -6483,7 +6627,7 @@
         <v>5</v>
       </c>
       <c r="M93" s="13">
-        <v>3186500</v>
+        <v>228983600</v>
       </c>
       <c r="N93" s="17">
         <v>0</v>
@@ -6492,7 +6636,7 @@
         <v>940</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q93" s="4">
         <v>14</v>
@@ -6537,7 +6681,7 @@
         <v>5</v>
       </c>
       <c r="M94" s="13">
-        <v>3258500</v>
+        <v>238234500</v>
       </c>
       <c r="N94" s="17">
         <v>0</v>
@@ -6546,7 +6690,7 @@
         <v>950</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q94" s="4">
         <v>14</v>
@@ -6591,7 +6735,7 @@
         <v>5</v>
       </c>
       <c r="M95" s="13">
-        <v>3331300</v>
+        <v>247859200</v>
       </c>
       <c r="N95" s="17">
         <v>0</v>
@@ -6600,7 +6744,7 @@
         <v>960</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q95" s="4">
         <v>14</v>
@@ -6645,7 +6789,7 @@
         <v>5</v>
       </c>
       <c r="M96" s="13">
-        <v>3405000</v>
+        <v>257872700</v>
       </c>
       <c r="N96" s="17">
         <v>0</v>
@@ -6654,7 +6798,7 @@
         <v>970</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q96" s="4">
         <v>14</v>
@@ -6699,7 +6843,7 @@
         <v>5</v>
       </c>
       <c r="M97" s="13">
-        <v>3479400</v>
+        <v>268290800</v>
       </c>
       <c r="N97" s="17">
         <v>0</v>
@@ -6708,7 +6852,7 @@
         <v>980</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q97" s="4">
         <v>14</v>
@@ -6753,7 +6897,7 @@
         <v>5</v>
       </c>
       <c r="M98" s="13">
-        <v>3554600</v>
+        <v>279129700</v>
       </c>
       <c r="N98" s="17">
         <v>0</v>
@@ -6762,7 +6906,7 @@
         <v>990</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q98" s="4">
         <v>14</v>
@@ -6807,7 +6951,7 @@
         <v>5</v>
       </c>
       <c r="M99" s="13">
-        <v>3630700</v>
+        <v>290406600</v>
       </c>
       <c r="N99" s="17">
         <v>0</v>
@@ -6816,7 +6960,7 @@
         <v>1000</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q99" s="4">
         <v>14</v>
@@ -6861,7 +7005,7 @@
         <v>5</v>
       </c>
       <c r="M100" s="13">
-        <v>3707500</v>
+        <v>302139000</v>
       </c>
       <c r="N100" s="17">
         <v>0</v>
@@ -6870,7 +7014,7 @@
         <v>1010</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q100" s="4">
         <v>14</v>
@@ -6915,7 +7059,7 @@
         <v>5</v>
       </c>
       <c r="M101" s="13">
-        <v>3785100</v>
+        <v>314345400</v>
       </c>
       <c r="N101" s="17">
         <v>0</v>
@@ -6924,7 +7068,7 @@
         <v>1020</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q101" s="4">
         <v>14</v>
@@ -6969,7 +7113,7 @@
         <v>5</v>
       </c>
       <c r="M102" s="13">
-        <v>3863600</v>
+        <v>327045000</v>
       </c>
       <c r="N102" s="17">
         <v>0</v>
@@ -6978,7 +7122,7 @@
         <v>1030</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q102" s="4">
         <v>14</v>
@@ -7023,7 +7167,7 @@
         <v>5</v>
       </c>
       <c r="M103" s="13">
-        <v>99999999</v>
+        <v>340257600</v>
       </c>
       <c r="N103" s="17">
         <v>0</v>
@@ -7032,7 +7176,7 @@
         <v>1040</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="Q103" s="4">
         <v>14</v>
@@ -7171,7 +7315,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -7192,7 +7336,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -7213,7 +7357,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -7234,7 +7378,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -7255,7 +7399,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7276,7 +7420,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -7297,7 +7441,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -7318,7 +7462,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -7339,7 +7483,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -7360,7 +7504,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7381,7 +7525,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -7402,7 +7546,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -7423,7 +7567,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="2" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -7444,251 +7588,251 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="B23" s="2"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="B25" s="2"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="B28" s="2"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="B30" s="2"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="B32" s="2"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="B34" s="2"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="B35" s="2"/>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="B36" s="2"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="B37" s="2"/>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="B38" s="2"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="B39" s="2"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="B40" s="2"/>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="B41" s="2"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="B42" s="2"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="B44" s="2"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="B45" s="2"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="B46" s="2"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B47" s="2"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B48" s="2"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B49" s="2"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B50" s="2"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B51" s="2"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="B52" s="2"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="B53" s="2"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="B54" s="2"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="B55" s="2"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="B56" s="2"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="B57" s="2"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
